--- a/input/Anjar_manning.xlsx
+++ b/input/Anjar_manning.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/Manning_FInal_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="13_ncr:1_{45658262-96CC-4946-9B46-BB1FC1723B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B10BFC4-2EB2-401E-8B93-CFA5B36898E8}"/>
+  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{45658262-96CC-4946-9B46-BB1FC1723B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8435356F-C94B-4189-B563-851A0E7B345E}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
   </bookViews>
   <sheets>
     <sheet name="Anjar" sheetId="1" r:id="rId1"/>
+    <sheet name="Spinning" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anjar!$A$1:$W$450</definedName>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="901">
   <si>
     <t>Location</t>
   </si>
@@ -3197,7 +3198,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3259,7 +3260,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3327,7 +3328,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3395,7 +3396,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3463,7 +3464,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3599,7 +3600,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3655,7 +3656,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3723,7 +3724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3782,7 +3783,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -3844,7 +3845,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3903,7 +3904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3971,7 +3972,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -4033,7 +4034,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4095,7 +4096,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -4157,7 +4158,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -4219,7 +4220,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -4281,7 +4282,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4343,7 +4344,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -4405,7 +4406,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -4467,7 +4468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -4529,7 +4530,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -4597,7 +4598,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -4659,7 +4660,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -4721,7 +4722,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -4783,7 +4784,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -4845,7 +4846,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -4907,7 +4908,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -4969,7 +4970,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -5031,7 +5032,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -5093,7 +5094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -5155,7 +5156,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -5217,7 +5218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="34" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -5285,7 +5286,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -5347,7 +5348,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>22</v>
       </c>
@@ -5409,7 +5410,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -5471,7 +5472,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -5539,7 +5540,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -5601,7 +5602,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -5663,7 +5664,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -5725,7 +5726,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -5787,7 +5788,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -5846,7 +5847,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -5905,7 +5906,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -6023,7 +6024,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -6082,7 +6083,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -6141,7 +6142,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -6200,7 +6201,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -6259,7 +6260,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="51" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -6318,7 +6319,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="52" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -6377,7 +6378,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="53" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -6445,7 +6446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="55" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -6581,7 +6582,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -6649,7 +6650,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -6773,7 +6774,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -6841,7 +6842,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -6903,7 +6904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -6953,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -7003,7 +7004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:23" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>22</v>
       </c>
@@ -31447,21 +31448,5746 @@
   <autoFilter ref="A1:W450" xr:uid="{80233CC7-9F29-4521-9F43-292ADE3B342B}">
     <filterColumn colId="1">
       <filters>
+        <filter val="Open End"/>
         <filter val="Spinning"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Engg &amp; Utility"/>
-        <filter val="Spinning - 3 Auto-Corner"/>
-        <filter val="Spinning 3 - Preparatory"/>
-        <filter val="Spinning 3 - Ring Frame"/>
-        <filter val="Spinning -3 Contractor"/>
-        <filter val="Spinning Maintenance"/>
-        <filter val="Spinning Quality Control-TQM"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D549529-A98F-4A5A-AF79-6F36A9D03A7C}">
+  <dimension ref="A1:W92"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>851</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" t="s">
+        <v>852</v>
+      </c>
+      <c r="J2" t="s">
+        <v>312</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="W2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>7</v>
+      </c>
+      <c r="H3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>6</v>
+      </c>
+      <c r="O3">
+        <v>6</v>
+      </c>
+      <c r="P3">
+        <v>3</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>2</v>
+      </c>
+      <c r="S3">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <v>2</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>12</v>
+      </c>
+      <c r="O4">
+        <v>12</v>
+      </c>
+      <c r="P4">
+        <v>3</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <v>4</v>
+      </c>
+      <c r="T4">
+        <v>4</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4" t="s">
+        <v>36</v>
+      </c>
+      <c r="W4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>15</v>
+      </c>
+      <c r="O5">
+        <v>15</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5" t="s">
+        <v>40</v>
+      </c>
+      <c r="W5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>854</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>12</v>
+      </c>
+      <c r="O6">
+        <v>12</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>4</v>
+      </c>
+      <c r="S6">
+        <v>4</v>
+      </c>
+      <c r="T6">
+        <v>4</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6" t="s">
+        <v>44</v>
+      </c>
+      <c r="W6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K7">
+        <v>21</v>
+      </c>
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>21</v>
+      </c>
+      <c r="O7">
+        <v>21</v>
+      </c>
+      <c r="P7">
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>7</v>
+      </c>
+      <c r="S7">
+        <v>7</v>
+      </c>
+      <c r="T7">
+        <v>7</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7" t="s">
+        <v>47</v>
+      </c>
+      <c r="W7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" t="s">
+        <v>853</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="W8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9">
+        <v>9</v>
+      </c>
+      <c r="L9" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>9</v>
+      </c>
+      <c r="O9">
+        <v>9</v>
+      </c>
+      <c r="P9">
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>3</v>
+      </c>
+      <c r="S9">
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>301</v>
+      </c>
+      <c r="J10" t="s">
+        <v>853</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="W10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" t="s">
+        <v>864</v>
+      </c>
+      <c r="J11" t="s">
+        <v>232</v>
+      </c>
+      <c r="K11">
+        <v>3</v>
+      </c>
+      <c r="L11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>3</v>
+      </c>
+      <c r="O11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12">
+        <v>6</v>
+      </c>
+      <c r="L12" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>6</v>
+      </c>
+      <c r="O12">
+        <v>6</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+      <c r="S12">
+        <v>2</v>
+      </c>
+      <c r="T12">
+        <v>2</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" t="s">
+        <v>856</v>
+      </c>
+      <c r="K13">
+        <v>36</v>
+      </c>
+      <c r="L13" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13">
+        <v>6</v>
+      </c>
+      <c r="N13">
+        <v>30</v>
+      </c>
+      <c r="O13">
+        <v>36</v>
+      </c>
+      <c r="P13">
+        <v>3</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>12</v>
+      </c>
+      <c r="S13">
+        <v>12</v>
+      </c>
+      <c r="T13">
+        <v>12</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13" t="s">
+        <v>60</v>
+      </c>
+      <c r="W13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14">
+        <v>2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" t="s">
+        <v>855</v>
+      </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>12</v>
+      </c>
+      <c r="O14">
+        <v>12</v>
+      </c>
+      <c r="P14">
+        <v>3</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>4</v>
+      </c>
+      <c r="S14">
+        <v>4</v>
+      </c>
+      <c r="T14">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="W14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15">
+        <v>3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
+        <v>857</v>
+      </c>
+      <c r="K15">
+        <v>9</v>
+      </c>
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>9</v>
+      </c>
+      <c r="O15">
+        <v>9</v>
+      </c>
+      <c r="P15">
+        <v>3</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>3</v>
+      </c>
+      <c r="S15">
+        <v>3</v>
+      </c>
+      <c r="T15">
+        <v>3</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="W15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" t="s">
+        <v>69</v>
+      </c>
+      <c r="J16" t="s">
+        <v>858</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>6</v>
+      </c>
+      <c r="O16">
+        <v>6</v>
+      </c>
+      <c r="P16">
+        <v>3</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+      <c r="S16">
+        <v>2</v>
+      </c>
+      <c r="T16">
+        <v>2</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="W16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" t="s">
+        <v>855</v>
+      </c>
+      <c r="K17">
+        <v>12</v>
+      </c>
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>12</v>
+      </c>
+      <c r="O17">
+        <v>12</v>
+      </c>
+      <c r="P17">
+        <v>3</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>4</v>
+      </c>
+      <c r="S17">
+        <v>4</v>
+      </c>
+      <c r="T17">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="W17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18">
+        <v>6</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" t="s">
+        <v>859</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>3</v>
+      </c>
+      <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="P18">
+        <v>3</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="W18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s">
+        <v>76</v>
+      </c>
+      <c r="J19" t="s">
+        <v>860</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>2</v>
+      </c>
+      <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0.67</v>
+      </c>
+      <c r="S19">
+        <v>0.67</v>
+      </c>
+      <c r="T19">
+        <v>0.66</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="W19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20" t="s">
+        <v>77</v>
+      </c>
+      <c r="H20" t="s">
+        <v>78</v>
+      </c>
+      <c r="J20" t="s">
+        <v>859</v>
+      </c>
+      <c r="K20">
+        <v>3</v>
+      </c>
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>3</v>
+      </c>
+      <c r="O20">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="W20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
+      <c r="E21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" t="s">
+        <v>859</v>
+      </c>
+      <c r="K21">
+        <v>3</v>
+      </c>
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>3</v>
+      </c>
+      <c r="O21">
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <v>3</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="W21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+      <c r="E22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" t="s">
+        <v>855</v>
+      </c>
+      <c r="K22">
+        <v>3</v>
+      </c>
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>3</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22">
+        <v>3</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="W22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23">
+        <v>39</v>
+      </c>
+      <c r="H23" t="s">
+        <v>61</v>
+      </c>
+      <c r="J23" t="s">
+        <v>865</v>
+      </c>
+      <c r="K23">
+        <v>54</v>
+      </c>
+      <c r="L23" t="s">
+        <v>62</v>
+      </c>
+      <c r="M23">
+        <v>6</v>
+      </c>
+      <c r="N23">
+        <v>48</v>
+      </c>
+      <c r="O23">
+        <v>54</v>
+      </c>
+      <c r="P23">
+        <v>3</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>18</v>
+      </c>
+      <c r="S23">
+        <v>18</v>
+      </c>
+      <c r="T23">
+        <v>18</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23" t="s">
+        <v>83</v>
+      </c>
+      <c r="W23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="s">
+        <v>84</v>
+      </c>
+      <c r="J24" t="s">
+        <v>866</v>
+      </c>
+      <c r="K24">
+        <v>9</v>
+      </c>
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>9</v>
+      </c>
+      <c r="O24">
+        <v>9</v>
+      </c>
+      <c r="P24">
+        <v>3</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>3</v>
+      </c>
+      <c r="S24">
+        <v>3</v>
+      </c>
+      <c r="T24">
+        <v>3</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="W24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" t="s">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" t="s">
+        <v>867</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>2</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25">
+        <v>3</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>0.67</v>
+      </c>
+      <c r="S25">
+        <v>0.67</v>
+      </c>
+      <c r="T25">
+        <v>0.66</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="W25" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F26" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" t="s">
+        <v>869</v>
+      </c>
+      <c r="K26">
+        <v>6</v>
+      </c>
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>6</v>
+      </c>
+      <c r="O26">
+        <v>6</v>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>2</v>
+      </c>
+      <c r="S26">
+        <v>2</v>
+      </c>
+      <c r="T26">
+        <v>2</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="W26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" t="s">
+        <v>90</v>
+      </c>
+      <c r="J27" t="s">
+        <v>866</v>
+      </c>
+      <c r="K27">
+        <v>9</v>
+      </c>
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>9</v>
+      </c>
+      <c r="O27">
+        <v>9</v>
+      </c>
+      <c r="P27">
+        <v>3</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+      <c r="S27">
+        <v>3</v>
+      </c>
+      <c r="T27">
+        <v>3</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="W27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" t="s">
+        <v>82</v>
+      </c>
+      <c r="F28" t="s">
+        <v>91</v>
+      </c>
+      <c r="H28" t="s">
+        <v>92</v>
+      </c>
+      <c r="J28" t="s">
+        <v>869</v>
+      </c>
+      <c r="K28">
+        <v>6</v>
+      </c>
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>6</v>
+      </c>
+      <c r="O28">
+        <v>6</v>
+      </c>
+      <c r="P28">
+        <v>3</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>2</v>
+      </c>
+      <c r="S28">
+        <v>2</v>
+      </c>
+      <c r="T28">
+        <v>2</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="W28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" t="s">
+        <v>93</v>
+      </c>
+      <c r="H29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" t="s">
+        <v>870</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>3</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0.33</v>
+      </c>
+      <c r="S29">
+        <v>0.33</v>
+      </c>
+      <c r="T29">
+        <v>0.34</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="W29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30" t="s">
+        <v>82</v>
+      </c>
+      <c r="F30" t="s">
+        <v>95</v>
+      </c>
+      <c r="H30" t="s">
+        <v>96</v>
+      </c>
+      <c r="J30" t="s">
+        <v>871</v>
+      </c>
+      <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>4</v>
+      </c>
+      <c r="O30">
+        <v>4</v>
+      </c>
+      <c r="P30">
+        <v>3</v>
+      </c>
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>1.33</v>
+      </c>
+      <c r="S30">
+        <v>1.33</v>
+      </c>
+      <c r="T30">
+        <v>1.34</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="W30" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" t="s">
+        <v>97</v>
+      </c>
+      <c r="J31" t="s">
+        <v>872</v>
+      </c>
+      <c r="K31">
+        <v>3</v>
+      </c>
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>3</v>
+      </c>
+      <c r="O31">
+        <v>3</v>
+      </c>
+      <c r="P31">
+        <v>3</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="W31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" t="s">
+        <v>98</v>
+      </c>
+      <c r="J32" t="s">
+        <v>872</v>
+      </c>
+      <c r="K32">
+        <v>3</v>
+      </c>
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>3</v>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
+      <c r="P32">
+        <v>3</v>
+      </c>
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <v>1</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="W32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" t="s">
+        <v>872</v>
+      </c>
+      <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>3</v>
+      </c>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33">
+        <v>3</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="W33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34">
+        <v>650</v>
+      </c>
+      <c r="H34" t="s">
+        <v>102</v>
+      </c>
+      <c r="J34" t="s">
+        <v>861</v>
+      </c>
+      <c r="K34">
+        <v>33</v>
+      </c>
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>33</v>
+      </c>
+      <c r="O34">
+        <v>33</v>
+      </c>
+      <c r="P34">
+        <v>3</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>11</v>
+      </c>
+      <c r="S34">
+        <v>11</v>
+      </c>
+      <c r="T34">
+        <v>11</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34" t="s">
+        <v>101</v>
+      </c>
+      <c r="W34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" t="s">
+        <v>104</v>
+      </c>
+      <c r="J35" t="s">
+        <v>862</v>
+      </c>
+      <c r="K35">
+        <v>2.5</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>2.5</v>
+      </c>
+      <c r="O35">
+        <v>2.5</v>
+      </c>
+      <c r="P35">
+        <v>3</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0.83</v>
+      </c>
+      <c r="S35">
+        <v>0.83</v>
+      </c>
+      <c r="T35">
+        <v>0.84</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="W35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" t="s">
+        <v>105</v>
+      </c>
+      <c r="H36" t="s">
+        <v>106</v>
+      </c>
+      <c r="J36" t="s">
+        <v>863</v>
+      </c>
+      <c r="K36">
+        <v>3</v>
+      </c>
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>3</v>
+      </c>
+      <c r="O36">
+        <v>3</v>
+      </c>
+      <c r="P36">
+        <v>3</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36">
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <v>1</v>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="W36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>100</v>
+      </c>
+      <c r="F37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" t="s">
+        <v>863</v>
+      </c>
+      <c r="K37">
+        <v>3</v>
+      </c>
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>3</v>
+      </c>
+      <c r="O37">
+        <v>3</v>
+      </c>
+      <c r="P37">
+        <v>3</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="W37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38" t="s">
+        <v>100</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38">
+        <v>780</v>
+      </c>
+      <c r="H38" t="s">
+        <v>109</v>
+      </c>
+      <c r="J38" t="s">
+        <v>868</v>
+      </c>
+      <c r="K38">
+        <v>30</v>
+      </c>
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>30</v>
+      </c>
+      <c r="O38">
+        <v>30</v>
+      </c>
+      <c r="P38">
+        <v>3</v>
+      </c>
+      <c r="Q38">
+        <v>0</v>
+      </c>
+      <c r="R38">
+        <v>10</v>
+      </c>
+      <c r="S38">
+        <v>10</v>
+      </c>
+      <c r="T38">
+        <v>10</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38" t="s">
+        <v>108</v>
+      </c>
+      <c r="W38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39">
+        <v>2</v>
+      </c>
+      <c r="E39" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" t="s">
+        <v>110</v>
+      </c>
+      <c r="J39" t="s">
+        <v>873</v>
+      </c>
+      <c r="K39">
+        <v>3</v>
+      </c>
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>3</v>
+      </c>
+      <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="P39">
+        <v>3</v>
+      </c>
+      <c r="Q39">
+        <v>0</v>
+      </c>
+      <c r="R39">
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="W39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" t="s">
+        <v>111</v>
+      </c>
+      <c r="J40" t="s">
+        <v>874</v>
+      </c>
+      <c r="K40">
+        <v>1.5</v>
+      </c>
+      <c r="L40" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>1.5</v>
+      </c>
+      <c r="O40">
+        <v>1.5</v>
+      </c>
+      <c r="P40">
+        <v>3</v>
+      </c>
+      <c r="Q40">
+        <v>0</v>
+      </c>
+      <c r="R40">
+        <v>0.5</v>
+      </c>
+      <c r="S40">
+        <v>0.5</v>
+      </c>
+      <c r="T40">
+        <v>0.5</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="W40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>81</v>
+      </c>
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>110</v>
+      </c>
+      <c r="J41" t="s">
+        <v>873</v>
+      </c>
+      <c r="K41">
+        <v>3</v>
+      </c>
+      <c r="L41" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>3</v>
+      </c>
+      <c r="O41">
+        <v>3</v>
+      </c>
+      <c r="P41">
+        <v>3</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="W41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" t="s">
+        <v>28</v>
+      </c>
+      <c r="C42" t="s">
+        <v>81</v>
+      </c>
+      <c r="D42">
+        <v>5</v>
+      </c>
+      <c r="E42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" t="s">
+        <v>113</v>
+      </c>
+      <c r="J42" t="s">
+        <v>875</v>
+      </c>
+      <c r="K42">
+        <v>3</v>
+      </c>
+      <c r="L42" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>3</v>
+      </c>
+      <c r="O42">
+        <v>3</v>
+      </c>
+      <c r="P42">
+        <v>3</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="W42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" t="s">
+        <v>116</v>
+      </c>
+      <c r="J43" t="s">
+        <v>216</v>
+      </c>
+      <c r="K43">
+        <v>6</v>
+      </c>
+      <c r="L43" t="s">
+        <v>115</v>
+      </c>
+      <c r="M43">
+        <v>6</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
+        <v>6</v>
+      </c>
+      <c r="P43">
+        <v>3</v>
+      </c>
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43">
+        <v>2</v>
+      </c>
+      <c r="T43">
+        <v>2</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
+      </c>
+      <c r="C44" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
+      <c r="E44" t="s">
+        <v>115</v>
+      </c>
+      <c r="F44" t="s">
+        <v>117</v>
+      </c>
+      <c r="J44" t="s">
+        <v>549</v>
+      </c>
+      <c r="K44">
+        <v>4</v>
+      </c>
+      <c r="L44" t="s">
+        <v>115</v>
+      </c>
+      <c r="M44">
+        <v>4</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>4</v>
+      </c>
+      <c r="P44">
+        <v>3</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>1.33</v>
+      </c>
+      <c r="S44">
+        <v>1.33</v>
+      </c>
+      <c r="T44">
+        <v>1.34</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45" t="s">
+        <v>115</v>
+      </c>
+      <c r="F45" t="s">
+        <v>118</v>
+      </c>
+      <c r="J45" t="s">
+        <v>241</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" t="s">
+        <v>115</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" t="s">
+        <v>28</v>
+      </c>
+      <c r="C46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46">
+        <v>4</v>
+      </c>
+      <c r="E46" t="s">
+        <v>115</v>
+      </c>
+      <c r="F46" t="s">
+        <v>119</v>
+      </c>
+      <c r="J46" t="s">
+        <v>232</v>
+      </c>
+      <c r="K46">
+        <v>3</v>
+      </c>
+      <c r="L46" t="s">
+        <v>115</v>
+      </c>
+      <c r="M46">
+        <v>3</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>3</v>
+      </c>
+      <c r="P46">
+        <v>3</v>
+      </c>
+      <c r="Q46">
+        <v>0</v>
+      </c>
+      <c r="R46">
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <v>1</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" t="s">
+        <v>28</v>
+      </c>
+      <c r="C47" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47">
+        <v>5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" t="s">
+        <v>120</v>
+      </c>
+      <c r="J47" t="s">
+        <v>876</v>
+      </c>
+      <c r="K47">
+        <v>4</v>
+      </c>
+      <c r="L47" t="s">
+        <v>115</v>
+      </c>
+      <c r="M47">
+        <v>4</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>4</v>
+      </c>
+      <c r="P47">
+        <v>3</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>1.33</v>
+      </c>
+      <c r="S47">
+        <v>1.33</v>
+      </c>
+      <c r="T47">
+        <v>1.34</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48">
+        <v>6</v>
+      </c>
+      <c r="E48" t="s">
+        <v>115</v>
+      </c>
+      <c r="F48" t="s">
+        <v>121</v>
+      </c>
+      <c r="J48" t="s">
+        <v>312</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48" t="s">
+        <v>115</v>
+      </c>
+      <c r="M48">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>2</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <v>2</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>115</v>
+      </c>
+      <c r="F49" t="s">
+        <v>122</v>
+      </c>
+      <c r="J49" t="s">
+        <v>232</v>
+      </c>
+      <c r="K49">
+        <v>3</v>
+      </c>
+      <c r="L49" t="s">
+        <v>115</v>
+      </c>
+      <c r="M49">
+        <v>3</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>3</v>
+      </c>
+      <c r="P49">
+        <v>3</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50">
+        <v>8</v>
+      </c>
+      <c r="E50" t="s">
+        <v>115</v>
+      </c>
+      <c r="F50" t="s">
+        <v>123</v>
+      </c>
+      <c r="J50" t="s">
+        <v>312</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50" t="s">
+        <v>115</v>
+      </c>
+      <c r="M50">
+        <v>2</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50">
+        <v>2</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <v>2</v>
+      </c>
+      <c r="R50">
+        <v>0</v>
+      </c>
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51">
+        <v>9</v>
+      </c>
+      <c r="E51" t="s">
+        <v>115</v>
+      </c>
+      <c r="F51" t="s">
+        <v>124</v>
+      </c>
+      <c r="J51" t="s">
+        <v>241</v>
+      </c>
+      <c r="K51">
+        <v>1</v>
+      </c>
+      <c r="L51" t="s">
+        <v>115</v>
+      </c>
+      <c r="M51">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>0</v>
+      </c>
+      <c r="O51">
+        <v>1</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <v>1</v>
+      </c>
+      <c r="R51">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>115</v>
+      </c>
+      <c r="F52" t="s">
+        <v>125</v>
+      </c>
+      <c r="J52" t="s">
+        <v>312</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52" t="s">
+        <v>115</v>
+      </c>
+      <c r="M52">
+        <v>2</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>2</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <v>2</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" t="s">
+        <v>127</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>128</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53" t="s">
+        <v>130</v>
+      </c>
+      <c r="J53" t="s">
+        <v>131</v>
+      </c>
+      <c r="K53">
+        <v>12</v>
+      </c>
+      <c r="L53" t="s">
+        <v>62</v>
+      </c>
+      <c r="M53">
+        <v>10</v>
+      </c>
+      <c r="N53">
+        <v>2</v>
+      </c>
+      <c r="O53">
+        <v>12</v>
+      </c>
+      <c r="P53">
+        <v>3</v>
+      </c>
+      <c r="Q53">
+        <v>0</v>
+      </c>
+      <c r="R53">
+        <v>4</v>
+      </c>
+      <c r="S53">
+        <v>4</v>
+      </c>
+      <c r="T53">
+        <v>4</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53" t="s">
+        <v>129</v>
+      </c>
+      <c r="W53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" t="s">
+        <v>126</v>
+      </c>
+      <c r="C54" t="s">
+        <v>127</v>
+      </c>
+      <c r="D54">
+        <v>2</v>
+      </c>
+      <c r="E54" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="G54">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>134</v>
+      </c>
+      <c r="J54" t="s">
+        <v>882</v>
+      </c>
+      <c r="K54">
+        <v>3</v>
+      </c>
+      <c r="L54" t="s">
+        <v>25</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>3</v>
+      </c>
+      <c r="O54">
+        <v>3</v>
+      </c>
+      <c r="P54">
+        <v>3</v>
+      </c>
+      <c r="Q54">
+        <v>0</v>
+      </c>
+      <c r="R54">
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54" t="s">
+        <v>133</v>
+      </c>
+      <c r="W54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>135</v>
+      </c>
+      <c r="F55" t="s">
+        <v>31</v>
+      </c>
+      <c r="G55">
+        <v>6</v>
+      </c>
+      <c r="H55" t="s">
+        <v>137</v>
+      </c>
+      <c r="J55" t="s">
+        <v>138</v>
+      </c>
+      <c r="K55">
+        <v>3</v>
+      </c>
+      <c r="L55" t="s">
+        <v>25</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55">
+        <v>3</v>
+      </c>
+      <c r="P55">
+        <v>3</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55" t="s">
+        <v>136</v>
+      </c>
+      <c r="W55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+      <c r="E56" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="G56">
+        <v>7</v>
+      </c>
+      <c r="H56" t="s">
+        <v>140</v>
+      </c>
+      <c r="J56" t="s">
+        <v>141</v>
+      </c>
+      <c r="K56">
+        <v>6</v>
+      </c>
+      <c r="L56" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>6</v>
+      </c>
+      <c r="O56">
+        <v>6</v>
+      </c>
+      <c r="P56">
+        <v>3</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>2</v>
+      </c>
+      <c r="S56">
+        <v>2</v>
+      </c>
+      <c r="T56">
+        <v>2</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56" t="s">
+        <v>139</v>
+      </c>
+      <c r="W56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" t="s">
+        <v>142</v>
+      </c>
+      <c r="D57">
+        <v>5</v>
+      </c>
+      <c r="E57" t="s">
+        <v>143</v>
+      </c>
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" t="s">
+        <v>140</v>
+      </c>
+      <c r="J57" t="s">
+        <v>312</v>
+      </c>
+      <c r="K57">
+        <v>2</v>
+      </c>
+      <c r="L57" t="s">
+        <v>25</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
+      <c r="P57">
+        <v>3</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0.67</v>
+      </c>
+      <c r="S57">
+        <v>0.67</v>
+      </c>
+      <c r="T57">
+        <v>0.66</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="W57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" t="s">
+        <v>126</v>
+      </c>
+      <c r="C58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="E58" t="s">
+        <v>144</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" t="s">
+        <v>145</v>
+      </c>
+      <c r="J58" t="s">
+        <v>232</v>
+      </c>
+      <c r="K58">
+        <v>3</v>
+      </c>
+      <c r="L58" t="s">
+        <v>25</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>3</v>
+      </c>
+      <c r="O58">
+        <v>3</v>
+      </c>
+      <c r="P58">
+        <v>3</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="W58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G59">
+        <v>2952</v>
+      </c>
+      <c r="H59" t="s">
+        <v>148</v>
+      </c>
+      <c r="J59" t="s">
+        <v>883</v>
+      </c>
+      <c r="K59">
+        <v>6</v>
+      </c>
+      <c r="L59" t="s">
+        <v>25</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>6</v>
+      </c>
+      <c r="O59">
+        <v>6</v>
+      </c>
+      <c r="P59">
+        <v>3</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>2</v>
+      </c>
+      <c r="S59">
+        <v>2</v>
+      </c>
+      <c r="T59">
+        <v>2</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59" t="s">
+        <v>147</v>
+      </c>
+      <c r="W59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60" t="s">
+        <v>126</v>
+      </c>
+      <c r="D60">
+        <v>8</v>
+      </c>
+      <c r="E60" t="s">
+        <v>146</v>
+      </c>
+      <c r="F60" t="s">
+        <v>50</v>
+      </c>
+      <c r="H60" t="s">
+        <v>149</v>
+      </c>
+      <c r="J60" t="s">
+        <v>883</v>
+      </c>
+      <c r="K60">
+        <v>6</v>
+      </c>
+      <c r="L60" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>6</v>
+      </c>
+      <c r="O60">
+        <v>6</v>
+      </c>
+      <c r="P60">
+        <v>3</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>2</v>
+      </c>
+      <c r="S60">
+        <v>2</v>
+      </c>
+      <c r="T60">
+        <v>2</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="W60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" t="s">
+        <v>879</v>
+      </c>
+      <c r="D61">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>879</v>
+      </c>
+      <c r="F61" t="s">
+        <v>879</v>
+      </c>
+      <c r="K61">
+        <v>3</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>3</v>
+      </c>
+      <c r="O61">
+        <v>3</v>
+      </c>
+      <c r="P61">
+        <v>3</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" t="s">
+        <v>880</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
+        <v>880</v>
+      </c>
+      <c r="F62" t="s">
+        <v>880</v>
+      </c>
+      <c r="K62">
+        <v>14</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>14</v>
+      </c>
+      <c r="O62">
+        <v>14</v>
+      </c>
+      <c r="P62">
+        <v>3</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>5</v>
+      </c>
+      <c r="S62">
+        <v>5</v>
+      </c>
+      <c r="T62">
+        <v>4</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" t="s">
+        <v>881</v>
+      </c>
+      <c r="D63">
+        <v>11</v>
+      </c>
+      <c r="E63" t="s">
+        <v>881</v>
+      </c>
+      <c r="F63" t="s">
+        <v>881</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>3</v>
+      </c>
+      <c r="O63">
+        <v>3</v>
+      </c>
+      <c r="P63">
+        <v>3</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <v>1</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" t="s">
+        <v>28</v>
+      </c>
+      <c r="C64" t="s">
+        <v>150</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64" t="s">
+        <v>884</v>
+      </c>
+      <c r="F64" t="s">
+        <v>151</v>
+      </c>
+      <c r="H64" t="s">
+        <v>885</v>
+      </c>
+      <c r="J64" t="s">
+        <v>312</v>
+      </c>
+      <c r="K64">
+        <v>2</v>
+      </c>
+      <c r="L64" t="s">
+        <v>25</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>2</v>
+      </c>
+      <c r="O64">
+        <v>2</v>
+      </c>
+      <c r="P64">
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <v>2</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64" t="s">
+        <v>26</v>
+      </c>
+      <c r="W64" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>30</v>
+      </c>
+      <c r="F65" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65">
+        <v>8</v>
+      </c>
+      <c r="H65" t="s">
+        <v>154</v>
+      </c>
+      <c r="J65" t="s">
+        <v>886</v>
+      </c>
+      <c r="K65">
+        <v>12</v>
+      </c>
+      <c r="L65" t="s">
+        <v>25</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>12</v>
+      </c>
+      <c r="O65">
+        <v>12</v>
+      </c>
+      <c r="P65">
+        <v>3</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>4</v>
+      </c>
+      <c r="S65">
+        <v>4</v>
+      </c>
+      <c r="T65">
+        <v>4</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65" t="s">
+        <v>153</v>
+      </c>
+      <c r="W65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C66" t="s">
+        <v>150</v>
+      </c>
+      <c r="D66">
+        <v>3</v>
+      </c>
+      <c r="E66" t="s">
+        <v>132</v>
+      </c>
+      <c r="F66" t="s">
+        <v>31</v>
+      </c>
+      <c r="G66">
+        <v>56</v>
+      </c>
+      <c r="H66" t="s">
+        <v>155</v>
+      </c>
+      <c r="J66" t="s">
+        <v>156</v>
+      </c>
+      <c r="K66">
+        <v>6</v>
+      </c>
+      <c r="L66" t="s">
+        <v>25</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>6</v>
+      </c>
+      <c r="O66">
+        <v>6</v>
+      </c>
+      <c r="P66">
+        <v>3</v>
+      </c>
+      <c r="Q66">
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <v>2</v>
+      </c>
+      <c r="S66">
+        <v>2</v>
+      </c>
+      <c r="T66">
+        <v>2</v>
+      </c>
+      <c r="U66">
+        <v>0</v>
+      </c>
+      <c r="W66" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" t="s">
+        <v>150</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+      <c r="E67" t="s">
+        <v>157</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+      <c r="G67">
+        <v>17</v>
+      </c>
+      <c r="H67" t="s">
+        <v>158</v>
+      </c>
+      <c r="J67" t="s">
+        <v>159</v>
+      </c>
+      <c r="K67">
+        <v>15</v>
+      </c>
+      <c r="L67" t="s">
+        <v>25</v>
+      </c>
+      <c r="M67">
+        <v>0</v>
+      </c>
+      <c r="N67">
+        <v>15</v>
+      </c>
+      <c r="O67">
+        <v>15</v>
+      </c>
+      <c r="P67">
+        <v>3</v>
+      </c>
+      <c r="Q67">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>5</v>
+      </c>
+      <c r="S67">
+        <v>5</v>
+      </c>
+      <c r="T67">
+        <v>5</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="W67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" t="s">
+        <v>28</v>
+      </c>
+      <c r="C68" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68" t="s">
+        <v>160</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="G68">
+        <v>20</v>
+      </c>
+      <c r="H68" t="s">
+        <v>161</v>
+      </c>
+      <c r="J68" t="s">
+        <v>887</v>
+      </c>
+      <c r="K68">
+        <v>9</v>
+      </c>
+      <c r="L68" t="s">
+        <v>25</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>9</v>
+      </c>
+      <c r="O68">
+        <v>9</v>
+      </c>
+      <c r="P68">
+        <v>3</v>
+      </c>
+      <c r="Q68">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>3</v>
+      </c>
+      <c r="S68">
+        <v>3</v>
+      </c>
+      <c r="T68">
+        <v>3</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68" t="s">
+        <v>162</v>
+      </c>
+      <c r="W68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69">
+        <v>6</v>
+      </c>
+      <c r="E69" t="s">
+        <v>163</v>
+      </c>
+      <c r="F69" t="s">
+        <v>31</v>
+      </c>
+      <c r="G69">
+        <v>20</v>
+      </c>
+      <c r="H69" t="s">
+        <v>161</v>
+      </c>
+      <c r="J69" t="s">
+        <v>887</v>
+      </c>
+      <c r="K69">
+        <v>9</v>
+      </c>
+      <c r="L69" t="s">
+        <v>25</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>9</v>
+      </c>
+      <c r="O69">
+        <v>9</v>
+      </c>
+      <c r="P69">
+        <v>3</v>
+      </c>
+      <c r="Q69">
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <v>3</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <v>3</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69" t="s">
+        <v>162</v>
+      </c>
+      <c r="W69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" t="s">
+        <v>28</v>
+      </c>
+      <c r="C70" t="s">
+        <v>150</v>
+      </c>
+      <c r="D70">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
+        <v>164</v>
+      </c>
+      <c r="F70" t="s">
+        <v>31</v>
+      </c>
+      <c r="G70">
+        <v>20</v>
+      </c>
+      <c r="H70" t="s">
+        <v>161</v>
+      </c>
+      <c r="J70" t="s">
+        <v>888</v>
+      </c>
+      <c r="K70">
+        <v>15</v>
+      </c>
+      <c r="L70" t="s">
+        <v>25</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>15</v>
+      </c>
+      <c r="O70">
+        <v>15</v>
+      </c>
+      <c r="P70">
+        <v>3</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>5</v>
+      </c>
+      <c r="S70">
+        <v>5</v>
+      </c>
+      <c r="T70">
+        <v>5</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70" t="s">
+        <v>165</v>
+      </c>
+      <c r="W70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" t="s">
+        <v>28</v>
+      </c>
+      <c r="C71" t="s">
+        <v>150</v>
+      </c>
+      <c r="D71">
+        <v>8</v>
+      </c>
+      <c r="E71" t="s">
+        <v>164</v>
+      </c>
+      <c r="F71" t="s">
+        <v>55</v>
+      </c>
+      <c r="H71" t="s">
+        <v>301</v>
+      </c>
+      <c r="J71" t="s">
+        <v>232</v>
+      </c>
+      <c r="K71">
+        <v>3</v>
+      </c>
+      <c r="L71" t="s">
+        <v>25</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>3</v>
+      </c>
+      <c r="O71">
+        <v>3</v>
+      </c>
+      <c r="P71">
+        <v>3</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>1</v>
+      </c>
+      <c r="S71">
+        <v>1</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71" t="s">
+        <v>56</v>
+      </c>
+      <c r="W71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>150</v>
+      </c>
+      <c r="D72">
+        <v>9</v>
+      </c>
+      <c r="E72" t="s">
+        <v>164</v>
+      </c>
+      <c r="F72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>889</v>
+      </c>
+      <c r="J72" t="s">
+        <v>232</v>
+      </c>
+      <c r="K72">
+        <v>3</v>
+      </c>
+      <c r="L72" t="s">
+        <v>25</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>3</v>
+      </c>
+      <c r="O72">
+        <v>3</v>
+      </c>
+      <c r="P72">
+        <v>3</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>1</v>
+      </c>
+      <c r="S72">
+        <v>1</v>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72" t="s">
+        <v>56</v>
+      </c>
+      <c r="W72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" t="s">
+        <v>166</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" t="s">
+        <v>31</v>
+      </c>
+      <c r="G73" s="1">
+        <v>104</v>
+      </c>
+      <c r="H73" t="s">
+        <v>168</v>
+      </c>
+      <c r="J73" t="s">
+        <v>169</v>
+      </c>
+      <c r="K73">
+        <v>156</v>
+      </c>
+      <c r="L73" t="s">
+        <v>62</v>
+      </c>
+      <c r="M73">
+        <v>54</v>
+      </c>
+      <c r="N73">
+        <v>102</v>
+      </c>
+      <c r="O73">
+        <v>156</v>
+      </c>
+      <c r="P73">
+        <v>3</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>52</v>
+      </c>
+      <c r="S73">
+        <v>52</v>
+      </c>
+      <c r="T73">
+        <v>52</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73" t="s">
+        <v>890</v>
+      </c>
+      <c r="W73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
+      <c r="E74" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" t="s">
+        <v>55</v>
+      </c>
+      <c r="H74" t="s">
+        <v>170</v>
+      </c>
+      <c r="J74" t="s">
+        <v>891</v>
+      </c>
+      <c r="K74">
+        <v>6</v>
+      </c>
+      <c r="L74" t="s">
+        <v>25</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>6</v>
+      </c>
+      <c r="O74">
+        <v>6</v>
+      </c>
+      <c r="P74">
+        <v>3</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>2</v>
+      </c>
+      <c r="S74">
+        <v>2</v>
+      </c>
+      <c r="T74">
+        <v>2</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="W74" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" t="s">
+        <v>63</v>
+      </c>
+      <c r="H75" t="s">
+        <v>171</v>
+      </c>
+      <c r="J75" t="s">
+        <v>892</v>
+      </c>
+      <c r="K75">
+        <v>15</v>
+      </c>
+      <c r="L75" t="s">
+        <v>25</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>15</v>
+      </c>
+      <c r="O75">
+        <v>15</v>
+      </c>
+      <c r="P75">
+        <v>3</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>5</v>
+      </c>
+      <c r="S75">
+        <v>5</v>
+      </c>
+      <c r="T75">
+        <v>5</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="W75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" t="s">
+        <v>28</v>
+      </c>
+      <c r="C76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76">
+        <v>4</v>
+      </c>
+      <c r="E76" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" t="s">
+        <v>172</v>
+      </c>
+      <c r="H76" t="s">
+        <v>173</v>
+      </c>
+      <c r="J76" t="s">
+        <v>893</v>
+      </c>
+      <c r="K76">
+        <v>12</v>
+      </c>
+      <c r="L76" t="s">
+        <v>25</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>12</v>
+      </c>
+      <c r="O76">
+        <v>12</v>
+      </c>
+      <c r="P76">
+        <v>3</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>4</v>
+      </c>
+      <c r="S76">
+        <v>4</v>
+      </c>
+      <c r="T76">
+        <v>4</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="W76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" t="s">
+        <v>28</v>
+      </c>
+      <c r="C77" t="s">
+        <v>166</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" t="s">
+        <v>174</v>
+      </c>
+      <c r="H77" t="s">
+        <v>175</v>
+      </c>
+      <c r="J77" t="s">
+        <v>894</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
+      </c>
+      <c r="L77" t="s">
+        <v>25</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>3</v>
+      </c>
+      <c r="O77">
+        <v>3</v>
+      </c>
+      <c r="P77">
+        <v>3</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="S77">
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="W77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78">
+        <v>6</v>
+      </c>
+      <c r="E78" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" t="s">
+        <v>176</v>
+      </c>
+      <c r="H78" t="s">
+        <v>177</v>
+      </c>
+      <c r="J78" t="s">
+        <v>893</v>
+      </c>
+      <c r="K78">
+        <v>12</v>
+      </c>
+      <c r="L78" t="s">
+        <v>25</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>12</v>
+      </c>
+      <c r="O78">
+        <v>12</v>
+      </c>
+      <c r="P78">
+        <v>3</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>4</v>
+      </c>
+      <c r="S78">
+        <v>4</v>
+      </c>
+      <c r="T78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="W78" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79">
+        <v>7</v>
+      </c>
+      <c r="E79" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>179</v>
+      </c>
+      <c r="J79" t="s">
+        <v>893</v>
+      </c>
+      <c r="K79">
+        <v>12</v>
+      </c>
+      <c r="L79" t="s">
+        <v>25</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>12</v>
+      </c>
+      <c r="O79">
+        <v>12</v>
+      </c>
+      <c r="P79">
+        <v>3</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>4</v>
+      </c>
+      <c r="S79">
+        <v>4</v>
+      </c>
+      <c r="T79">
+        <v>4</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="W79" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" t="s">
+        <v>28</v>
+      </c>
+      <c r="C80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" t="s">
+        <v>180</v>
+      </c>
+      <c r="H80" t="s">
+        <v>181</v>
+      </c>
+      <c r="J80" t="s">
+        <v>895</v>
+      </c>
+      <c r="K80">
+        <v>9</v>
+      </c>
+      <c r="L80" t="s">
+        <v>25</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>9</v>
+      </c>
+      <c r="O80">
+        <v>9</v>
+      </c>
+      <c r="P80">
+        <v>3</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>3</v>
+      </c>
+      <c r="S80">
+        <v>3</v>
+      </c>
+      <c r="T80">
+        <v>3</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="W80" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" t="s">
+        <v>182</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81" t="s">
+        <v>183</v>
+      </c>
+      <c r="F81" t="s">
+        <v>31</v>
+      </c>
+      <c r="G81" s="1">
+        <v>2772</v>
+      </c>
+      <c r="H81" t="s">
+        <v>184</v>
+      </c>
+      <c r="J81" t="s">
+        <v>897</v>
+      </c>
+      <c r="K81">
+        <v>36</v>
+      </c>
+      <c r="L81" t="s">
+        <v>25</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>36</v>
+      </c>
+      <c r="O81">
+        <v>36</v>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>12</v>
+      </c>
+      <c r="S81">
+        <v>12</v>
+      </c>
+      <c r="T81">
+        <v>12</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81" t="s">
+        <v>896</v>
+      </c>
+      <c r="W81" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" t="s">
+        <v>28</v>
+      </c>
+      <c r="C82" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82">
+        <v>2</v>
+      </c>
+      <c r="E82" t="s">
+        <v>183</v>
+      </c>
+      <c r="F82" t="s">
+        <v>55</v>
+      </c>
+      <c r="H82" t="s">
+        <v>185</v>
+      </c>
+      <c r="J82" t="s">
+        <v>898</v>
+      </c>
+      <c r="K82">
+        <v>3</v>
+      </c>
+      <c r="L82" t="s">
+        <v>25</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>3</v>
+      </c>
+      <c r="O82">
+        <v>3</v>
+      </c>
+      <c r="P82">
+        <v>3</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>1</v>
+      </c>
+      <c r="S82">
+        <v>1</v>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="W82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" t="s">
+        <v>28</v>
+      </c>
+      <c r="C83" t="s">
+        <v>182</v>
+      </c>
+      <c r="D83">
+        <v>3</v>
+      </c>
+      <c r="E83" t="s">
+        <v>183</v>
+      </c>
+      <c r="F83" t="s">
+        <v>186</v>
+      </c>
+      <c r="H83" t="s">
+        <v>187</v>
+      </c>
+      <c r="J83" t="s">
+        <v>898</v>
+      </c>
+      <c r="K83">
+        <v>3</v>
+      </c>
+      <c r="L83" t="s">
+        <v>25</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>3</v>
+      </c>
+      <c r="O83">
+        <v>3</v>
+      </c>
+      <c r="P83">
+        <v>3</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>1</v>
+      </c>
+      <c r="S83">
+        <v>1</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="W83" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" t="s">
+        <v>28</v>
+      </c>
+      <c r="C84" t="s">
+        <v>182</v>
+      </c>
+      <c r="D84">
+        <v>4</v>
+      </c>
+      <c r="E84" t="s">
+        <v>183</v>
+      </c>
+      <c r="F84" t="s">
+        <v>188</v>
+      </c>
+      <c r="H84" t="s">
+        <v>189</v>
+      </c>
+      <c r="J84" t="s">
+        <v>899</v>
+      </c>
+      <c r="K84">
+        <v>6</v>
+      </c>
+      <c r="L84" t="s">
+        <v>25</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>6</v>
+      </c>
+      <c r="O84">
+        <v>6</v>
+      </c>
+      <c r="P84">
+        <v>3</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>2</v>
+      </c>
+      <c r="S84">
+        <v>2</v>
+      </c>
+      <c r="T84">
+        <v>2</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="W84" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>190</v>
+      </c>
+      <c r="D85">
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>191</v>
+      </c>
+      <c r="J85" t="s">
+        <v>24</v>
+      </c>
+      <c r="K85">
+        <v>4</v>
+      </c>
+      <c r="L85" t="s">
+        <v>115</v>
+      </c>
+      <c r="M85">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
+      <c r="P85">
+        <v>3</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>1.33</v>
+      </c>
+      <c r="S85">
+        <v>1.33</v>
+      </c>
+      <c r="T85">
+        <v>1.34</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85" t="s">
+        <v>56</v>
+      </c>
+      <c r="W85" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" t="s">
+        <v>190</v>
+      </c>
+      <c r="D86">
+        <v>2</v>
+      </c>
+      <c r="F86" t="s">
+        <v>192</v>
+      </c>
+      <c r="J86" t="s">
+        <v>24</v>
+      </c>
+      <c r="K86">
+        <v>3</v>
+      </c>
+      <c r="L86" t="s">
+        <v>115</v>
+      </c>
+      <c r="M86">
+        <v>3</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>3</v>
+      </c>
+      <c r="P86">
+        <v>3</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>1</v>
+      </c>
+      <c r="S86">
+        <v>1</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86" t="s">
+        <v>56</v>
+      </c>
+      <c r="W86" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" t="s">
+        <v>190</v>
+      </c>
+      <c r="D87">
+        <v>3</v>
+      </c>
+      <c r="F87" t="s">
+        <v>193</v>
+      </c>
+      <c r="J87" t="s">
+        <v>24</v>
+      </c>
+      <c r="K87">
+        <v>11</v>
+      </c>
+      <c r="L87" t="s">
+        <v>115</v>
+      </c>
+      <c r="M87">
+        <v>11</v>
+      </c>
+      <c r="N87">
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <v>11</v>
+      </c>
+      <c r="P87">
+        <v>3</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>3.67</v>
+      </c>
+      <c r="S87">
+        <v>3.67</v>
+      </c>
+      <c r="T87">
+        <v>3.66</v>
+      </c>
+      <c r="U87">
+        <v>0</v>
+      </c>
+      <c r="V87" t="s">
+        <v>56</v>
+      </c>
+      <c r="W87" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" t="s">
+        <v>28</v>
+      </c>
+      <c r="C88" t="s">
+        <v>190</v>
+      </c>
+      <c r="D88">
+        <v>4</v>
+      </c>
+      <c r="F88" t="s">
+        <v>194</v>
+      </c>
+      <c r="J88" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88">
+        <v>4</v>
+      </c>
+      <c r="L88" t="s">
+        <v>115</v>
+      </c>
+      <c r="M88">
+        <v>4</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>4</v>
+      </c>
+      <c r="P88">
+        <v>3</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>1.33</v>
+      </c>
+      <c r="S88">
+        <v>1.33</v>
+      </c>
+      <c r="T88">
+        <v>1.34</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88" t="s">
+        <v>56</v>
+      </c>
+      <c r="W88" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89" t="s">
+        <v>190</v>
+      </c>
+      <c r="D89">
+        <v>5</v>
+      </c>
+      <c r="F89" t="s">
+        <v>195</v>
+      </c>
+      <c r="J89" t="s">
+        <v>24</v>
+      </c>
+      <c r="K89">
+        <v>2</v>
+      </c>
+      <c r="L89" t="s">
+        <v>115</v>
+      </c>
+      <c r="M89">
+        <v>2</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>2</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>2</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>0</v>
+      </c>
+      <c r="U89">
+        <v>0</v>
+      </c>
+      <c r="V89" t="s">
+        <v>26</v>
+      </c>
+      <c r="W89" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" t="s">
+        <v>877</v>
+      </c>
+      <c r="D90">
+        <v>1</v>
+      </c>
+      <c r="E90" t="s">
+        <v>877</v>
+      </c>
+      <c r="F90" t="s">
+        <v>877</v>
+      </c>
+      <c r="K90">
+        <v>82</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>82</v>
+      </c>
+      <c r="O90">
+        <v>82</v>
+      </c>
+      <c r="P90">
+        <v>3</v>
+      </c>
+      <c r="Q90">
+        <v>82</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>0</v>
+      </c>
+      <c r="U90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" t="s">
+        <v>28</v>
+      </c>
+      <c r="C91" t="s">
+        <v>900</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91" t="s">
+        <v>900</v>
+      </c>
+      <c r="F91" t="s">
+        <v>900</v>
+      </c>
+      <c r="K91">
+        <v>32</v>
+      </c>
+      <c r="M91">
+        <v>20</v>
+      </c>
+      <c r="N91">
+        <v>12</v>
+      </c>
+      <c r="O91">
+        <v>32</v>
+      </c>
+      <c r="P91">
+        <v>3</v>
+      </c>
+      <c r="Q91">
+        <v>32</v>
+      </c>
+      <c r="R91">
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <v>0</v>
+      </c>
+      <c r="T91">
+        <v>0</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" t="s">
+        <v>28</v>
+      </c>
+      <c r="C92" t="s">
+        <v>878</v>
+      </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
+      <c r="E92" t="s">
+        <v>878</v>
+      </c>
+      <c r="F92" t="s">
+        <v>878</v>
+      </c>
+      <c r="K92">
+        <v>9</v>
+      </c>
+      <c r="M92">
+        <v>9</v>
+      </c>
+      <c r="N92">
+        <v>9</v>
+      </c>
+      <c r="O92">
+        <v>9</v>
+      </c>
+      <c r="P92">
+        <v>3</v>
+      </c>
+      <c r="Q92">
+        <v>9</v>
+      </c>
+      <c r="R92">
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <v>0</v>
+      </c>
+      <c r="U92">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/input/Anjar_manning.xlsx
+++ b/input/Anjar_manning.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/Manning_FInal_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="365" documentId="13_ncr:1_{45658262-96CC-4946-9B46-BB1FC1723B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8435356F-C94B-4189-B563-851A0E7B345E}"/>
+  <xr:revisionPtr revIDLastSave="423" documentId="13_ncr:1_{45658262-96CC-4946-9B46-BB1FC1723B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCB5F83F-1F77-46FC-AF42-456D56344D15}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
   </bookViews>
   <sheets>
     <sheet name="Anjar" sheetId="1" r:id="rId1"/>
     <sheet name="Spinning" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anjar!$A$1:$W$450</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anjar!$A$1:$X$450</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5000" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5002" uniqueCount="902">
   <si>
     <t>Location</t>
   </si>
@@ -2597,9 +2597,6 @@
     <t>1 DEO / Shift</t>
   </si>
   <si>
-    <t xml:space="preserve">Manpower Count / Machine </t>
-  </si>
-  <si>
     <t>2 Operator</t>
   </si>
   <si>
@@ -2745,16 +2742,29 @@
   </si>
   <si>
     <t>Engg &amp; Utility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine Count / Manpower </t>
+  </si>
+  <si>
+    <t>Manpower_Base_Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2780,11 +2790,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2800,6 +2811,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3100,7 +3115,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80233CC7-9F29-4521-9F43-292ADE3B342B}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W450"/>
+  <dimension ref="A1:X450"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="11.1015625" bestFit="1" customWidth="1"/>
@@ -3110,8 +3125,8 @@
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="112.3125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="65.20703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="32.89453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.89453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="65.20703125" customWidth="1"/>
+    <col min="9" max="9" width="32.89453125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22.41796875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="25.68359375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
@@ -3125,9 +3140,10 @@
     <col min="21" max="21" width="11.1015625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="92" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="12.89453125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.5234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3149,11 +3165,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>851</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -3197,8 +3213,11 @@
       <c r="W1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="X1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3217,8 +3236,8 @@
       <c r="F2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
-        <v>852</v>
+      <c r="I2" t="s">
+        <v>851</v>
       </c>
       <c r="J2" t="s">
         <v>312</v>
@@ -3260,7 +3279,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3279,10 +3298,10 @@
       <c r="F3" t="s">
         <v>31</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>33</v>
       </c>
       <c r="J3" t="s">
@@ -3328,7 +3347,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3347,10 +3366,10 @@
       <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>37</v>
       </c>
       <c r="J4" t="s">
@@ -3396,7 +3415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -3418,7 +3437,7 @@
       <c r="G5">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>41</v>
       </c>
       <c r="J5" t="s">
@@ -3464,7 +3483,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3483,14 +3502,14 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -3532,7 +3551,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -3554,7 +3573,7 @@
       <c r="G7">
         <v>8</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>48</v>
       </c>
       <c r="J7" t="s">
@@ -3600,7 +3619,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -3620,7 +3639,7 @@
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3656,7 +3675,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -3678,7 +3697,7 @@
       <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>53</v>
       </c>
       <c r="J9" t="s">
@@ -3724,7 +3743,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -3743,11 +3762,11 @@
       <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>301</v>
       </c>
       <c r="J10" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3783,7 +3802,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -3802,8 +3821,8 @@
       <c r="F11" t="s">
         <v>55</v>
       </c>
-      <c r="H11" t="s">
-        <v>864</v>
+      <c r="I11" t="s">
+        <v>863</v>
       </c>
       <c r="J11" t="s">
         <v>232</v>
@@ -3845,7 +3864,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3904,7 +3923,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -3926,11 +3945,11 @@
       <c r="G13">
         <v>24</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="K13">
         <v>36</v>
@@ -3972,7 +3991,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -3991,11 +4010,11 @@
       <c r="F14" t="s">
         <v>63</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4034,7 +4053,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4053,11 +4072,11 @@
       <c r="F15" t="s">
         <v>65</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -4096,7 +4115,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -4115,11 +4134,11 @@
       <c r="F16" t="s">
         <v>68</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -4177,11 +4196,11 @@
       <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K17">
         <v>12</v>
@@ -4239,11 +4258,11 @@
       <c r="F18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -4301,11 +4320,11 @@
       <c r="F19" t="s">
         <v>75</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>76</v>
       </c>
       <c r="J19" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -4363,11 +4382,11 @@
       <c r="F20" t="s">
         <v>77</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -4425,11 +4444,11 @@
       <c r="F21" t="s">
         <v>19</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -4487,11 +4506,11 @@
       <c r="F22" t="s">
         <v>55</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>80</v>
       </c>
       <c r="J22" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -4552,11 +4571,11 @@
       <c r="G23">
         <v>39</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K23">
         <v>54</v>
@@ -4617,11 +4636,11 @@
       <c r="F24" t="s">
         <v>70</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>84</v>
       </c>
       <c r="J24" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -4679,11 +4698,11 @@
       <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -4741,11 +4760,11 @@
       <c r="F26" t="s">
         <v>63</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -4803,11 +4822,11 @@
       <c r="F27" t="s">
         <v>89</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>90</v>
       </c>
       <c r="J27" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -4865,11 +4884,11 @@
       <c r="F28" t="s">
         <v>91</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>92</v>
       </c>
       <c r="J28" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -4927,11 +4946,11 @@
       <c r="F29" t="s">
         <v>93</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -4989,11 +5008,11 @@
       <c r="F30" t="s">
         <v>95</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>96</v>
       </c>
       <c r="J30" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K30">
         <v>4</v>
@@ -5051,11 +5070,11 @@
       <c r="F31" t="s">
         <v>77</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>97</v>
       </c>
       <c r="J31" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K31">
         <v>3</v>
@@ -5113,11 +5132,11 @@
       <c r="F32" t="s">
         <v>57</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>98</v>
       </c>
       <c r="J32" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -5175,11 +5194,11 @@
       <c r="F33" t="s">
         <v>55</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>99</v>
       </c>
       <c r="J33" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -5237,14 +5256,14 @@
       <c r="F34" t="s">
         <v>31</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>650</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>102</v>
       </c>
       <c r="J34" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K34">
         <v>33</v>
@@ -5305,11 +5324,11 @@
       <c r="F35" t="s">
         <v>103</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K35">
         <v>2.5</v>
@@ -5367,11 +5386,11 @@
       <c r="F36" t="s">
         <v>105</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>106</v>
       </c>
       <c r="J36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K36">
         <v>3</v>
@@ -5429,11 +5448,11 @@
       <c r="F37" t="s">
         <v>19</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>107</v>
       </c>
       <c r="J37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -5491,14 +5510,14 @@
       <c r="F38" t="s">
         <v>31</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>780</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K38">
         <v>30</v>
@@ -5559,11 +5578,11 @@
       <c r="F39" t="s">
         <v>103</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -5621,11 +5640,11 @@
       <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>111</v>
       </c>
       <c r="J40" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="K40">
         <v>1.5</v>
@@ -5683,11 +5702,11 @@
       <c r="F41" t="s">
         <v>19</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>110</v>
       </c>
       <c r="J41" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -5745,11 +5764,11 @@
       <c r="F42" t="s">
         <v>55</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K42">
         <v>3</v>
@@ -6044,7 +6063,7 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K47">
         <v>4</v>
@@ -6400,7 +6419,7 @@
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>130</v>
       </c>
       <c r="J53" t="s">
@@ -6468,11 +6487,11 @@
       <c r="G54">
         <v>13</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>134</v>
       </c>
       <c r="J54" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -6536,7 +6555,7 @@
       <c r="G55">
         <v>6</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>137</v>
       </c>
       <c r="J55" t="s">
@@ -6604,7 +6623,7 @@
       <c r="G56">
         <v>7</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>140</v>
       </c>
       <c r="J56" t="s">
@@ -6669,7 +6688,7 @@
       <c r="F57" t="s">
         <v>31</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>140</v>
       </c>
       <c r="J57" t="s">
@@ -6731,7 +6750,7 @@
       <c r="F58" t="s">
         <v>31</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>145</v>
       </c>
       <c r="J58" t="s">
@@ -6793,14 +6812,14 @@
       <c r="F59" t="s">
         <v>31</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>2952</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>148</v>
       </c>
       <c r="J59" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K59">
         <v>6</v>
@@ -6861,11 +6880,11 @@
       <c r="F60" t="s">
         <v>50</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K60">
         <v>6</v>
@@ -6912,16 +6931,16 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D61">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K61">
         <v>3</v>
@@ -6962,16 +6981,16 @@
         <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D62">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K62">
         <v>14</v>
@@ -7012,16 +7031,16 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D63">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K63">
         <v>3</v>
@@ -7068,13 +7087,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F64" t="s">
         <v>151</v>
       </c>
-      <c r="H64" t="s">
-        <v>885</v>
+      <c r="I64" t="s">
+        <v>884</v>
       </c>
       <c r="J64" t="s">
         <v>312</v>
@@ -7138,14 +7157,14 @@
       <c r="F65" t="s">
         <v>31</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>8</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>154</v>
       </c>
       <c r="J65" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K65">
         <v>12</v>
@@ -7209,7 +7228,7 @@
       <c r="G66">
         <v>56</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>155</v>
       </c>
       <c r="J66" t="s">
@@ -7274,7 +7293,7 @@
       <c r="G67">
         <v>17</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>158</v>
       </c>
       <c r="J67" t="s">
@@ -7339,11 +7358,11 @@
       <c r="G68">
         <v>20</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>161</v>
       </c>
       <c r="J68" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K68">
         <v>9</v>
@@ -7407,11 +7426,11 @@
       <c r="G69">
         <v>20</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>161</v>
       </c>
       <c r="J69" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K69">
         <v>9</v>
@@ -7475,11 +7494,11 @@
       <c r="G70">
         <v>20</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>161</v>
       </c>
       <c r="J70" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K70">
         <v>15</v>
@@ -7540,7 +7559,7 @@
       <c r="F71" t="s">
         <v>55</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>301</v>
       </c>
       <c r="J71" t="s">
@@ -7605,8 +7624,8 @@
       <c r="F72" t="s">
         <v>19</v>
       </c>
-      <c r="H72" t="s">
-        <v>889</v>
+      <c r="I72" t="s">
+        <v>888</v>
       </c>
       <c r="J72" t="s">
         <v>232</v>
@@ -7673,7 +7692,8 @@
       <c r="G73" s="1">
         <v>104</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1"/>
+      <c r="I73" t="s">
         <v>168</v>
       </c>
       <c r="J73" t="s">
@@ -7713,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="V73" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="W73" t="s">
         <v>27</v>
@@ -7738,11 +7758,11 @@
       <c r="F74" t="s">
         <v>55</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>170</v>
       </c>
       <c r="J74" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K74">
         <v>6</v>
@@ -7800,11 +7820,11 @@
       <c r="F75" t="s">
         <v>63</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>171</v>
       </c>
       <c r="J75" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K75">
         <v>15</v>
@@ -7862,11 +7882,11 @@
       <c r="F76" t="s">
         <v>172</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>173</v>
       </c>
       <c r="J76" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K76">
         <v>12</v>
@@ -7924,11 +7944,11 @@
       <c r="F77" t="s">
         <v>174</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>175</v>
       </c>
       <c r="J77" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K77">
         <v>3</v>
@@ -7986,11 +8006,11 @@
       <c r="F78" t="s">
         <v>176</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>177</v>
       </c>
       <c r="J78" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K78">
         <v>12</v>
@@ -8048,11 +8068,11 @@
       <c r="F79" t="s">
         <v>19</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>179</v>
       </c>
       <c r="J79" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K79">
         <v>12</v>
@@ -8110,11 +8130,11 @@
       <c r="F80" t="s">
         <v>180</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>181</v>
       </c>
       <c r="J80" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="K80">
         <v>9</v>
@@ -8172,14 +8192,14 @@
       <c r="F81" t="s">
         <v>31</v>
       </c>
-      <c r="G81" s="1">
+      <c r="H81" s="1">
         <v>2772</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>184</v>
       </c>
       <c r="J81" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="K81">
         <v>36</v>
@@ -8215,7 +8235,7 @@
         <v>0</v>
       </c>
       <c r="V81" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="W81" t="s">
         <v>27</v>
@@ -8240,11 +8260,11 @@
       <c r="F82" t="s">
         <v>55</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>185</v>
       </c>
       <c r="J82" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K82">
         <v>3</v>
@@ -8302,11 +8322,11 @@
       <c r="F83" t="s">
         <v>186</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>187</v>
       </c>
       <c r="J83" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K83">
         <v>3</v>
@@ -8364,11 +8384,11 @@
       <c r="F84" t="s">
         <v>188</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>189</v>
       </c>
       <c r="J84" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="K84">
         <v>6</v>
@@ -8710,16 +8730,16 @@
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K90">
         <v>82</v>
@@ -8760,16 +8780,16 @@
         <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K91">
         <v>32</v>
@@ -8810,16 +8830,16 @@
         <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K92">
         <v>9</v>
@@ -8874,7 +8894,7 @@
       <c r="G93" t="s">
         <v>200</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>201</v>
       </c>
       <c r="J93" t="s">
@@ -8936,7 +8956,7 @@
       <c r="F94" t="s">
         <v>203</v>
       </c>
-      <c r="H94" t="s">
+      <c r="I94" t="s">
         <v>204</v>
       </c>
       <c r="J94" t="s">
@@ -9001,7 +9021,7 @@
       <c r="G95" t="s">
         <v>206</v>
       </c>
-      <c r="H95" t="s">
+      <c r="I95" t="s">
         <v>201</v>
       </c>
       <c r="J95" t="s">
@@ -9063,7 +9083,7 @@
       <c r="F96" t="s">
         <v>203</v>
       </c>
-      <c r="H96" t="s">
+      <c r="I96" t="s">
         <v>208</v>
       </c>
       <c r="J96" t="s">
@@ -9128,7 +9148,7 @@
       <c r="G97" t="s">
         <v>200</v>
       </c>
-      <c r="H97" t="s">
+      <c r="I97" t="s">
         <v>211</v>
       </c>
       <c r="J97" t="s">
@@ -9190,7 +9210,7 @@
       <c r="F98" t="s">
         <v>212</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>213</v>
       </c>
       <c r="J98" t="s">
@@ -9252,7 +9272,7 @@
       <c r="F99" t="s">
         <v>214</v>
       </c>
-      <c r="H99" t="s">
+      <c r="I99" t="s">
         <v>215</v>
       </c>
       <c r="J99" t="s">
@@ -9317,7 +9337,7 @@
       <c r="G100" t="s">
         <v>218</v>
       </c>
-      <c r="H100" t="s">
+      <c r="I100" t="s">
         <v>219</v>
       </c>
       <c r="J100" t="s">
@@ -9382,7 +9402,7 @@
       <c r="G101" t="s">
         <v>223</v>
       </c>
-      <c r="H101" t="s">
+      <c r="I101" t="s">
         <v>224</v>
       </c>
       <c r="J101" t="s">
@@ -9447,7 +9467,7 @@
       <c r="F102" t="s">
         <v>227</v>
       </c>
-      <c r="H102" t="s">
+      <c r="I102" t="s">
         <v>228</v>
       </c>
       <c r="J102" t="s">
@@ -9509,7 +9529,7 @@
       <c r="F103" t="s">
         <v>229</v>
       </c>
-      <c r="H103" t="s">
+      <c r="I103" t="s">
         <v>228</v>
       </c>
       <c r="J103" t="s">
@@ -9571,7 +9591,7 @@
       <c r="F104" t="s">
         <v>230</v>
       </c>
-      <c r="H104" t="s">
+      <c r="I104" t="s">
         <v>231</v>
       </c>
       <c r="J104" t="s">
@@ -9633,7 +9653,7 @@
       <c r="F105" t="s">
         <v>233</v>
       </c>
-      <c r="H105" t="s">
+      <c r="I105" t="s">
         <v>234</v>
       </c>
       <c r="J105" t="s">
@@ -9698,7 +9718,7 @@
       <c r="F106" t="s">
         <v>237</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>238</v>
       </c>
       <c r="J106" t="s">
@@ -9760,7 +9780,7 @@
       <c r="F107" t="s">
         <v>239</v>
       </c>
-      <c r="H107" t="s">
+      <c r="I107" t="s">
         <v>240</v>
       </c>
       <c r="J107" t="s">
@@ -9825,7 +9845,7 @@
       <c r="F108" t="s">
         <v>242</v>
       </c>
-      <c r="H108" t="s">
+      <c r="I108" t="s">
         <v>243</v>
       </c>
       <c r="J108" t="s">
@@ -10014,7 +10034,7 @@
       <c r="G111" t="s">
         <v>249</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>250</v>
       </c>
       <c r="J111" t="s">
@@ -10079,7 +10099,7 @@
       <c r="F112" t="s">
         <v>253</v>
       </c>
-      <c r="H112" t="s">
+      <c r="I112" t="s">
         <v>254</v>
       </c>
       <c r="J112" t="s">
@@ -10144,7 +10164,7 @@
       <c r="G113" t="s">
         <v>256</v>
       </c>
-      <c r="H113" t="s">
+      <c r="I113" t="s">
         <v>257</v>
       </c>
       <c r="J113" t="s">
@@ -10209,7 +10229,7 @@
       <c r="F114" t="s">
         <v>227</v>
       </c>
-      <c r="H114" t="s">
+      <c r="I114" t="s">
         <v>260</v>
       </c>
       <c r="J114" t="s">
@@ -10271,7 +10291,7 @@
       <c r="F115" t="s">
         <v>261</v>
       </c>
-      <c r="H115" t="s">
+      <c r="I115" t="s">
         <v>262</v>
       </c>
       <c r="J115" t="s">
@@ -10333,7 +10353,7 @@
       <c r="F116" t="s">
         <v>263</v>
       </c>
-      <c r="H116" t="s">
+      <c r="I116" t="s">
         <v>262</v>
       </c>
       <c r="J116" t="s">
@@ -10395,7 +10415,7 @@
       <c r="F117" t="s">
         <v>264</v>
       </c>
-      <c r="H117" t="s">
+      <c r="I117" t="s">
         <v>265</v>
       </c>
       <c r="J117" t="s">
@@ -10457,7 +10477,7 @@
       <c r="F118" t="s">
         <v>267</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>268</v>
       </c>
       <c r="J118" t="s">
@@ -10522,7 +10542,7 @@
       <c r="F119" t="s">
         <v>271</v>
       </c>
-      <c r="H119" t="s">
+      <c r="I119" t="s">
         <v>272</v>
       </c>
       <c r="J119" t="s">
@@ -10584,7 +10604,7 @@
       <c r="F120" t="s">
         <v>273</v>
       </c>
-      <c r="H120" t="s">
+      <c r="I120" t="s">
         <v>274</v>
       </c>
       <c r="J120" t="s">
@@ -10646,7 +10666,7 @@
       <c r="F121" t="s">
         <v>275</v>
       </c>
-      <c r="H121" t="s">
+      <c r="I121" t="s">
         <v>234</v>
       </c>
       <c r="J121" t="s">
@@ -10711,7 +10731,7 @@
       <c r="F122" t="s">
         <v>277</v>
       </c>
-      <c r="H122" t="s">
+      <c r="I122" t="s">
         <v>278</v>
       </c>
       <c r="J122" t="s">
@@ -10776,7 +10796,7 @@
       <c r="F123" t="s">
         <v>279</v>
       </c>
-      <c r="H123" t="s">
+      <c r="I123" t="s">
         <v>278</v>
       </c>
       <c r="J123" t="s">
@@ -10841,7 +10861,7 @@
       <c r="F124" t="s">
         <v>280</v>
       </c>
-      <c r="H124" t="s">
+      <c r="I124" t="s">
         <v>281</v>
       </c>
       <c r="J124" t="s">
@@ -10903,7 +10923,7 @@
       <c r="F125" t="s">
         <v>283</v>
       </c>
-      <c r="H125" t="s">
+      <c r="I125" t="s">
         <v>284</v>
       </c>
       <c r="J125" t="s">
@@ -10968,7 +10988,7 @@
       <c r="F126" t="s">
         <v>286</v>
       </c>
-      <c r="H126" t="s">
+      <c r="I126" t="s">
         <v>287</v>
       </c>
       <c r="J126" t="s">
@@ -11030,7 +11050,7 @@
       <c r="F127" t="s">
         <v>288</v>
       </c>
-      <c r="H127" t="s">
+      <c r="I127" t="s">
         <v>289</v>
       </c>
       <c r="J127" t="s">
@@ -11095,7 +11115,7 @@
       <c r="G128" t="s">
         <v>206</v>
       </c>
-      <c r="H128" t="s">
+      <c r="I128" t="s">
         <v>293</v>
       </c>
       <c r="J128" t="s">
@@ -11157,7 +11177,7 @@
       <c r="F129" t="s">
         <v>294</v>
       </c>
-      <c r="H129" t="s">
+      <c r="I129" t="s">
         <v>215</v>
       </c>
       <c r="J129" t="s">
@@ -11222,7 +11242,7 @@
       <c r="G130" t="s">
         <v>206</v>
       </c>
-      <c r="H130" t="s">
+      <c r="I130" t="s">
         <v>293</v>
       </c>
       <c r="J130" t="s">
@@ -11284,7 +11304,7 @@
       <c r="F131" t="s">
         <v>294</v>
       </c>
-      <c r="H131" t="s">
+      <c r="I131" t="s">
         <v>215</v>
       </c>
       <c r="J131" t="s">
@@ -11349,7 +11369,7 @@
       <c r="G132" t="s">
         <v>206</v>
       </c>
-      <c r="H132" t="s">
+      <c r="I132" t="s">
         <v>293</v>
       </c>
       <c r="J132" t="s">
@@ -11414,7 +11434,7 @@
       <c r="F133" t="s">
         <v>294</v>
       </c>
-      <c r="H133" t="s">
+      <c r="I133" t="s">
         <v>293</v>
       </c>
       <c r="J133" t="s">
@@ -11479,7 +11499,7 @@
       <c r="F134" t="s">
         <v>299</v>
       </c>
-      <c r="H134" t="s">
+      <c r="I134" t="s">
         <v>300</v>
       </c>
       <c r="J134" t="s">
@@ -11544,7 +11564,7 @@
       <c r="F135" t="s">
         <v>55</v>
       </c>
-      <c r="H135" t="s">
+      <c r="I135" t="s">
         <v>301</v>
       </c>
       <c r="J135" t="s">
@@ -11609,7 +11629,7 @@
       <c r="G136" t="s">
         <v>206</v>
       </c>
-      <c r="H136" t="s">
+      <c r="I136" t="s">
         <v>304</v>
       </c>
       <c r="J136" t="s">
@@ -11671,7 +11691,7 @@
       <c r="F137" t="s">
         <v>294</v>
       </c>
-      <c r="H137" t="s">
+      <c r="I137" t="s">
         <v>293</v>
       </c>
       <c r="J137" t="s">
@@ -11736,7 +11756,7 @@
       <c r="F138" t="s">
         <v>299</v>
       </c>
-      <c r="H138" t="s">
+      <c r="I138" t="s">
         <v>300</v>
       </c>
       <c r="J138" t="s">
@@ -11801,7 +11821,7 @@
       <c r="G139" t="s">
         <v>223</v>
       </c>
-      <c r="H139" t="s">
+      <c r="I139" t="s">
         <v>215</v>
       </c>
       <c r="J139" t="s">
@@ -11863,7 +11883,7 @@
       <c r="F140" t="s">
         <v>294</v>
       </c>
-      <c r="H140" t="s">
+      <c r="I140" t="s">
         <v>308</v>
       </c>
       <c r="J140" t="s">
@@ -11925,7 +11945,7 @@
       <c r="F141" t="s">
         <v>299</v>
       </c>
-      <c r="H141" t="s">
+      <c r="I141" t="s">
         <v>309</v>
       </c>
       <c r="J141" t="s">
@@ -11990,7 +12010,7 @@
       <c r="G142" t="s">
         <v>223</v>
       </c>
-      <c r="H142" t="s">
+      <c r="I142" t="s">
         <v>215</v>
       </c>
       <c r="J142" t="s">
@@ -12052,7 +12072,7 @@
       <c r="F143" t="s">
         <v>294</v>
       </c>
-      <c r="H143" t="s">
+      <c r="I143" t="s">
         <v>308</v>
       </c>
       <c r="J143" t="s">
@@ -12114,7 +12134,7 @@
       <c r="F144" t="s">
         <v>299</v>
       </c>
-      <c r="H144" t="s">
+      <c r="I144" t="s">
         <v>309</v>
       </c>
       <c r="J144" t="s">
@@ -12179,7 +12199,7 @@
       <c r="G145" t="s">
         <v>223</v>
       </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>308</v>
       </c>
       <c r="J145" t="s">
@@ -12241,7 +12261,7 @@
       <c r="F146" t="s">
         <v>299</v>
       </c>
-      <c r="H146" t="s">
+      <c r="I146" t="s">
         <v>308</v>
       </c>
       <c r="J146" t="s">
@@ -12303,7 +12323,7 @@
       <c r="F147" t="s">
         <v>242</v>
       </c>
-      <c r="H147" t="s">
+      <c r="I147" t="s">
         <v>314</v>
       </c>
       <c r="J147" t="s">
@@ -12430,7 +12450,7 @@
       <c r="F149" t="s">
         <v>31</v>
       </c>
-      <c r="H149" t="s">
+      <c r="I149" t="s">
         <v>308</v>
       </c>
       <c r="J149" t="s">
@@ -12492,7 +12512,7 @@
       <c r="F150" t="s">
         <v>294</v>
       </c>
-      <c r="H150" t="s">
+      <c r="I150" t="s">
         <v>308</v>
       </c>
       <c r="J150" t="s">
@@ -12554,7 +12574,7 @@
       <c r="F151" t="s">
         <v>299</v>
       </c>
-      <c r="H151" t="s">
+      <c r="I151" t="s">
         <v>309</v>
       </c>
       <c r="J151" t="s">
@@ -12684,7 +12704,7 @@
       <c r="G153" t="s">
         <v>321</v>
       </c>
-      <c r="H153" t="s">
+      <c r="I153" t="s">
         <v>322</v>
       </c>
       <c r="J153" t="s">
@@ -12746,7 +12766,7 @@
       <c r="F154" t="s">
         <v>294</v>
       </c>
-      <c r="H154" t="s">
+      <c r="I154" t="s">
         <v>304</v>
       </c>
       <c r="J154" t="s">
@@ -12808,7 +12828,7 @@
       <c r="F155" t="s">
         <v>299</v>
       </c>
-      <c r="H155" t="s">
+      <c r="I155" t="s">
         <v>309</v>
       </c>
       <c r="J155" t="s">
@@ -12876,7 +12896,7 @@
       <c r="G156" t="s">
         <v>223</v>
       </c>
-      <c r="H156" t="s">
+      <c r="I156" t="s">
         <v>215</v>
       </c>
       <c r="J156" t="s">
@@ -12938,7 +12958,7 @@
       <c r="F157" t="s">
         <v>294</v>
       </c>
-      <c r="H157" t="s">
+      <c r="I157" t="s">
         <v>308</v>
       </c>
       <c r="J157" t="s">
@@ -13000,7 +13020,7 @@
       <c r="F158" t="s">
         <v>299</v>
       </c>
-      <c r="H158" t="s">
+      <c r="I158" t="s">
         <v>309</v>
       </c>
       <c r="J158" t="s">
@@ -13068,7 +13088,7 @@
       <c r="G159" t="s">
         <v>206</v>
       </c>
-      <c r="H159" t="s">
+      <c r="I159" t="s">
         <v>304</v>
       </c>
       <c r="J159" t="s">
@@ -13130,7 +13150,7 @@
       <c r="F160" t="s">
         <v>294</v>
       </c>
-      <c r="H160" t="s">
+      <c r="I160" t="s">
         <v>215</v>
       </c>
       <c r="J160" t="s">
@@ -13192,7 +13212,7 @@
       <c r="F161" t="s">
         <v>299</v>
       </c>
-      <c r="H161" t="s">
+      <c r="I161" t="s">
         <v>215</v>
       </c>
       <c r="J161" t="s">
@@ -13254,7 +13274,7 @@
       <c r="F162" t="s">
         <v>31</v>
       </c>
-      <c r="H162" t="s">
+      <c r="I162" t="s">
         <v>304</v>
       </c>
       <c r="J162" t="s">
@@ -13316,7 +13336,7 @@
       <c r="F163" t="s">
         <v>55</v>
       </c>
-      <c r="H163" t="s">
+      <c r="I163" t="s">
         <v>308</v>
       </c>
       <c r="J163" t="s">
@@ -13378,7 +13398,7 @@
       <c r="F164" t="s">
         <v>327</v>
       </c>
-      <c r="H164" t="s">
+      <c r="I164" t="s">
         <v>314</v>
       </c>
       <c r="J164" t="s">
@@ -13446,7 +13466,7 @@
       <c r="G165" t="s">
         <v>223</v>
       </c>
-      <c r="H165" t="s">
+      <c r="I165" t="s">
         <v>330</v>
       </c>
       <c r="J165" t="s">
@@ -13514,7 +13534,7 @@
       <c r="G166" t="s">
         <v>223</v>
       </c>
-      <c r="H166" t="s">
+      <c r="I166" t="s">
         <v>334</v>
       </c>
       <c r="J166" t="s">
@@ -13579,7 +13599,7 @@
       <c r="G167" t="s">
         <v>223</v>
       </c>
-      <c r="H167" t="s">
+      <c r="I167" t="s">
         <v>308</v>
       </c>
       <c r="J167" t="s">
@@ -13641,7 +13661,7 @@
       <c r="F168" t="s">
         <v>299</v>
       </c>
-      <c r="H168" t="s">
+      <c r="I168" t="s">
         <v>309</v>
       </c>
       <c r="J168" t="s">
@@ -13703,7 +13723,7 @@
       <c r="F169" t="s">
         <v>336</v>
       </c>
-      <c r="H169" t="s">
+      <c r="I169" t="s">
         <v>337</v>
       </c>
       <c r="J169" t="s">
@@ -13765,7 +13785,7 @@
       <c r="F170" t="s">
         <v>31</v>
       </c>
-      <c r="H170" t="s">
+      <c r="I170" t="s">
         <v>314</v>
       </c>
       <c r="J170" t="s">
@@ -13830,7 +13850,7 @@
       <c r="F171" t="s">
         <v>299</v>
       </c>
-      <c r="H171" t="s">
+      <c r="I171" t="s">
         <v>314</v>
       </c>
       <c r="J171" t="s">
@@ -13892,7 +13912,7 @@
       <c r="E172" t="s">
         <v>339</v>
       </c>
-      <c r="H172" t="s">
+      <c r="I172" t="s">
         <v>340</v>
       </c>
       <c r="J172" t="s">
@@ -13960,7 +13980,7 @@
       <c r="G173" t="s">
         <v>343</v>
       </c>
-      <c r="H173" t="s">
+      <c r="I173" t="s">
         <v>293</v>
       </c>
       <c r="J173" t="s">
@@ -14025,7 +14045,7 @@
       <c r="G174" t="s">
         <v>218</v>
       </c>
-      <c r="H174" t="s">
+      <c r="I174" t="s">
         <v>322</v>
       </c>
       <c r="J174" t="s">
@@ -14087,7 +14107,7 @@
       <c r="F175" t="s">
         <v>299</v>
       </c>
-      <c r="H175" t="s">
+      <c r="I175" t="s">
         <v>345</v>
       </c>
       <c r="J175" t="s">
@@ -14149,7 +14169,7 @@
       <c r="F176" t="s">
         <v>299</v>
       </c>
-      <c r="H176" t="s">
+      <c r="I176" t="s">
         <v>300</v>
       </c>
       <c r="J176" t="s">
@@ -14211,7 +14231,7 @@
       <c r="F177" t="s">
         <v>348</v>
       </c>
-      <c r="H177" t="s">
+      <c r="I177" t="s">
         <v>349</v>
       </c>
       <c r="J177" t="s">
@@ -14273,7 +14293,7 @@
       <c r="F178" t="s">
         <v>350</v>
       </c>
-      <c r="H178" t="s">
+      <c r="I178" t="s">
         <v>351</v>
       </c>
       <c r="J178" t="s">
@@ -14335,7 +14355,7 @@
       <c r="F179" t="s">
         <v>353</v>
       </c>
-      <c r="H179" t="s">
+      <c r="I179" t="s">
         <v>301</v>
       </c>
       <c r="J179" t="s">
@@ -14397,7 +14417,7 @@
       <c r="F180" t="s">
         <v>242</v>
       </c>
-      <c r="H180" t="s">
+      <c r="I180" t="s">
         <v>243</v>
       </c>
       <c r="J180" t="s">
@@ -14459,7 +14479,7 @@
       <c r="F181" t="s">
         <v>354</v>
       </c>
-      <c r="H181" t="s">
+      <c r="I181" t="s">
         <v>314</v>
       </c>
       <c r="J181" t="s">
@@ -14524,7 +14544,7 @@
       <c r="F182" t="s">
         <v>355</v>
       </c>
-      <c r="H182" t="s">
+      <c r="I182" t="s">
         <v>314</v>
       </c>
       <c r="J182" t="s">
@@ -14589,7 +14609,7 @@
       <c r="F183" t="s">
         <v>288</v>
       </c>
-      <c r="H183" t="s">
+      <c r="I183" t="s">
         <v>356</v>
       </c>
       <c r="J183" t="s">
@@ -14654,7 +14674,7 @@
       <c r="G184" t="s">
         <v>343</v>
       </c>
-      <c r="H184" t="s">
+      <c r="I184" t="s">
         <v>361</v>
       </c>
       <c r="J184" t="s">
@@ -14719,7 +14739,7 @@
       <c r="F185" t="s">
         <v>364</v>
       </c>
-      <c r="H185" t="s">
+      <c r="I185" t="s">
         <v>365</v>
       </c>
       <c r="J185" t="s">
@@ -14843,7 +14863,7 @@
       <c r="G187" t="s">
         <v>371</v>
       </c>
-      <c r="H187" t="s">
+      <c r="I187" t="s">
         <v>372</v>
       </c>
       <c r="J187" t="s">
@@ -14905,7 +14925,7 @@
       <c r="F188" t="s">
         <v>374</v>
       </c>
-      <c r="H188" t="s">
+      <c r="I188" t="s">
         <v>375</v>
       </c>
       <c r="J188" t="s">
@@ -14970,7 +14990,7 @@
       <c r="F189" t="s">
         <v>378</v>
       </c>
-      <c r="H189" t="s">
+      <c r="I189" t="s">
         <v>379</v>
       </c>
       <c r="J189" t="s">
@@ -15029,7 +15049,7 @@
       <c r="F190" t="s">
         <v>380</v>
       </c>
-      <c r="H190" t="s">
+      <c r="I190" t="s">
         <v>381</v>
       </c>
       <c r="J190" t="s">
@@ -15091,7 +15111,7 @@
       <c r="F191" t="s">
         <v>383</v>
       </c>
-      <c r="H191" t="s">
+      <c r="I191" t="s">
         <v>384</v>
       </c>
       <c r="J191" t="s">
@@ -15156,7 +15176,7 @@
       <c r="F192" t="s">
         <v>387</v>
       </c>
-      <c r="H192" t="s">
+      <c r="I192" t="s">
         <v>243</v>
       </c>
       <c r="J192" t="s">
@@ -15280,7 +15300,7 @@
       <c r="G194" t="s">
         <v>392</v>
       </c>
-      <c r="H194" t="s">
+      <c r="I194" t="s">
         <v>393</v>
       </c>
       <c r="J194" t="s">
@@ -15342,7 +15362,7 @@
       <c r="F195" t="s">
         <v>395</v>
       </c>
-      <c r="H195" t="s">
+      <c r="I195" t="s">
         <v>396</v>
       </c>
       <c r="J195" t="s">
@@ -15407,7 +15427,7 @@
       <c r="F196" t="s">
         <v>399</v>
       </c>
-      <c r="H196" t="s">
+      <c r="I196" t="s">
         <v>375</v>
       </c>
       <c r="J196" t="s">
@@ -15472,7 +15492,7 @@
       <c r="F197" t="s">
         <v>400</v>
       </c>
-      <c r="H197" t="s">
+      <c r="I197" t="s">
         <v>401</v>
       </c>
       <c r="J197" t="s">
@@ -15534,7 +15554,7 @@
       <c r="F198" t="s">
         <v>387</v>
       </c>
-      <c r="H198" t="s">
+      <c r="I198" t="s">
         <v>243</v>
       </c>
       <c r="J198" t="s">
@@ -15596,7 +15616,7 @@
       <c r="F199" t="s">
         <v>403</v>
       </c>
-      <c r="H199" t="s">
+      <c r="I199" t="s">
         <v>375</v>
       </c>
       <c r="J199" t="s">
@@ -15723,7 +15743,7 @@
       <c r="G201" t="s">
         <v>200</v>
       </c>
-      <c r="H201" t="s">
+      <c r="I201" t="s">
         <v>409</v>
       </c>
       <c r="J201" t="s">
@@ -15785,7 +15805,7 @@
       <c r="F202" t="s">
         <v>400</v>
       </c>
-      <c r="H202" t="s">
+      <c r="I202" t="s">
         <v>301</v>
       </c>
       <c r="J202" t="s">
@@ -15847,7 +15867,7 @@
       <c r="F203" t="s">
         <v>411</v>
       </c>
-      <c r="H203" t="s">
+      <c r="I203" t="s">
         <v>412</v>
       </c>
       <c r="J203" t="s">
@@ -15909,7 +15929,7 @@
       <c r="F204" t="s">
         <v>413</v>
       </c>
-      <c r="H204" t="s">
+      <c r="I204" t="s">
         <v>334</v>
       </c>
       <c r="J204" t="s">
@@ -15971,7 +15991,7 @@
       <c r="F205" t="s">
         <v>414</v>
       </c>
-      <c r="H205" t="s">
+      <c r="I205" t="s">
         <v>415</v>
       </c>
       <c r="J205" t="s">
@@ -16033,7 +16053,7 @@
       <c r="F206" t="s">
         <v>417</v>
       </c>
-      <c r="H206" t="s">
+      <c r="I206" t="s">
         <v>418</v>
       </c>
       <c r="J206" t="s">
@@ -16160,7 +16180,7 @@
       <c r="G208" t="s">
         <v>425</v>
       </c>
-      <c r="H208" t="s">
+      <c r="I208" t="s">
         <v>426</v>
       </c>
       <c r="J208" t="s">
@@ -16225,7 +16245,7 @@
       <c r="G209" t="s">
         <v>429</v>
       </c>
-      <c r="H209" t="s">
+      <c r="I209" t="s">
         <v>365</v>
       </c>
       <c r="J209" t="s">
@@ -16290,7 +16310,7 @@
       <c r="G210" t="s">
         <v>200</v>
       </c>
-      <c r="H210" t="s">
+      <c r="I210" t="s">
         <v>409</v>
       </c>
       <c r="J210" t="s">
@@ -16352,7 +16372,7 @@
       <c r="F211" t="s">
         <v>431</v>
       </c>
-      <c r="H211" t="s">
+      <c r="I211" t="s">
         <v>361</v>
       </c>
       <c r="J211" t="s">
@@ -16417,7 +16437,7 @@
       <c r="F212" t="s">
         <v>434</v>
       </c>
-      <c r="H212" t="s">
+      <c r="I212" t="s">
         <v>435</v>
       </c>
       <c r="J212" t="s">
@@ -16479,7 +16499,7 @@
       <c r="F213" t="s">
         <v>436</v>
       </c>
-      <c r="H213" t="s">
+      <c r="I213" t="s">
         <v>375</v>
       </c>
       <c r="J213" t="s">
@@ -16544,7 +16564,7 @@
       <c r="F214" t="s">
         <v>439</v>
       </c>
-      <c r="H214" t="s">
+      <c r="I214" t="s">
         <v>440</v>
       </c>
       <c r="J214" t="s">
@@ -16606,7 +16626,7 @@
       <c r="F215" t="s">
         <v>441</v>
       </c>
-      <c r="H215" t="s">
+      <c r="I215" t="s">
         <v>300</v>
       </c>
       <c r="J215" t="s">
@@ -16727,7 +16747,7 @@
       <c r="F217" t="s">
         <v>55</v>
       </c>
-      <c r="H217" t="s">
+      <c r="I217" t="s">
         <v>445</v>
       </c>
       <c r="J217" t="s">
@@ -16792,7 +16812,7 @@
       <c r="F218" t="s">
         <v>447</v>
       </c>
-      <c r="H218" t="s">
+      <c r="I218" t="s">
         <v>300</v>
       </c>
       <c r="J218" t="s">
@@ -16857,7 +16877,7 @@
       <c r="G219" t="s">
         <v>450</v>
       </c>
-      <c r="H219" t="s">
+      <c r="I219" t="s">
         <v>451</v>
       </c>
       <c r="J219" t="s">
@@ -16922,7 +16942,7 @@
       <c r="G220" t="s">
         <v>454</v>
       </c>
-      <c r="H220" t="s">
+      <c r="I220" t="s">
         <v>455</v>
       </c>
       <c r="J220" t="s">
@@ -16984,7 +17004,7 @@
       <c r="F221" t="s">
         <v>457</v>
       </c>
-      <c r="H221" t="s">
+      <c r="I221" t="s">
         <v>361</v>
       </c>
       <c r="J221" t="s">
@@ -17052,7 +17072,7 @@
       <c r="G222" t="s">
         <v>454</v>
       </c>
-      <c r="H222" t="s">
+      <c r="I222" t="s">
         <v>455</v>
       </c>
       <c r="J222" t="s">
@@ -17114,7 +17134,7 @@
       <c r="F223" t="s">
         <v>431</v>
       </c>
-      <c r="H223" t="s">
+      <c r="I223" t="s">
         <v>459</v>
       </c>
       <c r="J223" t="s">
@@ -17179,7 +17199,7 @@
       <c r="G224" t="s">
         <v>462</v>
       </c>
-      <c r="H224" t="s">
+      <c r="I224" t="s">
         <v>463</v>
       </c>
       <c r="J224" t="s">
@@ -17241,7 +17261,7 @@
       <c r="F225" t="s">
         <v>465</v>
       </c>
-      <c r="H225" t="s">
+      <c r="I225" t="s">
         <v>466</v>
       </c>
       <c r="J225" t="s">
@@ -17303,7 +17323,7 @@
       <c r="F226" t="s">
         <v>387</v>
       </c>
-      <c r="H226" t="s">
+      <c r="I226" t="s">
         <v>467</v>
       </c>
       <c r="J226" t="s">
@@ -17365,7 +17385,7 @@
       <c r="F227" t="s">
         <v>468</v>
       </c>
-      <c r="H227" t="s">
+      <c r="I227" t="s">
         <v>469</v>
       </c>
       <c r="J227" t="s">
@@ -17430,7 +17450,7 @@
       <c r="G228" t="s">
         <v>472</v>
       </c>
-      <c r="H228" t="s">
+      <c r="I228" t="s">
         <v>473</v>
       </c>
       <c r="J228" t="s">
@@ -17492,7 +17512,7 @@
       <c r="F229" t="s">
         <v>475</v>
       </c>
-      <c r="H229" t="s">
+      <c r="I229" t="s">
         <v>476</v>
       </c>
       <c r="J229" t="s">
@@ -17616,7 +17636,7 @@
       <c r="F231" t="s">
         <v>481</v>
       </c>
-      <c r="H231" t="s">
+      <c r="I231" t="s">
         <v>480</v>
       </c>
       <c r="J231" t="s">
@@ -17681,7 +17701,7 @@
       <c r="F232" t="s">
         <v>483</v>
       </c>
-      <c r="H232" t="s">
+      <c r="I232" t="s">
         <v>480</v>
       </c>
       <c r="J232" t="s">
@@ -17746,7 +17766,7 @@
       <c r="F233" t="s">
         <v>484</v>
       </c>
-      <c r="H233" t="s">
+      <c r="I233" t="s">
         <v>480</v>
       </c>
       <c r="J233" t="s">
@@ -17811,7 +17831,7 @@
       <c r="F234" t="s">
         <v>485</v>
       </c>
-      <c r="H234" t="s">
+      <c r="I234" t="s">
         <v>480</v>
       </c>
       <c r="J234" t="s">
@@ -17876,7 +17896,7 @@
       <c r="F235" t="s">
         <v>486</v>
       </c>
-      <c r="H235" t="s">
+      <c r="I235" t="s">
         <v>480</v>
       </c>
       <c r="J235" t="s">
@@ -17941,7 +17961,7 @@
       <c r="F236" t="s">
         <v>488</v>
       </c>
-      <c r="H236" t="s">
+      <c r="I236" t="s">
         <v>480</v>
       </c>
       <c r="J236" t="s">
@@ -18065,7 +18085,7 @@
       <c r="F238" t="s">
         <v>491</v>
       </c>
-      <c r="H238" t="s">
+      <c r="I238" t="s">
         <v>492</v>
       </c>
       <c r="J238" t="s">
@@ -18133,7 +18153,7 @@
       <c r="G239" t="s">
         <v>494</v>
       </c>
-      <c r="H239" t="s">
+      <c r="I239" t="s">
         <v>495</v>
       </c>
       <c r="J239" t="s">
@@ -18198,7 +18218,7 @@
       <c r="F240" t="s">
         <v>498</v>
       </c>
-      <c r="H240" t="s">
+      <c r="I240" t="s">
         <v>499</v>
       </c>
       <c r="J240" t="s">
@@ -18263,7 +18283,7 @@
       <c r="F241" t="s">
         <v>500</v>
       </c>
-      <c r="H241" t="s">
+      <c r="I241" t="s">
         <v>501</v>
       </c>
       <c r="J241" t="s">
@@ -18328,7 +18348,7 @@
       <c r="F242" t="s">
         <v>417</v>
       </c>
-      <c r="H242" t="s">
+      <c r="I242" t="s">
         <v>504</v>
       </c>
       <c r="J242" t="s">
@@ -18396,7 +18416,7 @@
       <c r="G243" t="s">
         <v>223</v>
       </c>
-      <c r="H243" t="s">
+      <c r="I243" t="s">
         <v>508</v>
       </c>
       <c r="J243" t="s">
@@ -18458,7 +18478,7 @@
       <c r="F244" t="s">
         <v>509</v>
       </c>
-      <c r="H244" t="s">
+      <c r="I244" t="s">
         <v>510</v>
       </c>
       <c r="J244" t="s">
@@ -18523,7 +18543,7 @@
       <c r="F245" t="s">
         <v>513</v>
       </c>
-      <c r="H245" t="s">
+      <c r="I245" t="s">
         <v>445</v>
       </c>
       <c r="J245" t="s">
@@ -18591,7 +18611,7 @@
       <c r="G246" t="s">
         <v>223</v>
       </c>
-      <c r="H246" t="s">
+      <c r="I246" t="s">
         <v>508</v>
       </c>
       <c r="J246" t="s">
@@ -18656,7 +18676,7 @@
       <c r="G247" t="s">
         <v>454</v>
       </c>
-      <c r="H247" t="s">
+      <c r="I247" t="s">
         <v>516</v>
       </c>
       <c r="J247" t="s">
@@ -18721,7 +18741,7 @@
       <c r="F248" t="s">
         <v>519</v>
       </c>
-      <c r="H248" t="s">
+      <c r="I248" t="s">
         <v>412</v>
       </c>
       <c r="J248" t="s">
@@ -18786,7 +18806,7 @@
       <c r="F249" t="s">
         <v>520</v>
       </c>
-      <c r="H249" t="s">
+      <c r="I249" t="s">
         <v>521</v>
       </c>
       <c r="J249" t="s">
@@ -18851,7 +18871,7 @@
       <c r="F250" t="s">
         <v>522</v>
       </c>
-      <c r="H250" t="s">
+      <c r="I250" t="s">
         <v>523</v>
       </c>
       <c r="J250" t="s">
@@ -18913,7 +18933,7 @@
       <c r="F251" t="s">
         <v>524</v>
       </c>
-      <c r="H251" t="s">
+      <c r="I251" t="s">
         <v>525</v>
       </c>
       <c r="J251" t="s">
@@ -18978,7 +18998,7 @@
       <c r="F252" t="s">
         <v>527</v>
       </c>
-      <c r="H252" t="s">
+      <c r="I252" t="s">
         <v>528</v>
       </c>
       <c r="J252" t="s">
@@ -19040,7 +19060,7 @@
       <c r="F253" t="s">
         <v>529</v>
       </c>
-      <c r="H253" t="s">
+      <c r="I253" t="s">
         <v>528</v>
       </c>
       <c r="J253" t="s">
@@ -19105,7 +19125,7 @@
       <c r="F254" t="s">
         <v>530</v>
       </c>
-      <c r="H254" t="s">
+      <c r="I254" t="s">
         <v>531</v>
       </c>
       <c r="J254" t="s">
@@ -19170,7 +19190,7 @@
       <c r="F255" t="s">
         <v>532</v>
       </c>
-      <c r="H255" t="s">
+      <c r="I255" t="s">
         <v>533</v>
       </c>
       <c r="J255" t="s">
@@ -19235,7 +19255,7 @@
       <c r="G256" t="s">
         <v>536</v>
       </c>
-      <c r="H256" t="s">
+      <c r="I256" t="s">
         <v>537</v>
       </c>
       <c r="J256" t="s">
@@ -19294,7 +19314,7 @@
       <c r="F257" t="s">
         <v>539</v>
       </c>
-      <c r="H257" t="s">
+      <c r="I257" t="s">
         <v>540</v>
       </c>
       <c r="J257" t="s">
@@ -19356,7 +19376,7 @@
       <c r="F258" t="s">
         <v>543</v>
       </c>
-      <c r="H258" t="s">
+      <c r="I258" t="s">
         <v>544</v>
       </c>
       <c r="J258" t="s">
@@ -19415,7 +19435,7 @@
       <c r="F259" t="s">
         <v>545</v>
       </c>
-      <c r="H259" t="s">
+      <c r="I259" t="s">
         <v>546</v>
       </c>
       <c r="J259" t="s">
@@ -19474,7 +19494,7 @@
       <c r="F260" t="s">
         <v>547</v>
       </c>
-      <c r="H260" t="s">
+      <c r="I260" t="s">
         <v>548</v>
       </c>
       <c r="J260" t="s">
@@ -19536,7 +19556,7 @@
       <c r="F261" t="s">
         <v>242</v>
       </c>
-      <c r="H261" t="s">
+      <c r="I261" t="s">
         <v>349</v>
       </c>
       <c r="J261" t="s">
@@ -19595,7 +19615,7 @@
       <c r="F262" t="s">
         <v>550</v>
       </c>
-      <c r="H262" t="s">
+      <c r="I262" t="s">
         <v>349</v>
       </c>
       <c r="J262" t="s">
@@ -19654,7 +19674,7 @@
       <c r="F263" t="s">
         <v>551</v>
       </c>
-      <c r="H263" t="s">
+      <c r="I263" t="s">
         <v>349</v>
       </c>
       <c r="J263" t="s">
@@ -19713,7 +19733,7 @@
       <c r="F264" t="s">
         <v>552</v>
       </c>
-      <c r="H264" t="s">
+      <c r="I264" t="s">
         <v>553</v>
       </c>
       <c r="J264" t="s">
@@ -19778,7 +19798,7 @@
       <c r="G265" t="s">
         <v>557</v>
       </c>
-      <c r="H265" t="s">
+      <c r="I265" t="s">
         <v>558</v>
       </c>
       <c r="J265" t="s">
@@ -19840,7 +19860,7 @@
       <c r="F266" t="s">
         <v>561</v>
       </c>
-      <c r="H266" t="s">
+      <c r="I266" t="s">
         <v>523</v>
       </c>
       <c r="J266" t="s">
@@ -19902,7 +19922,7 @@
       <c r="F267" t="s">
         <v>564</v>
       </c>
-      <c r="H267" t="s">
+      <c r="I267" t="s">
         <v>565</v>
       </c>
       <c r="J267" t="s">
@@ -19961,7 +19981,7 @@
       <c r="F268" t="s">
         <v>566</v>
       </c>
-      <c r="H268" t="s">
+      <c r="I268" t="s">
         <v>567</v>
       </c>
       <c r="J268" t="s">
@@ -20020,7 +20040,7 @@
       <c r="F269" t="s">
         <v>242</v>
       </c>
-      <c r="H269" t="s">
+      <c r="I269" t="s">
         <v>568</v>
       </c>
       <c r="J269" t="s">
@@ -20082,7 +20102,7 @@
       <c r="F270" t="s">
         <v>151</v>
       </c>
-      <c r="H270" t="s">
+      <c r="I270" t="s">
         <v>508</v>
       </c>
       <c r="J270" t="s">
@@ -20141,7 +20161,7 @@
       <c r="F271" t="s">
         <v>151</v>
       </c>
-      <c r="H271" t="s">
+      <c r="I271" t="s">
         <v>571</v>
       </c>
       <c r="J271" t="s">
@@ -20200,7 +20220,7 @@
       <c r="F272" t="s">
         <v>572</v>
       </c>
-      <c r="H272" t="s">
+      <c r="I272" t="s">
         <v>571</v>
       </c>
       <c r="J272" t="s">
@@ -20259,7 +20279,7 @@
       <c r="F273" t="s">
         <v>573</v>
       </c>
-      <c r="H273" t="s">
+      <c r="I273" t="s">
         <v>361</v>
       </c>
       <c r="J273" t="s">
@@ -20374,7 +20394,7 @@
       <c r="F275" t="s">
         <v>575</v>
       </c>
-      <c r="H275" t="s">
+      <c r="I275" t="s">
         <v>576</v>
       </c>
       <c r="J275" t="s">
@@ -20436,7 +20456,7 @@
       <c r="F276" t="s">
         <v>578</v>
       </c>
-      <c r="H276" t="s">
+      <c r="I276" t="s">
         <v>334</v>
       </c>
       <c r="J276" t="s">
@@ -20495,7 +20515,7 @@
       <c r="F277" t="s">
         <v>579</v>
       </c>
-      <c r="H277" t="s">
+      <c r="I277" t="s">
         <v>580</v>
       </c>
       <c r="J277" t="s">
@@ -20616,7 +20636,7 @@
       <c r="F279" t="s">
         <v>151</v>
       </c>
-      <c r="H279" t="s">
+      <c r="I279" t="s">
         <v>583</v>
       </c>
       <c r="J279" t="s">
@@ -20675,7 +20695,7 @@
       <c r="F280" t="s">
         <v>348</v>
       </c>
-      <c r="H280" t="s">
+      <c r="I280" t="s">
         <v>585</v>
       </c>
       <c r="J280" t="s">
@@ -20734,7 +20754,7 @@
       <c r="F281" t="s">
         <v>573</v>
       </c>
-      <c r="H281" t="s">
+      <c r="I281" t="s">
         <v>587</v>
       </c>
       <c r="J281" t="s">
@@ -20793,7 +20813,7 @@
       <c r="F282" t="s">
         <v>350</v>
       </c>
-      <c r="H282" t="s">
+      <c r="I282" t="s">
         <v>588</v>
       </c>
       <c r="J282" t="s">
@@ -20852,7 +20872,7 @@
       <c r="F283" t="s">
         <v>579</v>
       </c>
-      <c r="H283" t="s">
+      <c r="I283" t="s">
         <v>590</v>
       </c>
       <c r="J283" t="s">
@@ -20911,7 +20931,7 @@
       <c r="F284" t="s">
         <v>591</v>
       </c>
-      <c r="H284" t="s">
+      <c r="I284" t="s">
         <v>592</v>
       </c>
       <c r="J284" t="s">
@@ -20970,7 +20990,7 @@
       <c r="F285" t="s">
         <v>299</v>
       </c>
-      <c r="H285" t="s">
+      <c r="I285" t="s">
         <v>593</v>
       </c>
       <c r="J285" t="s">
@@ -21029,7 +21049,7 @@
       <c r="F286" t="s">
         <v>595</v>
       </c>
-      <c r="H286" t="s">
+      <c r="I286" t="s">
         <v>585</v>
       </c>
       <c r="J286" t="s">
@@ -21088,7 +21108,7 @@
       <c r="F287" t="s">
         <v>348</v>
       </c>
-      <c r="H287" t="s">
+      <c r="I287" t="s">
         <v>590</v>
       </c>
       <c r="J287" t="s">
@@ -21209,7 +21229,7 @@
       <c r="G289" t="s">
         <v>429</v>
       </c>
-      <c r="H289" t="s">
+      <c r="I289" t="s">
         <v>201</v>
       </c>
       <c r="J289" t="s">
@@ -21271,7 +21291,7 @@
       <c r="F290" t="s">
         <v>203</v>
       </c>
-      <c r="H290" t="s">
+      <c r="I290" t="s">
         <v>600</v>
       </c>
       <c r="J290" t="s">
@@ -21336,7 +21356,7 @@
       <c r="G291" t="s">
         <v>343</v>
       </c>
-      <c r="H291" t="s">
+      <c r="I291" t="s">
         <v>211</v>
       </c>
       <c r="J291" t="s">
@@ -21398,7 +21418,7 @@
       <c r="F292" t="s">
         <v>212</v>
       </c>
-      <c r="H292" t="s">
+      <c r="I292" t="s">
         <v>213</v>
       </c>
       <c r="J292" t="s">
@@ -21460,7 +21480,7 @@
       <c r="F293" t="s">
         <v>214</v>
       </c>
-      <c r="H293" t="s">
+      <c r="I293" t="s">
         <v>293</v>
       </c>
       <c r="J293" t="s">
@@ -21522,7 +21542,7 @@
       <c r="F294" t="s">
         <v>602</v>
       </c>
-      <c r="H294" t="s">
+      <c r="I294" t="s">
         <v>293</v>
       </c>
       <c r="J294" t="s">
@@ -21584,7 +21604,7 @@
       <c r="F295" t="s">
         <v>603</v>
       </c>
-      <c r="H295" t="s">
+      <c r="I295" t="s">
         <v>240</v>
       </c>
       <c r="J295" t="s">
@@ -21649,7 +21669,7 @@
       <c r="F296" t="s">
         <v>604</v>
       </c>
-      <c r="H296" t="s">
+      <c r="I296" t="s">
         <v>334</v>
       </c>
       <c r="J296" t="s">
@@ -21711,7 +21731,7 @@
       <c r="F297" t="s">
         <v>605</v>
       </c>
-      <c r="H297" t="s">
+      <c r="I297" t="s">
         <v>240</v>
       </c>
       <c r="J297" t="s">
@@ -21776,7 +21796,7 @@
       <c r="F298" t="s">
         <v>606</v>
       </c>
-      <c r="H298" t="s">
+      <c r="I298" t="s">
         <v>334</v>
       </c>
       <c r="J298" t="s">
@@ -21838,7 +21858,7 @@
       <c r="F299" t="s">
         <v>607</v>
       </c>
-      <c r="H299" t="s">
+      <c r="I299" t="s">
         <v>293</v>
       </c>
       <c r="J299" t="s">
@@ -21900,7 +21920,7 @@
       <c r="F300" t="s">
         <v>608</v>
       </c>
-      <c r="H300" t="s">
+      <c r="I300" t="s">
         <v>240</v>
       </c>
       <c r="J300" t="s">
@@ -21965,7 +21985,7 @@
       <c r="F301" t="s">
         <v>609</v>
       </c>
-      <c r="H301" t="s">
+      <c r="I301" t="s">
         <v>567</v>
       </c>
       <c r="J301" t="s">
@@ -22027,7 +22047,7 @@
       <c r="F302" t="s">
         <v>227</v>
       </c>
-      <c r="H302" t="s">
+      <c r="I302" t="s">
         <v>293</v>
       </c>
       <c r="J302" t="s">
@@ -22092,7 +22112,7 @@
       <c r="G303" t="s">
         <v>612</v>
       </c>
-      <c r="H303" t="s">
+      <c r="I303" t="s">
         <v>613</v>
       </c>
       <c r="J303" t="s">
@@ -22157,7 +22177,7 @@
       <c r="F304" t="s">
         <v>253</v>
       </c>
-      <c r="H304" t="s">
+      <c r="I304" t="s">
         <v>254</v>
       </c>
       <c r="J304" t="s">
@@ -22219,7 +22239,7 @@
       <c r="F305" t="s">
         <v>616</v>
       </c>
-      <c r="H305" t="s">
+      <c r="I305" t="s">
         <v>440</v>
       </c>
       <c r="J305" t="s">
@@ -22281,7 +22301,7 @@
       <c r="F306" t="s">
         <v>617</v>
       </c>
-      <c r="H306" t="s">
+      <c r="I306" t="s">
         <v>618</v>
       </c>
       <c r="J306" t="s">
@@ -22343,7 +22363,7 @@
       <c r="F307" t="s">
         <v>619</v>
       </c>
-      <c r="H307" t="s">
+      <c r="I307" t="s">
         <v>620</v>
       </c>
       <c r="J307" t="s">
@@ -22405,7 +22425,7 @@
       <c r="F308" t="s">
         <v>255</v>
       </c>
-      <c r="H308" t="s">
+      <c r="I308" t="s">
         <v>621</v>
       </c>
       <c r="J308" t="s">
@@ -22467,7 +22487,7 @@
       <c r="F309" t="s">
         <v>622</v>
       </c>
-      <c r="H309" t="s">
+      <c r="I309" t="s">
         <v>623</v>
       </c>
       <c r="J309" t="s">
@@ -22529,7 +22549,7 @@
       <c r="F310" t="s">
         <v>264</v>
       </c>
-      <c r="H310" t="s">
+      <c r="I310" t="s">
         <v>624</v>
       </c>
       <c r="J310" t="s">
@@ -22591,7 +22611,7 @@
       <c r="F311" t="s">
         <v>263</v>
       </c>
-      <c r="H311" t="s">
+      <c r="I311" t="s">
         <v>262</v>
       </c>
       <c r="J311" t="s">
@@ -22653,7 +22673,7 @@
       <c r="F312" t="s">
         <v>261</v>
       </c>
-      <c r="H312" t="s">
+      <c r="I312" t="s">
         <v>625</v>
       </c>
       <c r="J312" t="s">
@@ -22715,7 +22735,7 @@
       <c r="F313" t="s">
         <v>626</v>
       </c>
-      <c r="H313" t="s">
+      <c r="I313" t="s">
         <v>340</v>
       </c>
       <c r="J313" t="s">
@@ -22780,7 +22800,7 @@
       <c r="F314" t="s">
         <v>627</v>
       </c>
-      <c r="H314" t="s">
+      <c r="I314" t="s">
         <v>628</v>
       </c>
       <c r="J314" t="s">
@@ -22845,7 +22865,7 @@
       <c r="F315" t="s">
         <v>629</v>
       </c>
-      <c r="H315" t="s">
+      <c r="I315" t="s">
         <v>630</v>
       </c>
       <c r="J315" t="s">
@@ -22910,7 +22930,7 @@
       <c r="F316" t="s">
         <v>631</v>
       </c>
-      <c r="H316" t="s">
+      <c r="I316" t="s">
         <v>340</v>
       </c>
       <c r="J316" t="s">
@@ -22975,7 +22995,7 @@
       <c r="F317" t="s">
         <v>632</v>
       </c>
-      <c r="H317" t="s">
+      <c r="I317" t="s">
         <v>583</v>
       </c>
       <c r="J317" t="s">
@@ -23037,7 +23057,7 @@
       <c r="F318" t="s">
         <v>633</v>
       </c>
-      <c r="H318" t="s">
+      <c r="I318" t="s">
         <v>634</v>
       </c>
       <c r="J318" t="s">
@@ -23102,7 +23122,7 @@
       <c r="G319" t="s">
         <v>321</v>
       </c>
-      <c r="H319" t="s">
+      <c r="I319" t="s">
         <v>637</v>
       </c>
       <c r="J319" t="s">
@@ -23164,7 +23184,7 @@
       <c r="F320" t="s">
         <v>294</v>
       </c>
-      <c r="H320" t="s">
+      <c r="I320" t="s">
         <v>637</v>
       </c>
       <c r="J320" t="s">
@@ -23226,7 +23246,7 @@
       <c r="F321" t="s">
         <v>299</v>
       </c>
-      <c r="H321" t="s">
+      <c r="I321" t="s">
         <v>638</v>
       </c>
       <c r="J321" t="s">
@@ -23291,7 +23311,7 @@
       <c r="G322" t="s">
         <v>223</v>
       </c>
-      <c r="H322" t="s">
+      <c r="I322" t="s">
         <v>508</v>
       </c>
       <c r="J322" t="s">
@@ -23353,7 +23373,7 @@
       <c r="F323" t="s">
         <v>294</v>
       </c>
-      <c r="H323" t="s">
+      <c r="I323" t="s">
         <v>508</v>
       </c>
       <c r="J323" t="s">
@@ -23418,7 +23438,7 @@
       <c r="G324" t="s">
         <v>321</v>
       </c>
-      <c r="H324" t="s">
+      <c r="I324" t="s">
         <v>637</v>
       </c>
       <c r="J324" t="s">
@@ -23480,7 +23500,7 @@
       <c r="F325" t="s">
         <v>294</v>
       </c>
-      <c r="H325" t="s">
+      <c r="I325" t="s">
         <v>637</v>
       </c>
       <c r="J325" t="s">
@@ -23542,7 +23562,7 @@
       <c r="F326" t="s">
         <v>299</v>
       </c>
-      <c r="H326" t="s">
+      <c r="I326" t="s">
         <v>587</v>
       </c>
       <c r="J326" t="s">
@@ -23607,7 +23627,7 @@
       <c r="G327" t="s">
         <v>321</v>
       </c>
-      <c r="H327" t="s">
+      <c r="I327" t="s">
         <v>334</v>
       </c>
       <c r="J327" t="s">
@@ -23672,7 +23692,7 @@
       <c r="F328" t="s">
         <v>294</v>
       </c>
-      <c r="H328" t="s">
+      <c r="I328" t="s">
         <v>334</v>
       </c>
       <c r="J328" t="s">
@@ -23734,7 +23754,7 @@
       <c r="F329" t="s">
         <v>299</v>
       </c>
-      <c r="H329" t="s">
+      <c r="I329" t="s">
         <v>593</v>
       </c>
       <c r="J329" t="s">
@@ -23799,7 +23819,7 @@
       <c r="G330" t="s">
         <v>321</v>
       </c>
-      <c r="H330" t="s">
+      <c r="I330" t="s">
         <v>334</v>
       </c>
       <c r="J330" t="s">
@@ -23864,7 +23884,7 @@
       <c r="G331" t="s">
         <v>223</v>
       </c>
-      <c r="H331" t="s">
+      <c r="I331" t="s">
         <v>508</v>
       </c>
       <c r="J331" t="s">
@@ -23926,7 +23946,7 @@
       <c r="F332" t="s">
         <v>55</v>
       </c>
-      <c r="H332" t="s">
+      <c r="I332" t="s">
         <v>301</v>
       </c>
       <c r="J332" t="s">
@@ -23988,7 +24008,7 @@
       <c r="F333" t="s">
         <v>645</v>
       </c>
-      <c r="H333" t="s">
+      <c r="I333" t="s">
         <v>646</v>
       </c>
       <c r="J333" t="s">
@@ -24050,7 +24070,7 @@
       <c r="F334" t="s">
         <v>648</v>
       </c>
-      <c r="H334" t="s">
+      <c r="I334" t="s">
         <v>649</v>
       </c>
       <c r="J334" t="s">
@@ -24115,7 +24135,7 @@
       <c r="F335" t="s">
         <v>652</v>
       </c>
-      <c r="H335" t="s">
+      <c r="I335" t="s">
         <v>653</v>
       </c>
       <c r="J335" t="s">
@@ -24180,7 +24200,7 @@
       <c r="G336" t="s">
         <v>321</v>
       </c>
-      <c r="H336" t="s">
+      <c r="I336" t="s">
         <v>637</v>
       </c>
       <c r="J336" t="s">
@@ -24242,7 +24262,7 @@
       <c r="F337" t="s">
         <v>294</v>
       </c>
-      <c r="H337" t="s">
+      <c r="I337" t="s">
         <v>637</v>
       </c>
       <c r="J337" t="s">
@@ -24304,7 +24324,7 @@
       <c r="F338" t="s">
         <v>299</v>
       </c>
-      <c r="H338" t="s">
+      <c r="I338" t="s">
         <v>638</v>
       </c>
       <c r="J338" t="s">
@@ -24369,7 +24389,7 @@
       <c r="G339" t="s">
         <v>206</v>
       </c>
-      <c r="H339" t="s">
+      <c r="I339" t="s">
         <v>657</v>
       </c>
       <c r="J339" t="s">
@@ -24431,7 +24451,7 @@
       <c r="F340" t="s">
         <v>294</v>
       </c>
-      <c r="H340" t="s">
+      <c r="I340" t="s">
         <v>334</v>
       </c>
       <c r="J340" t="s">
@@ -24493,7 +24513,7 @@
       <c r="F341" t="s">
         <v>299</v>
       </c>
-      <c r="H341" t="s">
+      <c r="I341" t="s">
         <v>384</v>
       </c>
       <c r="J341" t="s">
@@ -24558,7 +24578,7 @@
       <c r="G342" t="s">
         <v>223</v>
       </c>
-      <c r="H342" t="s">
+      <c r="I342" t="s">
         <v>658</v>
       </c>
       <c r="J342" t="s">
@@ -24620,7 +24640,7 @@
       <c r="F343" t="s">
         <v>294</v>
       </c>
-      <c r="H343" t="s">
+      <c r="I343" t="s">
         <v>659</v>
       </c>
       <c r="J343" t="s">
@@ -24682,7 +24702,7 @@
       <c r="F344" t="s">
         <v>299</v>
       </c>
-      <c r="H344" t="s">
+      <c r="I344" t="s">
         <v>660</v>
       </c>
       <c r="J344" t="s">
@@ -24747,7 +24767,7 @@
       <c r="G345" t="s">
         <v>223</v>
       </c>
-      <c r="H345" t="s">
+      <c r="I345" t="s">
         <v>508</v>
       </c>
       <c r="J345" t="s">
@@ -24809,7 +24829,7 @@
       <c r="F346" t="s">
         <v>294</v>
       </c>
-      <c r="H346" t="s">
+      <c r="I346" t="s">
         <v>508</v>
       </c>
       <c r="J346" t="s">
@@ -24871,7 +24891,7 @@
       <c r="F347" t="s">
         <v>299</v>
       </c>
-      <c r="H347" t="s">
+      <c r="I347" t="s">
         <v>567</v>
       </c>
       <c r="J347" t="s">
@@ -24936,7 +24956,7 @@
       <c r="G348" t="s">
         <v>206</v>
       </c>
-      <c r="H348" t="s">
+      <c r="I348" t="s">
         <v>664</v>
       </c>
       <c r="J348" t="s">
@@ -25001,7 +25021,7 @@
       <c r="G349" t="s">
         <v>223</v>
       </c>
-      <c r="H349" t="s">
+      <c r="I349" t="s">
         <v>544</v>
       </c>
       <c r="J349" t="s">
@@ -25066,7 +25086,7 @@
       <c r="G350" t="s">
         <v>223</v>
       </c>
-      <c r="H350" t="s">
+      <c r="I350" t="s">
         <v>668</v>
       </c>
       <c r="J350" t="s">
@@ -25131,7 +25151,7 @@
       <c r="G351" t="s">
         <v>223</v>
       </c>
-      <c r="H351" t="s">
+      <c r="I351" t="s">
         <v>671</v>
       </c>
       <c r="J351" t="s">
@@ -25193,7 +25213,7 @@
       <c r="F352" t="s">
         <v>55</v>
       </c>
-      <c r="H352" t="s">
+      <c r="I352" t="s">
         <v>314</v>
       </c>
       <c r="J352" t="s">
@@ -25258,7 +25278,7 @@
       <c r="F353" t="s">
         <v>672</v>
       </c>
-      <c r="H353" t="s">
+      <c r="I353" t="s">
         <v>649</v>
       </c>
       <c r="J353" t="s">
@@ -25320,7 +25340,7 @@
       <c r="F354" t="s">
         <v>673</v>
       </c>
-      <c r="H354" t="s">
+      <c r="I354" t="s">
         <v>649</v>
       </c>
       <c r="J354" t="s">
@@ -25382,7 +25402,7 @@
       <c r="F355" t="s">
         <v>674</v>
       </c>
-      <c r="H355" t="s">
+      <c r="I355" t="s">
         <v>628</v>
       </c>
       <c r="J355" t="s">
@@ -25450,7 +25470,7 @@
       <c r="G356" t="s">
         <v>677</v>
       </c>
-      <c r="H356" t="s">
+      <c r="I356" t="s">
         <v>576</v>
       </c>
       <c r="J356" t="s">
@@ -25512,7 +25532,7 @@
       <c r="F357" t="s">
         <v>294</v>
       </c>
-      <c r="H357" t="s">
+      <c r="I357" t="s">
         <v>576</v>
       </c>
       <c r="J357" t="s">
@@ -25574,7 +25594,7 @@
       <c r="F358" t="s">
         <v>299</v>
       </c>
-      <c r="H358" t="s">
+      <c r="I358" t="s">
         <v>361</v>
       </c>
       <c r="J358" t="s">
@@ -25639,7 +25659,7 @@
       <c r="G359" t="s">
         <v>206</v>
       </c>
-      <c r="H359" t="s">
+      <c r="I359" t="s">
         <v>637</v>
       </c>
       <c r="J359" t="s">
@@ -25701,7 +25721,7 @@
       <c r="F360" t="s">
         <v>294</v>
       </c>
-      <c r="H360" t="s">
+      <c r="I360" t="s">
         <v>637</v>
       </c>
       <c r="J360" t="s">
@@ -25766,7 +25786,7 @@
       <c r="G361" t="s">
         <v>206</v>
       </c>
-      <c r="H361" t="s">
+      <c r="I361" t="s">
         <v>334</v>
       </c>
       <c r="J361" t="s">
@@ -25828,7 +25848,7 @@
       <c r="F362" t="s">
         <v>294</v>
       </c>
-      <c r="H362" t="s">
+      <c r="I362" t="s">
         <v>334</v>
       </c>
       <c r="J362" t="s">
@@ -25893,7 +25913,7 @@
       <c r="G363" t="s">
         <v>206</v>
       </c>
-      <c r="H363" t="s">
+      <c r="I363" t="s">
         <v>508</v>
       </c>
       <c r="J363" t="s">
@@ -25955,7 +25975,7 @@
       <c r="F364" t="s">
         <v>294</v>
       </c>
-      <c r="H364" t="s">
+      <c r="I364" t="s">
         <v>334</v>
       </c>
       <c r="J364" t="s">
@@ -26020,7 +26040,7 @@
       <c r="G365" t="s">
         <v>223</v>
       </c>
-      <c r="H365" t="s">
+      <c r="I365" t="s">
         <v>508</v>
       </c>
       <c r="J365" t="s">
@@ -26082,7 +26102,7 @@
       <c r="F366" t="s">
         <v>294</v>
       </c>
-      <c r="H366" t="s">
+      <c r="I366" t="s">
         <v>508</v>
       </c>
       <c r="J366" t="s">
@@ -26144,7 +26164,7 @@
       <c r="F367" t="s">
         <v>299</v>
       </c>
-      <c r="H367" t="s">
+      <c r="I367" t="s">
         <v>567</v>
       </c>
       <c r="J367" t="s">
@@ -26209,7 +26229,7 @@
       <c r="G368" t="s">
         <v>223</v>
       </c>
-      <c r="H368" t="s">
+      <c r="I368" t="s">
         <v>334</v>
       </c>
       <c r="J368" t="s">
@@ -26271,7 +26291,7 @@
       <c r="F369" t="s">
         <v>294</v>
       </c>
-      <c r="H369" t="s">
+      <c r="I369" t="s">
         <v>334</v>
       </c>
       <c r="J369" t="s">
@@ -26336,7 +26356,7 @@
       <c r="G370" t="s">
         <v>223</v>
       </c>
-      <c r="H370" t="s">
+      <c r="I370" t="s">
         <v>508</v>
       </c>
       <c r="J370" t="s">
@@ -26398,7 +26418,7 @@
       <c r="F371" t="s">
         <v>294</v>
       </c>
-      <c r="H371" t="s">
+      <c r="I371" t="s">
         <v>508</v>
       </c>
       <c r="J371" t="s">
@@ -26460,7 +26480,7 @@
       <c r="F372" t="s">
         <v>645</v>
       </c>
-      <c r="H372" t="s">
+      <c r="I372" t="s">
         <v>646</v>
       </c>
       <c r="J372" t="s">
@@ -26522,7 +26542,7 @@
       <c r="F373" t="s">
         <v>684</v>
       </c>
-      <c r="H373" t="s">
+      <c r="I373" t="s">
         <v>671</v>
       </c>
       <c r="J373" t="s">
@@ -26584,7 +26604,7 @@
       <c r="F374" t="s">
         <v>685</v>
       </c>
-      <c r="H374" t="s">
+      <c r="I374" t="s">
         <v>686</v>
       </c>
       <c r="J374" t="s">
@@ -26646,7 +26666,7 @@
       <c r="F375" t="s">
         <v>55</v>
       </c>
-      <c r="H375" t="s">
+      <c r="I375" t="s">
         <v>314</v>
       </c>
       <c r="J375" t="s">
@@ -26711,7 +26731,7 @@
       <c r="F376" t="s">
         <v>648</v>
       </c>
-      <c r="H376" t="s">
+      <c r="I376" t="s">
         <v>533</v>
       </c>
       <c r="J376" t="s">
@@ -26776,7 +26796,7 @@
       <c r="G377" t="s">
         <v>206</v>
       </c>
-      <c r="H377" t="s">
+      <c r="I377" t="s">
         <v>334</v>
       </c>
       <c r="J377" t="s">
@@ -26838,7 +26858,7 @@
       <c r="F378" t="s">
         <v>299</v>
       </c>
-      <c r="H378" t="s">
+      <c r="I378" t="s">
         <v>384</v>
       </c>
       <c r="J378" t="s">
@@ -26903,7 +26923,7 @@
       <c r="G379" t="s">
         <v>206</v>
       </c>
-      <c r="H379" t="s">
+      <c r="I379" t="s">
         <v>689</v>
       </c>
       <c r="J379" t="s">
@@ -26968,7 +26988,7 @@
       <c r="F380" t="s">
         <v>299</v>
       </c>
-      <c r="H380" t="s">
+      <c r="I380" t="s">
         <v>689</v>
       </c>
       <c r="J380" t="s">
@@ -27036,7 +27056,7 @@
       <c r="G381" t="s">
         <v>206</v>
       </c>
-      <c r="H381" t="s">
+      <c r="I381" t="s">
         <v>657</v>
       </c>
       <c r="J381" t="s">
@@ -27101,7 +27121,7 @@
       <c r="F382" t="s">
         <v>294</v>
       </c>
-      <c r="H382" t="s">
+      <c r="I382" t="s">
         <v>576</v>
       </c>
       <c r="J382" t="s">
@@ -27166,7 +27186,7 @@
       <c r="F383" t="s">
         <v>299</v>
       </c>
-      <c r="H383" t="s">
+      <c r="I383" t="s">
         <v>587</v>
       </c>
       <c r="J383" t="s">
@@ -27231,7 +27251,7 @@
       <c r="G384" t="s">
         <v>206</v>
       </c>
-      <c r="H384" t="s">
+      <c r="I384" t="s">
         <v>334</v>
       </c>
       <c r="J384" t="s">
@@ -27293,7 +27313,7 @@
       <c r="F385" t="s">
         <v>299</v>
       </c>
-      <c r="H385" t="s">
+      <c r="I385" t="s">
         <v>384</v>
       </c>
       <c r="J385" t="s">
@@ -27355,7 +27375,7 @@
       <c r="F386" t="s">
         <v>645</v>
       </c>
-      <c r="H386" t="s">
+      <c r="I386" t="s">
         <v>692</v>
       </c>
       <c r="J386" t="s">
@@ -27417,7 +27437,7 @@
       <c r="F387" t="s">
         <v>693</v>
       </c>
-      <c r="H387" t="s">
+      <c r="I387" t="s">
         <v>694</v>
       </c>
       <c r="J387" t="s">
@@ -27482,7 +27502,7 @@
       <c r="F388" t="s">
         <v>696</v>
       </c>
-      <c r="H388" t="s">
+      <c r="I388" t="s">
         <v>314</v>
       </c>
       <c r="J388" t="s">
@@ -27547,7 +27567,7 @@
       <c r="F389" t="s">
         <v>698</v>
       </c>
-      <c r="H389" t="s">
+      <c r="I389" t="s">
         <v>630</v>
       </c>
       <c r="J389" t="s">
@@ -27612,7 +27632,7 @@
       <c r="G390" t="s">
         <v>702</v>
       </c>
-      <c r="H390" t="s">
+      <c r="I390" t="s">
         <v>703</v>
       </c>
       <c r="J390" t="s">
@@ -27677,7 +27697,7 @@
       <c r="F391" t="s">
         <v>31</v>
       </c>
-      <c r="H391" t="s">
+      <c r="I391" t="s">
         <v>706</v>
       </c>
       <c r="J391" t="s">
@@ -27739,7 +27759,7 @@
       <c r="F392" t="s">
         <v>707</v>
       </c>
-      <c r="H392" t="s">
+      <c r="I392" t="s">
         <v>708</v>
       </c>
       <c r="J392" t="s">
@@ -27801,7 +27821,7 @@
       <c r="F393" t="s">
         <v>299</v>
       </c>
-      <c r="H393" t="s">
+      <c r="I393" t="s">
         <v>709</v>
       </c>
       <c r="J393" t="s">
@@ -27863,7 +27883,7 @@
       <c r="F394" t="s">
         <v>711</v>
       </c>
-      <c r="H394" t="s">
+      <c r="I394" t="s">
         <v>712</v>
       </c>
       <c r="J394" t="s">
@@ -27925,7 +27945,7 @@
       <c r="F395" t="s">
         <v>714</v>
       </c>
-      <c r="H395" t="s">
+      <c r="I395" t="s">
         <v>715</v>
       </c>
       <c r="J395" t="s">
@@ -27987,7 +28007,7 @@
       <c r="F396" t="s">
         <v>242</v>
       </c>
-      <c r="H396" t="s">
+      <c r="I396" t="s">
         <v>716</v>
       </c>
       <c r="J396" t="s">
@@ -28052,7 +28072,7 @@
       <c r="G397" t="s">
         <v>719</v>
       </c>
-      <c r="H397" t="s">
+      <c r="I397" t="s">
         <v>720</v>
       </c>
       <c r="J397" t="s">
@@ -28117,7 +28137,7 @@
       <c r="F398" t="s">
         <v>723</v>
       </c>
-      <c r="H398" t="s">
+      <c r="I398" t="s">
         <v>724</v>
       </c>
       <c r="J398" t="s">
@@ -28179,7 +28199,7 @@
       <c r="F399" t="s">
         <v>725</v>
       </c>
-      <c r="H399" t="s">
+      <c r="I399" t="s">
         <v>726</v>
       </c>
       <c r="J399" t="s">
@@ -28241,7 +28261,7 @@
       <c r="F400" t="s">
         <v>727</v>
       </c>
-      <c r="H400" t="s">
+      <c r="I400" t="s">
         <v>728</v>
       </c>
       <c r="J400" t="s">
@@ -28303,7 +28323,7 @@
       <c r="F401" t="s">
         <v>729</v>
       </c>
-      <c r="H401" t="s">
+      <c r="I401" t="s">
         <v>730</v>
       </c>
       <c r="J401" t="s">
@@ -28368,7 +28388,7 @@
       <c r="G402" t="s">
         <v>732</v>
       </c>
-      <c r="H402" t="s">
+      <c r="I402" t="s">
         <v>733</v>
       </c>
       <c r="J402" t="s">
@@ -28433,7 +28453,7 @@
       <c r="F403" t="s">
         <v>299</v>
       </c>
-      <c r="H403" t="s">
+      <c r="I403" t="s">
         <v>736</v>
       </c>
       <c r="J403" t="s">
@@ -28675,7 +28695,7 @@
       <c r="G407" t="s">
         <v>741</v>
       </c>
-      <c r="H407" t="s">
+      <c r="I407" t="s">
         <v>742</v>
       </c>
       <c r="J407" t="s">
@@ -28740,7 +28760,7 @@
       <c r="F408" t="s">
         <v>745</v>
       </c>
-      <c r="H408" t="s">
+      <c r="I408" t="s">
         <v>746</v>
       </c>
       <c r="J408" t="s">
@@ -28802,7 +28822,7 @@
       <c r="F409" t="s">
         <v>747</v>
       </c>
-      <c r="H409" t="s">
+      <c r="I409" t="s">
         <v>748</v>
       </c>
       <c r="J409" t="s">
@@ -28867,7 +28887,7 @@
       <c r="G410" t="s">
         <v>677</v>
       </c>
-      <c r="H410" t="s">
+      <c r="I410" t="s">
         <v>751</v>
       </c>
       <c r="J410" t="s">
@@ -28932,7 +28952,7 @@
       <c r="F411" t="s">
         <v>299</v>
       </c>
-      <c r="H411" t="s">
+      <c r="I411" t="s">
         <v>753</v>
       </c>
       <c r="J411" t="s">
@@ -28997,7 +29017,7 @@
       <c r="G412" t="s">
         <v>755</v>
       </c>
-      <c r="H412" t="s">
+      <c r="I412" t="s">
         <v>756</v>
       </c>
       <c r="J412" t="s">
@@ -29062,7 +29082,7 @@
       <c r="F413" t="s">
         <v>759</v>
       </c>
-      <c r="H413" t="s">
+      <c r="I413" t="s">
         <v>760</v>
       </c>
       <c r="J413" t="s">
@@ -29127,7 +29147,7 @@
       <c r="G414" t="s">
         <v>762</v>
       </c>
-      <c r="H414" t="s">
+      <c r="I414" t="s">
         <v>763</v>
       </c>
       <c r="J414" t="s">
@@ -29192,7 +29212,7 @@
       <c r="F415" t="s">
         <v>766</v>
       </c>
-      <c r="H415" t="s">
+      <c r="I415" t="s">
         <v>767</v>
       </c>
       <c r="J415" t="s">
@@ -29254,7 +29274,7 @@
       <c r="F416" t="s">
         <v>768</v>
       </c>
-      <c r="H416" t="s">
+      <c r="I416" t="s">
         <v>769</v>
       </c>
       <c r="J416" t="s">
@@ -29316,7 +29336,7 @@
       <c r="F417" t="s">
         <v>242</v>
       </c>
-      <c r="H417" t="s">
+      <c r="I417" t="s">
         <v>770</v>
       </c>
       <c r="J417" t="s">
@@ -29378,7 +29398,7 @@
       <c r="F418" t="s">
         <v>771</v>
       </c>
-      <c r="H418" t="s">
+      <c r="I418" t="s">
         <v>772</v>
       </c>
       <c r="J418" t="s">
@@ -29440,7 +29460,7 @@
       <c r="F419" t="s">
         <v>773</v>
       </c>
-      <c r="H419" t="s">
+      <c r="I419" t="s">
         <v>774</v>
       </c>
       <c r="J419" t="s">
@@ -29505,7 +29525,7 @@
       <c r="F420" t="s">
         <v>776</v>
       </c>
-      <c r="H420" t="s">
+      <c r="I420" t="s">
         <v>777</v>
       </c>
       <c r="J420" t="s">
@@ -29570,7 +29590,7 @@
       <c r="G421" t="s">
         <v>779</v>
       </c>
-      <c r="H421" t="s">
+      <c r="I421" t="s">
         <v>742</v>
       </c>
       <c r="J421" t="s">
@@ -29635,7 +29655,7 @@
       <c r="F422" t="s">
         <v>781</v>
       </c>
-      <c r="H422" t="s">
+      <c r="I422" t="s">
         <v>782</v>
       </c>
       <c r="J422" t="s">
@@ -29697,7 +29717,7 @@
       <c r="F423" t="s">
         <v>783</v>
       </c>
-      <c r="H423" t="s">
+      <c r="I423" t="s">
         <v>784</v>
       </c>
       <c r="J423" t="s">
@@ -29762,7 +29782,7 @@
       <c r="F424" t="s">
         <v>785</v>
       </c>
-      <c r="H424" t="s">
+      <c r="I424" t="s">
         <v>786</v>
       </c>
       <c r="J424" t="s">
@@ -29824,7 +29844,7 @@
       <c r="F425" t="s">
         <v>787</v>
       </c>
-      <c r="H425" t="s">
+      <c r="I425" t="s">
         <v>788</v>
       </c>
       <c r="J425" t="s">
@@ -29886,7 +29906,7 @@
       <c r="F426" t="s">
         <v>789</v>
       </c>
-      <c r="H426" t="s">
+      <c r="I426" t="s">
         <v>790</v>
       </c>
       <c r="J426" t="s">
@@ -29948,7 +29968,7 @@
       <c r="F427" t="s">
         <v>791</v>
       </c>
-      <c r="H427" t="s">
+      <c r="I427" t="s">
         <v>792</v>
       </c>
       <c r="J427" t="s">
@@ -30010,7 +30030,7 @@
       <c r="F428" t="s">
         <v>793</v>
       </c>
-      <c r="H428" t="s">
+      <c r="I428" t="s">
         <v>794</v>
       </c>
       <c r="J428" t="s">
@@ -30075,7 +30095,7 @@
       <c r="F429" t="s">
         <v>797</v>
       </c>
-      <c r="H429" t="s">
+      <c r="I429" t="s">
         <v>798</v>
       </c>
       <c r="J429" t="s">
@@ -30143,7 +30163,7 @@
       <c r="G430" t="s">
         <v>802</v>
       </c>
-      <c r="H430" t="s">
+      <c r="I430" t="s">
         <v>803</v>
       </c>
       <c r="J430" t="s">
@@ -30208,7 +30228,7 @@
       <c r="F431" t="s">
         <v>781</v>
       </c>
-      <c r="H431" t="s">
+      <c r="I431" t="s">
         <v>806</v>
       </c>
       <c r="J431" t="s">
@@ -30270,7 +30290,7 @@
       <c r="F432" t="s">
         <v>807</v>
       </c>
-      <c r="H432" t="s">
+      <c r="I432" t="s">
         <v>808</v>
       </c>
       <c r="J432" t="s">
@@ -30335,7 +30355,7 @@
       <c r="F433" t="s">
         <v>810</v>
       </c>
-      <c r="H433" t="s">
+      <c r="I433" t="s">
         <v>811</v>
       </c>
       <c r="J433" t="s">
@@ -30397,7 +30417,7 @@
       <c r="F434" t="s">
         <v>739</v>
       </c>
-      <c r="H434" t="s">
+      <c r="I434" t="s">
         <v>813</v>
       </c>
       <c r="J434" t="s">
@@ -30459,7 +30479,7 @@
       <c r="F435" t="s">
         <v>814</v>
       </c>
-      <c r="H435" t="s">
+      <c r="I435" t="s">
         <v>815</v>
       </c>
       <c r="J435" t="s">
@@ -30521,7 +30541,7 @@
       <c r="F436" t="s">
         <v>242</v>
       </c>
-      <c r="H436" t="s">
+      <c r="I436" t="s">
         <v>817</v>
       </c>
       <c r="J436" t="s">
@@ -30583,7 +30603,7 @@
       <c r="F437" t="s">
         <v>718</v>
       </c>
-      <c r="H437" t="s">
+      <c r="I437" t="s">
         <v>819</v>
       </c>
       <c r="J437" t="s">
@@ -30645,7 +30665,7 @@
       <c r="F438" t="s">
         <v>820</v>
       </c>
-      <c r="H438" t="s">
+      <c r="I438" t="s">
         <v>821</v>
       </c>
       <c r="J438" t="s">
@@ -30707,7 +30727,7 @@
       <c r="F439" t="s">
         <v>754</v>
       </c>
-      <c r="H439" t="s">
+      <c r="I439" t="s">
         <v>823</v>
       </c>
       <c r="J439" t="s">
@@ -30772,7 +30792,7 @@
       <c r="F440" t="s">
         <v>299</v>
       </c>
-      <c r="H440" t="s">
+      <c r="I440" t="s">
         <v>826</v>
       </c>
       <c r="J440" t="s">
@@ -30837,7 +30857,7 @@
       <c r="F441" t="s">
         <v>55</v>
       </c>
-      <c r="H441" t="s">
+      <c r="I441" t="s">
         <v>828</v>
       </c>
       <c r="J441" t="s">
@@ -30899,7 +30919,7 @@
       <c r="F442" t="s">
         <v>242</v>
       </c>
-      <c r="H442" t="s">
+      <c r="I442" t="s">
         <v>770</v>
       </c>
       <c r="J442" t="s">
@@ -30961,7 +30981,7 @@
       <c r="F443" t="s">
         <v>830</v>
       </c>
-      <c r="H443" t="s">
+      <c r="I443" t="s">
         <v>831</v>
       </c>
       <c r="J443" t="s">
@@ -31023,7 +31043,7 @@
       <c r="F444" t="s">
         <v>55</v>
       </c>
-      <c r="H444" t="s">
+      <c r="I444" t="s">
         <v>833</v>
       </c>
       <c r="J444" t="s">
@@ -31085,7 +31105,7 @@
       <c r="F445" t="s">
         <v>836</v>
       </c>
-      <c r="H445" t="s">
+      <c r="I445" t="s">
         <v>837</v>
       </c>
       <c r="J445" t="s">
@@ -31150,7 +31170,7 @@
       <c r="F446" t="s">
         <v>841</v>
       </c>
-      <c r="H446" t="s">
+      <c r="I446" t="s">
         <v>842</v>
       </c>
       <c r="J446" t="s">
@@ -31212,7 +31232,7 @@
       <c r="F447" t="s">
         <v>843</v>
       </c>
-      <c r="H447" t="s">
+      <c r="I447" t="s">
         <v>833</v>
       </c>
       <c r="J447" t="s">
@@ -31277,7 +31297,7 @@
       <c r="F448" t="s">
         <v>55</v>
       </c>
-      <c r="H448" t="s">
+      <c r="I448" t="s">
         <v>846</v>
       </c>
       <c r="J448" t="s">
@@ -31339,7 +31359,7 @@
       <c r="F449" t="s">
         <v>847</v>
       </c>
-      <c r="H449" t="s">
+      <c r="I449" t="s">
         <v>848</v>
       </c>
       <c r="J449" t="s">
@@ -31401,7 +31421,7 @@
       <c r="F450" t="s">
         <v>242</v>
       </c>
-      <c r="H450" t="s">
+      <c r="I450" t="s">
         <v>850</v>
       </c>
       <c r="J450" t="s">
@@ -31445,7 +31465,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W450" xr:uid="{80233CC7-9F29-4521-9F43-292ADE3B342B}">
+  <autoFilter ref="A1:X450" xr:uid="{80233CC7-9F29-4521-9F43-292ADE3B342B}">
     <filterColumn colId="1">
       <filters>
         <filter val="Open End"/>
@@ -31459,10 +31479,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D549529-A98F-4A5A-AF79-6F36A9D03A7C}">
-  <dimension ref="A1:W92"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="7.47265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.3125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.20703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5234375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.05078125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="84.89453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26171875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.62890625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7890625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.3671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.62890625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.05078125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.26171875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.3125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.26171875" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.20703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="45.05078125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.9453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.5234375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17.89453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -31484,11 +31529,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>851</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -31532,8 +31577,11 @@
       <c r="W1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+      <c r="X1" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -31552,8 +31600,8 @@
       <c r="F2" t="s">
         <v>31</v>
       </c>
-      <c r="H2" t="s">
-        <v>852</v>
+      <c r="I2" t="s">
+        <v>851</v>
       </c>
       <c r="J2" t="s">
         <v>312</v>
@@ -31595,7 +31643,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -31614,10 +31662,10 @@
       <c r="F3" t="s">
         <v>31</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>7</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>33</v>
       </c>
       <c r="J3" t="s">
@@ -31663,7 +31711,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -31682,10 +31730,10 @@
       <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>49</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>37</v>
       </c>
       <c r="J4" t="s">
@@ -31731,7 +31779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -31753,7 +31801,7 @@
       <c r="G5">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>41</v>
       </c>
       <c r="J5" t="s">
@@ -31799,7 +31847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -31818,14 +31866,14 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>15</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -31867,7 +31915,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -31889,7 +31937,7 @@
       <c r="G7">
         <v>8</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>48</v>
       </c>
       <c r="J7" t="s">
@@ -31935,7 +31983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -31955,7 +32003,7 @@
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -31991,7 +32039,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -32013,7 +32061,7 @@
       <c r="G9">
         <v>8</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>53</v>
       </c>
       <c r="J9" t="s">
@@ -32059,7 +32107,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -32078,11 +32126,11 @@
       <c r="F10" t="s">
         <v>50</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>301</v>
       </c>
       <c r="J10" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -32118,7 +32166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -32137,8 +32185,8 @@
       <c r="F11" t="s">
         <v>55</v>
       </c>
-      <c r="H11" t="s">
-        <v>864</v>
+      <c r="I11" t="s">
+        <v>863</v>
       </c>
       <c r="J11" t="s">
         <v>232</v>
@@ -32180,7 +32228,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -32239,7 +32287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -32261,11 +32309,11 @@
       <c r="G13">
         <v>24</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="K13">
         <v>36</v>
@@ -32307,7 +32355,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -32326,11 +32374,11 @@
       <c r="F14" t="s">
         <v>63</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -32369,7 +32417,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -32388,11 +32436,11 @@
       <c r="F15" t="s">
         <v>65</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -32431,7 +32479,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -32450,11 +32498,11 @@
       <c r="F16" t="s">
         <v>68</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -32512,11 +32560,11 @@
       <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K17">
         <v>12</v>
@@ -32574,11 +32622,11 @@
       <c r="F18" t="s">
         <v>72</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -32636,11 +32684,11 @@
       <c r="F19" t="s">
         <v>75</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>76</v>
       </c>
       <c r="J19" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -32698,11 +32746,11 @@
       <c r="F20" t="s">
         <v>77</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -32760,11 +32808,11 @@
       <c r="F21" t="s">
         <v>19</v>
       </c>
-      <c r="H21" t="s">
+      <c r="I21" t="s">
         <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -32822,11 +32870,11 @@
       <c r="F22" t="s">
         <v>55</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
         <v>80</v>
       </c>
       <c r="J22" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -32887,11 +32935,11 @@
       <c r="G23">
         <v>39</v>
       </c>
-      <c r="H23" t="s">
+      <c r="I23" t="s">
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K23">
         <v>54</v>
@@ -32952,11 +33000,11 @@
       <c r="F24" t="s">
         <v>70</v>
       </c>
-      <c r="H24" t="s">
+      <c r="I24" t="s">
         <v>84</v>
       </c>
       <c r="J24" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -33014,11 +33062,11 @@
       <c r="F25" t="s">
         <v>85</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -33076,11 +33124,11 @@
       <c r="F26" t="s">
         <v>63</v>
       </c>
-      <c r="H26" t="s">
+      <c r="I26" t="s">
         <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -33138,11 +33186,11 @@
       <c r="F27" t="s">
         <v>89</v>
       </c>
-      <c r="H27" t="s">
+      <c r="I27" t="s">
         <v>90</v>
       </c>
       <c r="J27" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -33200,11 +33248,11 @@
       <c r="F28" t="s">
         <v>91</v>
       </c>
-      <c r="H28" t="s">
+      <c r="I28" t="s">
         <v>92</v>
       </c>
       <c r="J28" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -33262,11 +33310,11 @@
       <c r="F29" t="s">
         <v>93</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -33324,11 +33372,11 @@
       <c r="F30" t="s">
         <v>95</v>
       </c>
-      <c r="H30" t="s">
+      <c r="I30" t="s">
         <v>96</v>
       </c>
       <c r="J30" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K30">
         <v>4</v>
@@ -33386,11 +33434,11 @@
       <c r="F31" t="s">
         <v>77</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>97</v>
       </c>
       <c r="J31" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K31">
         <v>3</v>
@@ -33448,11 +33496,11 @@
       <c r="F32" t="s">
         <v>57</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
         <v>98</v>
       </c>
       <c r="J32" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -33510,11 +33558,11 @@
       <c r="F33" t="s">
         <v>55</v>
       </c>
-      <c r="H33" t="s">
+      <c r="I33" t="s">
         <v>99</v>
       </c>
       <c r="J33" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -33572,14 +33620,14 @@
       <c r="F34" t="s">
         <v>31</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>650</v>
       </c>
-      <c r="H34" t="s">
+      <c r="I34" t="s">
         <v>102</v>
       </c>
       <c r="J34" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K34">
         <v>33</v>
@@ -33640,11 +33688,11 @@
       <c r="F35" t="s">
         <v>103</v>
       </c>
-      <c r="H35" t="s">
+      <c r="I35" t="s">
         <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K35">
         <v>2.5</v>
@@ -33702,11 +33750,11 @@
       <c r="F36" t="s">
         <v>105</v>
       </c>
-      <c r="H36" t="s">
+      <c r="I36" t="s">
         <v>106</v>
       </c>
       <c r="J36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K36">
         <v>3</v>
@@ -33764,11 +33812,11 @@
       <c r="F37" t="s">
         <v>19</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>107</v>
       </c>
       <c r="J37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -33826,14 +33874,14 @@
       <c r="F38" t="s">
         <v>31</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>780</v>
       </c>
-      <c r="H38" t="s">
+      <c r="I38" t="s">
         <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K38">
         <v>30</v>
@@ -33894,11 +33942,11 @@
       <c r="F39" t="s">
         <v>103</v>
       </c>
-      <c r="H39" t="s">
+      <c r="I39" t="s">
         <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -33956,11 +34004,11 @@
       <c r="F40" t="s">
         <v>105</v>
       </c>
-      <c r="H40" t="s">
+      <c r="I40" t="s">
         <v>111</v>
       </c>
       <c r="J40" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="K40">
         <v>1.5</v>
@@ -34018,11 +34066,11 @@
       <c r="F41" t="s">
         <v>19</v>
       </c>
-      <c r="H41" t="s">
+      <c r="I41" t="s">
         <v>110</v>
       </c>
       <c r="J41" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -34080,11 +34128,11 @@
       <c r="F42" t="s">
         <v>55</v>
       </c>
-      <c r="H42" t="s">
+      <c r="I42" t="s">
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="K42">
         <v>3</v>
@@ -34379,7 +34427,7 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="K47">
         <v>4</v>
@@ -34735,7 +34783,7 @@
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="H53" t="s">
+      <c r="I53" t="s">
         <v>130</v>
       </c>
       <c r="J53" t="s">
@@ -34803,11 +34851,11 @@
       <c r="G54">
         <v>13</v>
       </c>
-      <c r="H54" t="s">
+      <c r="I54" t="s">
         <v>134</v>
       </c>
       <c r="J54" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -34871,7 +34919,7 @@
       <c r="G55">
         <v>6</v>
       </c>
-      <c r="H55" t="s">
+      <c r="I55" t="s">
         <v>137</v>
       </c>
       <c r="J55" t="s">
@@ -34939,7 +34987,7 @@
       <c r="G56">
         <v>7</v>
       </c>
-      <c r="H56" t="s">
+      <c r="I56" t="s">
         <v>140</v>
       </c>
       <c r="J56" t="s">
@@ -35004,7 +35052,7 @@
       <c r="F57" t="s">
         <v>31</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>140</v>
       </c>
       <c r="J57" t="s">
@@ -35066,7 +35114,7 @@
       <c r="F58" t="s">
         <v>31</v>
       </c>
-      <c r="H58" t="s">
+      <c r="I58" t="s">
         <v>145</v>
       </c>
       <c r="J58" t="s">
@@ -35128,14 +35176,14 @@
       <c r="F59" t="s">
         <v>31</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <v>2952</v>
       </c>
-      <c r="H59" t="s">
+      <c r="I59" t="s">
         <v>148</v>
       </c>
       <c r="J59" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K59">
         <v>6</v>
@@ -35196,11 +35244,11 @@
       <c r="F60" t="s">
         <v>50</v>
       </c>
-      <c r="H60" t="s">
+      <c r="I60" t="s">
         <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="K60">
         <v>6</v>
@@ -35247,16 +35295,16 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D61">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F61" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="K61">
         <v>3</v>
@@ -35297,16 +35345,16 @@
         <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D62">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F62" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="K62">
         <v>14</v>
@@ -35347,16 +35395,16 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D63">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F63" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="K63">
         <v>3</v>
@@ -35403,13 +35451,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F64" t="s">
         <v>151</v>
       </c>
-      <c r="H64" t="s">
-        <v>885</v>
+      <c r="I64" t="s">
+        <v>884</v>
       </c>
       <c r="J64" t="s">
         <v>312</v>
@@ -35473,14 +35521,14 @@
       <c r="F65" t="s">
         <v>31</v>
       </c>
-      <c r="G65">
+      <c r="H65">
         <v>8</v>
       </c>
-      <c r="H65" t="s">
+      <c r="I65" t="s">
         <v>154</v>
       </c>
       <c r="J65" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="K65">
         <v>12</v>
@@ -35544,7 +35592,7 @@
       <c r="G66">
         <v>56</v>
       </c>
-      <c r="H66" t="s">
+      <c r="I66" t="s">
         <v>155</v>
       </c>
       <c r="J66" t="s">
@@ -35609,7 +35657,7 @@
       <c r="G67">
         <v>17</v>
       </c>
-      <c r="H67" t="s">
+      <c r="I67" t="s">
         <v>158</v>
       </c>
       <c r="J67" t="s">
@@ -35674,11 +35722,11 @@
       <c r="G68">
         <v>20</v>
       </c>
-      <c r="H68" t="s">
+      <c r="I68" t="s">
         <v>161</v>
       </c>
       <c r="J68" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K68">
         <v>9</v>
@@ -35742,11 +35790,11 @@
       <c r="G69">
         <v>20</v>
       </c>
-      <c r="H69" t="s">
+      <c r="I69" t="s">
         <v>161</v>
       </c>
       <c r="J69" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="K69">
         <v>9</v>
@@ -35810,11 +35858,11 @@
       <c r="G70">
         <v>20</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>161</v>
       </c>
       <c r="J70" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="K70">
         <v>15</v>
@@ -35875,7 +35923,7 @@
       <c r="F71" t="s">
         <v>55</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>301</v>
       </c>
       <c r="J71" t="s">
@@ -35940,8 +35988,8 @@
       <c r="F72" t="s">
         <v>19</v>
       </c>
-      <c r="H72" t="s">
-        <v>889</v>
+      <c r="I72" t="s">
+        <v>888</v>
       </c>
       <c r="J72" t="s">
         <v>232</v>
@@ -36008,7 +36056,8 @@
       <c r="G73" s="1">
         <v>104</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="1"/>
+      <c r="I73" t="s">
         <v>168</v>
       </c>
       <c r="J73" t="s">
@@ -36048,7 +36097,7 @@
         <v>0</v>
       </c>
       <c r="V73" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="W73" t="s">
         <v>27</v>
@@ -36073,11 +36122,11 @@
       <c r="F74" t="s">
         <v>55</v>
       </c>
-      <c r="H74" t="s">
+      <c r="I74" t="s">
         <v>170</v>
       </c>
       <c r="J74" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="K74">
         <v>6</v>
@@ -36135,11 +36184,11 @@
       <c r="F75" t="s">
         <v>63</v>
       </c>
-      <c r="H75" t="s">
+      <c r="I75" t="s">
         <v>171</v>
       </c>
       <c r="J75" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="K75">
         <v>15</v>
@@ -36197,11 +36246,11 @@
       <c r="F76" t="s">
         <v>172</v>
       </c>
-      <c r="H76" t="s">
+      <c r="I76" t="s">
         <v>173</v>
       </c>
       <c r="J76" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K76">
         <v>12</v>
@@ -36259,11 +36308,11 @@
       <c r="F77" t="s">
         <v>174</v>
       </c>
-      <c r="H77" t="s">
+      <c r="I77" t="s">
         <v>175</v>
       </c>
       <c r="J77" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="K77">
         <v>3</v>
@@ -36321,11 +36370,11 @@
       <c r="F78" t="s">
         <v>176</v>
       </c>
-      <c r="H78" t="s">
+      <c r="I78" t="s">
         <v>177</v>
       </c>
       <c r="J78" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K78">
         <v>12</v>
@@ -36383,11 +36432,11 @@
       <c r="F79" t="s">
         <v>19</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>179</v>
       </c>
       <c r="J79" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="K79">
         <v>12</v>
@@ -36445,11 +36494,11 @@
       <c r="F80" t="s">
         <v>180</v>
       </c>
-      <c r="H80" t="s">
+      <c r="I80" t="s">
         <v>181</v>
       </c>
       <c r="J80" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="K80">
         <v>9</v>
@@ -36507,14 +36556,14 @@
       <c r="F81" t="s">
         <v>31</v>
       </c>
-      <c r="G81" s="1">
+      <c r="H81" s="1">
         <v>2772</v>
       </c>
-      <c r="H81" t="s">
+      <c r="I81" t="s">
         <v>184</v>
       </c>
       <c r="J81" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="K81">
         <v>36</v>
@@ -36550,7 +36599,7 @@
         <v>0</v>
       </c>
       <c r="V81" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="W81" t="s">
         <v>27</v>
@@ -36575,11 +36624,11 @@
       <c r="F82" t="s">
         <v>55</v>
       </c>
-      <c r="H82" t="s">
+      <c r="I82" t="s">
         <v>185</v>
       </c>
       <c r="J82" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K82">
         <v>3</v>
@@ -36637,11 +36686,11 @@
       <c r="F83" t="s">
         <v>186</v>
       </c>
-      <c r="H83" t="s">
+      <c r="I83" t="s">
         <v>187</v>
       </c>
       <c r="J83" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="K83">
         <v>3</v>
@@ -36699,11 +36748,11 @@
       <c r="F84" t="s">
         <v>188</v>
       </c>
-      <c r="H84" t="s">
+      <c r="I84" t="s">
         <v>189</v>
       </c>
       <c r="J84" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="K84">
         <v>6</v>
@@ -37045,16 +37094,16 @@
         <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F90" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="K90">
         <v>82</v>
@@ -37095,16 +37144,16 @@
         <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F91" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="K91">
         <v>32</v>
@@ -37145,16 +37194,16 @@
         <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F92" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K92">
         <v>9</v>

--- a/input/Anjar_manning.xlsx
+++ b/input/Anjar_manning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nikhitha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://welspungroup-my.sharepoint.com/personal/sahith_thadimudupula_welspun_com/Documents/Desktop/Manning_FInal_sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA25551-B56D-472F-BED2-082008FA24D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1050" documentId="13_ncr:1_{45658262-96CC-4946-9B46-BB1FC1723B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642364D8-ACF9-42F5-8D73-33B645D069DB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
   </bookViews>
   <sheets>
     <sheet name="Anjar" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -1742,6 +1745,9 @@
     <t>Housekeeping</t>
   </si>
   <si>
+    <t>Sheeting</t>
+  </si>
+  <si>
     <t>Sheeting - Weaving Preparatory</t>
   </si>
   <si>
@@ -2922,9 +2928,6 @@
   </si>
   <si>
     <t>Flat Bed</t>
-  </si>
-  <si>
-    <t>Bedsheet</t>
   </si>
 </sst>
 </file>
@@ -3338,7 +3341,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -3386,7 +3389,7 @@
         <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -3409,7 +3412,7 @@
         <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J2" t="s">
         <v>305</v>
@@ -3681,7 +3684,7 @@
         <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -3811,7 +3814,7 @@
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -3938,7 +3941,7 @@
         <v>294</v>
       </c>
       <c r="J10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3994,7 +3997,7 @@
         <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J11" t="s">
         <v>227</v>
@@ -4121,7 +4124,7 @@
         <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="K13">
         <v>36</v>
@@ -4186,7 +4189,7 @@
         <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -4248,7 +4251,7 @@
         <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -4310,7 +4313,7 @@
         <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -4372,7 +4375,7 @@
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K17">
         <v>12</v>
@@ -4434,7 +4437,7 @@
         <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -4496,7 +4499,7 @@
         <v>76</v>
       </c>
       <c r="J19" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -4558,7 +4561,7 @@
         <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -4620,7 +4623,7 @@
         <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -4682,7 +4685,7 @@
         <v>80</v>
       </c>
       <c r="J22" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -4747,7 +4750,7 @@
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K23">
         <v>54</v>
@@ -4812,7 +4815,7 @@
         <v>84</v>
       </c>
       <c r="J24" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -4874,7 +4877,7 @@
         <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -4936,7 +4939,7 @@
         <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -4998,7 +5001,7 @@
         <v>90</v>
       </c>
       <c r="J27" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -5060,7 +5063,7 @@
         <v>92</v>
       </c>
       <c r="J28" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -5122,7 +5125,7 @@
         <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -5184,7 +5187,7 @@
         <v>96</v>
       </c>
       <c r="J30" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K30">
         <v>4</v>
@@ -5246,7 +5249,7 @@
         <v>97</v>
       </c>
       <c r="J31" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K31">
         <v>3</v>
@@ -5308,7 +5311,7 @@
         <v>98</v>
       </c>
       <c r="J32" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -5370,7 +5373,7 @@
         <v>99</v>
       </c>
       <c r="J33" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -5435,7 +5438,7 @@
         <v>102</v>
       </c>
       <c r="J34" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K34">
         <v>33</v>
@@ -5500,7 +5503,7 @@
         <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K35">
         <v>2.5</v>
@@ -5562,7 +5565,7 @@
         <v>106</v>
       </c>
       <c r="J36" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K36">
         <v>3</v>
@@ -5624,7 +5627,7 @@
         <v>107</v>
       </c>
       <c r="J37" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -5689,7 +5692,7 @@
         <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K38">
         <v>30</v>
@@ -5754,7 +5757,7 @@
         <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -5816,7 +5819,7 @@
         <v>111</v>
       </c>
       <c r="J40" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K40">
         <v>1.5</v>
@@ -5878,7 +5881,7 @@
         <v>110</v>
       </c>
       <c r="J41" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -5940,7 +5943,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K42">
         <v>3</v>
@@ -6235,7 +6238,7 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K47">
         <v>4</v>
@@ -6577,7 +6580,7 @@
         <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -6589,7 +6592,7 @@
         <v>453</v>
       </c>
       <c r="J53" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="K53">
         <v>46</v>
@@ -6612,19 +6615,19 @@
         <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="F54" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="J54" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="K54">
         <v>11</v>
@@ -6733,7 +6736,7 @@
         <v>134</v>
       </c>
       <c r="J56" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="K56">
         <v>3</v>
@@ -7061,7 +7064,7 @@
         <v>148</v>
       </c>
       <c r="J61" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K61">
         <v>6</v>
@@ -7126,7 +7129,7 @@
         <v>149</v>
       </c>
       <c r="J62" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K62">
         <v>6</v>
@@ -7173,16 +7176,16 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D63">
         <v>9</v>
       </c>
       <c r="E63" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F63" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K63">
         <v>3</v>
@@ -7223,16 +7226,16 @@
         <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D64">
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F64" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K64">
         <v>14</v>
@@ -7273,16 +7276,16 @@
         <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D65">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F65" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K65">
         <v>3</v>
@@ -7329,13 +7332,13 @@
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F66" t="s">
         <v>151</v>
       </c>
       <c r="I66" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J66" t="s">
         <v>305</v>
@@ -7406,7 +7409,7 @@
         <v>154</v>
       </c>
       <c r="J67" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K67">
         <v>12</v>
@@ -7604,7 +7607,7 @@
         <v>161</v>
       </c>
       <c r="J70" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K70">
         <v>9</v>
@@ -7672,7 +7675,7 @@
         <v>161</v>
       </c>
       <c r="J71" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K71">
         <v>9</v>
@@ -7740,7 +7743,7 @@
         <v>161</v>
       </c>
       <c r="J72" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K72">
         <v>15</v>
@@ -7867,7 +7870,7 @@
         <v>19</v>
       </c>
       <c r="I74" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J74" t="s">
         <v>227</v>
@@ -7975,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="V75" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="W75" t="s">
         <v>27</v>
@@ -8004,7 +8007,7 @@
         <v>170</v>
       </c>
       <c r="J76" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K76">
         <v>6</v>
@@ -8066,7 +8069,7 @@
         <v>171</v>
       </c>
       <c r="J77" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K77">
         <v>15</v>
@@ -8128,7 +8131,7 @@
         <v>173</v>
       </c>
       <c r="J78" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K78">
         <v>12</v>
@@ -8190,7 +8193,7 @@
         <v>175</v>
       </c>
       <c r="J79" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K79">
         <v>3</v>
@@ -8252,7 +8255,7 @@
         <v>177</v>
       </c>
       <c r="J80" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K80">
         <v>12</v>
@@ -8314,7 +8317,7 @@
         <v>179</v>
       </c>
       <c r="J81" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K81">
         <v>12</v>
@@ -8376,7 +8379,7 @@
         <v>181</v>
       </c>
       <c r="J82" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="K82">
         <v>9</v>
@@ -8441,7 +8444,7 @@
         <v>184</v>
       </c>
       <c r="J83" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="K83">
         <v>36</v>
@@ -8477,7 +8480,7 @@
         <v>0</v>
       </c>
       <c r="V83" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="W83" t="s">
         <v>27</v>
@@ -8506,7 +8509,7 @@
         <v>185</v>
       </c>
       <c r="J84" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="K84">
         <v>3</v>
@@ -8568,7 +8571,7 @@
         <v>187</v>
       </c>
       <c r="J85" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="K85">
         <v>3</v>
@@ -8630,7 +8633,7 @@
         <v>189</v>
       </c>
       <c r="J86" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="K86">
         <v>6</v>
@@ -8972,16 +8975,16 @@
         <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F92" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="K92">
         <v>82</v>
@@ -9022,16 +9025,16 @@
         <v>28</v>
       </c>
       <c r="C93" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D93">
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F93" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K93">
         <v>32</v>
@@ -9072,16 +9075,16 @@
         <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D94">
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F94" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K94">
         <v>9</v>
@@ -9140,7 +9143,7 @@
         <v>200</v>
       </c>
       <c r="J95" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="K95">
         <v>30</v>
@@ -9329,7 +9332,7 @@
         <v>206</v>
       </c>
       <c r="J98" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="K98">
         <v>3</v>
@@ -9648,7 +9651,7 @@
         <v>220</v>
       </c>
       <c r="J103" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="K103">
         <v>30</v>
@@ -9704,7 +9707,7 @@
         <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F104" t="s">
         <v>222</v>
@@ -9766,7 +9769,7 @@
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F105" t="s">
         <v>224</v>
@@ -9828,7 +9831,7 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F106" t="s">
         <v>225</v>
@@ -9890,7 +9893,7 @@
         <v>13</v>
       </c>
       <c r="E107" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F107" t="s">
         <v>228</v>
@@ -9955,7 +9958,7 @@
         <v>14</v>
       </c>
       <c r="E108" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F108" t="s">
         <v>232</v>
@@ -10017,7 +10020,7 @@
         <v>15</v>
       </c>
       <c r="E109" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F109" t="s">
         <v>234</v>
@@ -10082,7 +10085,7 @@
         <v>16</v>
       </c>
       <c r="E110" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F110" t="s">
         <v>237</v>
@@ -10144,7 +10147,7 @@
         <v>17</v>
       </c>
       <c r="E111" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F111" t="s">
         <v>239</v>
@@ -10206,7 +10209,7 @@
         <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F112" t="s">
         <v>240</v>
@@ -10280,7 +10283,7 @@
         <v>244</v>
       </c>
       <c r="J113" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="K113">
         <v>205</v>
@@ -10475,7 +10478,7 @@
         <v>253</v>
       </c>
       <c r="J116" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="K116">
         <v>15</v>
@@ -10537,7 +10540,7 @@
         <v>255</v>
       </c>
       <c r="J117" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K117">
         <v>12</v>
@@ -10599,7 +10602,7 @@
         <v>255</v>
       </c>
       <c r="J118" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="K118">
         <v>12</v>
@@ -10850,7 +10853,7 @@
         <v>267</v>
       </c>
       <c r="J122" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="K122">
         <v>33</v>
@@ -11234,7 +11237,7 @@
         <v>280</v>
       </c>
       <c r="J128" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="K128">
         <v>21</v>
@@ -11296,7 +11299,7 @@
         <v>282</v>
       </c>
       <c r="J129" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="K129">
         <v>9</v>
@@ -17720,7 +17723,7 @@
         <v>458</v>
       </c>
       <c r="H230" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="I230" t="s">
         <v>453</v>
@@ -19076,7 +19079,7 @@
         <v>196</v>
       </c>
       <c r="C251" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -19099,7 +19102,7 @@
         <v>196</v>
       </c>
       <c r="C252" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -19122,7 +19125,7 @@
         <v>196</v>
       </c>
       <c r="C253" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -19145,7 +19148,7 @@
         <v>196</v>
       </c>
       <c r="C254" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -19168,7 +19171,7 @@
         <v>196</v>
       </c>
       <c r="C255" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -21103,10 +21106,10 @@
         <v>22</v>
       </c>
       <c r="B288" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C288" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -21124,7 +21127,7 @@
         <v>200</v>
       </c>
       <c r="J288" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="K288">
         <v>24</v>
@@ -21168,10 +21171,10 @@
         <v>22</v>
       </c>
       <c r="B289" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C289" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D289">
         <v>2</v>
@@ -21183,10 +21186,10 @@
         <v>202</v>
       </c>
       <c r="I289" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J289" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="K289">
         <v>15</v>
@@ -21230,10 +21233,10 @@
         <v>22</v>
       </c>
       <c r="B290" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C290" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D290">
         <v>3</v>
@@ -21251,7 +21254,7 @@
         <v>209</v>
       </c>
       <c r="J290" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K290">
         <v>12</v>
@@ -21295,10 +21298,10 @@
         <v>22</v>
       </c>
       <c r="B291" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C291" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D291">
         <v>4</v>
@@ -21313,7 +21316,7 @@
         <v>211</v>
       </c>
       <c r="J291" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K291">
         <v>12</v>
@@ -21357,10 +21360,10 @@
         <v>22</v>
       </c>
       <c r="B292" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C292" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D292">
         <v>5</v>
@@ -21419,10 +21422,10 @@
         <v>22</v>
       </c>
       <c r="B293" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C293" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D293">
         <v>6</v>
@@ -21431,7 +21434,7 @@
         <v>207</v>
       </c>
       <c r="F293" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="I293" t="s">
         <v>286</v>
@@ -21481,10 +21484,10 @@
         <v>22</v>
       </c>
       <c r="B294" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C294" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D294">
         <v>7</v>
@@ -21493,7 +21496,7 @@
         <v>207</v>
       </c>
       <c r="F294" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="I294" t="s">
         <v>235</v>
@@ -21546,10 +21549,10 @@
         <v>22</v>
       </c>
       <c r="B295" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C295" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D295">
         <v>8</v>
@@ -21558,7 +21561,7 @@
         <v>207</v>
       </c>
       <c r="F295" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="I295" t="s">
         <v>326</v>
@@ -21608,10 +21611,10 @@
         <v>22</v>
       </c>
       <c r="B296" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C296" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D296">
         <v>9</v>
@@ -21620,7 +21623,7 @@
         <v>207</v>
       </c>
       <c r="F296" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I296" t="s">
         <v>235</v>
@@ -21673,10 +21676,10 @@
         <v>22</v>
       </c>
       <c r="B297" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C297" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D297">
         <v>10</v>
@@ -21685,7 +21688,7 @@
         <v>207</v>
       </c>
       <c r="F297" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="I297" t="s">
         <v>326</v>
@@ -21735,10 +21738,10 @@
         <v>22</v>
       </c>
       <c r="B298" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C298" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D298">
         <v>11</v>
@@ -21747,7 +21750,7 @@
         <v>207</v>
       </c>
       <c r="F298" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I298" t="s">
         <v>286</v>
@@ -21797,10 +21800,10 @@
         <v>22</v>
       </c>
       <c r="B299" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C299" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D299">
         <v>12</v>
@@ -21809,7 +21812,7 @@
         <v>207</v>
       </c>
       <c r="F299" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I299" t="s">
         <v>235</v>
@@ -21862,10 +21865,10 @@
         <v>22</v>
       </c>
       <c r="B300" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C300" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D300">
         <v>13</v>
@@ -21874,7 +21877,7 @@
         <v>207</v>
       </c>
       <c r="F300" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="I300" t="s">
         <v>536</v>
@@ -21924,10 +21927,10 @@
         <v>22</v>
       </c>
       <c r="B301" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C301" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D301">
         <v>14</v>
@@ -21986,16 +21989,16 @@
         <v>22</v>
       </c>
       <c r="B302" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C302" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D302">
         <v>1</v>
       </c>
       <c r="E302" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F302" t="s">
         <v>243</v>
@@ -22004,10 +22007,10 @@
         <v>602</v>
       </c>
       <c r="I302" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J302" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K302">
         <v>258</v>
@@ -22043,7 +22046,7 @@
         <v>0</v>
       </c>
       <c r="V302" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="W302" t="s">
         <v>152</v>
@@ -22054,16 +22057,16 @@
         <v>22</v>
       </c>
       <c r="B303" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C303" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D303">
         <v>2</v>
       </c>
       <c r="E303" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F303" t="s">
         <v>247</v>
@@ -22075,7 +22078,7 @@
         <v>248</v>
       </c>
       <c r="J303" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="K303">
         <v>48</v>
@@ -22119,19 +22122,19 @@
         <v>22</v>
       </c>
       <c r="B304" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C304" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D304">
         <v>3</v>
       </c>
       <c r="E304" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F304" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="I304" t="s">
         <v>419</v>
@@ -22181,25 +22184,25 @@
         <v>22</v>
       </c>
       <c r="B305" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C305" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D305">
         <v>4</v>
       </c>
       <c r="E305" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F305" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="I305" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J305" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="K305">
         <v>27</v>
@@ -22243,25 +22246,25 @@
         <v>22</v>
       </c>
       <c r="B306" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C306" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D306">
         <v>5</v>
       </c>
       <c r="E306" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F306" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="I306" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="J306" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="K306">
         <v>66</v>
@@ -22305,25 +22308,25 @@
         <v>22</v>
       </c>
       <c r="B307" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C307" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D307">
         <v>6</v>
       </c>
       <c r="E307" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F307" t="s">
         <v>249</v>
       </c>
       <c r="I307" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="J307" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="K307">
         <v>30</v>
@@ -22367,22 +22370,22 @@
         <v>22</v>
       </c>
       <c r="B308" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C308" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D308">
         <v>7</v>
       </c>
       <c r="E308" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F308" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="I308" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="J308" t="s">
         <v>227</v>
@@ -22429,22 +22432,22 @@
         <v>22</v>
       </c>
       <c r="B309" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C309" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D309">
         <v>8</v>
       </c>
       <c r="E309" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F309" t="s">
         <v>257</v>
       </c>
       <c r="I309" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J309" t="s">
         <v>214</v>
@@ -22491,16 +22494,16 @@
         <v>22</v>
       </c>
       <c r="B310" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C310" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D310">
         <v>9</v>
       </c>
       <c r="E310" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F310" t="s">
         <v>256</v>
@@ -22509,7 +22512,7 @@
         <v>255</v>
       </c>
       <c r="J310" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="K310">
         <v>18</v>
@@ -22545,7 +22548,7 @@
         <v>0</v>
       </c>
       <c r="V310" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="W310" t="s">
         <v>74</v>
@@ -22556,22 +22559,22 @@
         <v>22</v>
       </c>
       <c r="B311" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C311" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D311">
         <v>10</v>
       </c>
       <c r="E311" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F311" t="s">
         <v>254</v>
       </c>
       <c r="I311" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="J311" t="s">
         <v>298</v>
@@ -22618,19 +22621,19 @@
         <v>22</v>
       </c>
       <c r="B312" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C312" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D312">
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F312" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="I312" t="s">
         <v>332</v>
@@ -22683,22 +22686,22 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C313" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D313">
         <v>12</v>
       </c>
       <c r="E313" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F313" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="I313" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J313" t="s">
         <v>519</v>
@@ -22748,22 +22751,22 @@
         <v>22</v>
       </c>
       <c r="B314" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C314" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D314">
         <v>13</v>
       </c>
       <c r="E314" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F314" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="I314" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J314" t="s">
         <v>411</v>
@@ -22813,19 +22816,19 @@
         <v>22</v>
       </c>
       <c r="B315" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C315" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D315">
         <v>14</v>
       </c>
       <c r="E315" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F315" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="I315" t="s">
         <v>332</v>
@@ -22878,19 +22881,19 @@
         <v>22</v>
       </c>
       <c r="B316" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C316" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D316">
         <v>15</v>
       </c>
       <c r="E316" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F316" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="I316" t="s">
         <v>552</v>
@@ -22940,25 +22943,25 @@
         <v>22</v>
       </c>
       <c r="B317" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C317" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D317">
         <v>16</v>
       </c>
       <c r="E317" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F317" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="I317" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J317" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="K317">
         <v>113</v>
@@ -23002,16 +23005,16 @@
         <v>22</v>
       </c>
       <c r="B318" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C318" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D318">
         <v>1</v>
       </c>
       <c r="E318" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F318" t="s">
         <v>31</v>
@@ -23020,7 +23023,7 @@
         <v>3</v>
       </c>
       <c r="I318" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J318" t="s">
         <v>275</v>
@@ -23067,22 +23070,22 @@
         <v>22</v>
       </c>
       <c r="B319" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C319" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D319">
         <v>2</v>
       </c>
       <c r="E319" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F319" t="s">
         <v>287</v>
       </c>
       <c r="I319" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J319" t="s">
         <v>275</v>
@@ -23129,22 +23132,22 @@
         <v>22</v>
       </c>
       <c r="B320" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C320" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D320">
         <v>3</v>
       </c>
       <c r="E320" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F320" t="s">
         <v>292</v>
       </c>
       <c r="I320" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J320" t="s">
         <v>275</v>
@@ -23191,16 +23194,16 @@
         <v>22</v>
       </c>
       <c r="B321" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C321" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D321">
         <v>4</v>
       </c>
       <c r="E321" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F321" t="s">
         <v>31</v>
@@ -23256,16 +23259,16 @@
         <v>22</v>
       </c>
       <c r="B322" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C322" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D322">
         <v>5</v>
       </c>
       <c r="E322" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F322" t="s">
         <v>287</v>
@@ -23318,16 +23321,16 @@
         <v>22</v>
       </c>
       <c r="B323" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C323" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D323">
         <v>6</v>
       </c>
       <c r="E323" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F323" t="s">
         <v>31</v>
@@ -23336,7 +23339,7 @@
         <v>3</v>
       </c>
       <c r="I323" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J323" t="s">
         <v>275</v>
@@ -23383,22 +23386,22 @@
         <v>22</v>
       </c>
       <c r="B324" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C324" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D324">
         <v>7</v>
       </c>
       <c r="E324" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F324" t="s">
         <v>287</v>
       </c>
       <c r="I324" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J324" t="s">
         <v>275</v>
@@ -23445,16 +23448,16 @@
         <v>22</v>
       </c>
       <c r="B325" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C325" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D325">
         <v>8</v>
       </c>
       <c r="E325" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F325" t="s">
         <v>292</v>
@@ -23507,16 +23510,16 @@
         <v>22</v>
       </c>
       <c r="B326" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C326" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D326">
         <v>9</v>
       </c>
       <c r="E326" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F326" t="s">
         <v>31</v>
@@ -23575,16 +23578,16 @@
         <v>22</v>
       </c>
       <c r="B327" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C327" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D327">
         <v>10</v>
       </c>
       <c r="E327" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F327" t="s">
         <v>287</v>
@@ -23637,16 +23640,16 @@
         <v>22</v>
       </c>
       <c r="B328" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C328" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D328">
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F328" t="s">
         <v>292</v>
@@ -23699,16 +23702,16 @@
         <v>22</v>
       </c>
       <c r="B329" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C329" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D329">
         <v>12</v>
       </c>
       <c r="E329" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F329" t="s">
         <v>31</v>
@@ -23764,16 +23767,16 @@
         <v>22</v>
       </c>
       <c r="B330" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C330" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D330">
         <v>13</v>
       </c>
       <c r="E330" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="F330" t="s">
         <v>31</v>
@@ -23829,16 +23832,16 @@
         <v>22</v>
       </c>
       <c r="B331" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C331" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D331">
         <v>14</v>
       </c>
       <c r="E331" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F331" t="s">
         <v>55</v>
@@ -23891,10 +23894,10 @@
         <v>22</v>
       </c>
       <c r="B332" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C332" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D332">
         <v>15</v>
@@ -23903,10 +23906,10 @@
         <v>331</v>
       </c>
       <c r="F332" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I332" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J332" t="s">
         <v>214</v>
@@ -23953,22 +23956,22 @@
         <v>22</v>
       </c>
       <c r="B333" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C333" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D333">
         <v>16</v>
       </c>
       <c r="E333" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F333" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I333" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J333" t="s">
         <v>353</v>
@@ -24007,7 +24010,7 @@
         <v>0</v>
       </c>
       <c r="V333" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="W333" t="s">
         <v>178</v>
@@ -24018,22 +24021,22 @@
         <v>22</v>
       </c>
       <c r="B334" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C334" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D334">
         <v>17</v>
       </c>
       <c r="E334" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F334" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="I334" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="J334" t="s">
         <v>227</v>
@@ -24080,16 +24083,16 @@
         <v>22</v>
       </c>
       <c r="B335" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C335" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D335">
         <v>1</v>
       </c>
       <c r="E335" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F335" t="s">
         <v>31</v>
@@ -24098,7 +24101,7 @@
         <v>3</v>
       </c>
       <c r="I335" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J335" t="s">
         <v>275</v>
@@ -24145,22 +24148,22 @@
         <v>22</v>
       </c>
       <c r="B336" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C336" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D336">
         <v>2</v>
       </c>
       <c r="E336" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F336" t="s">
         <v>287</v>
       </c>
       <c r="I336" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J336" t="s">
         <v>275</v>
@@ -24207,22 +24210,22 @@
         <v>22</v>
       </c>
       <c r="B337" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C337" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D337">
         <v>3</v>
       </c>
       <c r="E337" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F337" t="s">
         <v>292</v>
       </c>
       <c r="I337" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J337" t="s">
         <v>275</v>
@@ -24269,16 +24272,16 @@
         <v>22</v>
       </c>
       <c r="B338" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C338" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D338">
         <v>4</v>
       </c>
       <c r="E338" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F338" t="s">
         <v>31</v>
@@ -24287,7 +24290,7 @@
         <v>2</v>
       </c>
       <c r="I338" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J338" t="s">
         <v>298</v>
@@ -24334,16 +24337,16 @@
         <v>22</v>
       </c>
       <c r="B339" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C339" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D339">
         <v>5</v>
       </c>
       <c r="E339" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F339" t="s">
         <v>287</v>
@@ -24396,16 +24399,16 @@
         <v>22</v>
       </c>
       <c r="B340" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C340" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D340">
         <v>6</v>
       </c>
       <c r="E340" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F340" t="s">
         <v>292</v>
@@ -24458,10 +24461,10 @@
         <v>22</v>
       </c>
       <c r="B341" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C341" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D341">
         <v>7</v>
@@ -24476,7 +24479,7 @@
         <v>1</v>
       </c>
       <c r="I341" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J341" t="s">
         <v>348</v>
@@ -24523,10 +24526,10 @@
         <v>22</v>
       </c>
       <c r="B342" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C342" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D342">
         <v>8</v>
@@ -24538,7 +24541,7 @@
         <v>287</v>
       </c>
       <c r="I342" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J342" t="s">
         <v>305</v>
@@ -24585,10 +24588,10 @@
         <v>22</v>
       </c>
       <c r="B343" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C343" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D343">
         <v>9</v>
@@ -24600,7 +24603,7 @@
         <v>292</v>
       </c>
       <c r="I343" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J343" t="s">
         <v>305</v>
@@ -24647,16 +24650,16 @@
         <v>22</v>
       </c>
       <c r="B344" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C344" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D344">
         <v>10</v>
       </c>
       <c r="E344" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F344" t="s">
         <v>31</v>
@@ -24712,16 +24715,16 @@
         <v>22</v>
       </c>
       <c r="B345" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C345" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D345">
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F345" t="s">
         <v>287</v>
@@ -24774,16 +24777,16 @@
         <v>22</v>
       </c>
       <c r="B346" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C346" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D346">
         <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F346" t="s">
         <v>292</v>
@@ -24836,25 +24839,25 @@
         <v>22</v>
       </c>
       <c r="B347" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C347" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D347">
         <v>13</v>
       </c>
       <c r="E347" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F347" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G347">
         <v>2</v>
       </c>
       <c r="I347" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="J347" t="s">
         <v>348</v>
@@ -24901,10 +24904,10 @@
         <v>22</v>
       </c>
       <c r="B348" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C348" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D348">
         <v>14</v>
@@ -24913,7 +24916,7 @@
         <v>308</v>
       </c>
       <c r="F348" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G348">
         <v>1</v>
@@ -24966,25 +24969,25 @@
         <v>22</v>
       </c>
       <c r="B349" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C349" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D349">
         <v>15</v>
       </c>
       <c r="E349" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F349" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G349">
         <v>1</v>
       </c>
       <c r="I349" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J349" t="s">
         <v>426</v>
@@ -25031,25 +25034,25 @@
         <v>22</v>
       </c>
       <c r="B350" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C350" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D350">
         <v>16</v>
       </c>
       <c r="E350" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F350" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G350">
         <v>1</v>
       </c>
       <c r="I350" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J350" t="s">
         <v>227</v>
@@ -25096,16 +25099,16 @@
         <v>22</v>
       </c>
       <c r="B351" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C351" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D351">
         <v>17</v>
       </c>
       <c r="E351" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F351" t="s">
         <v>55</v>
@@ -25161,22 +25164,22 @@
         <v>22</v>
       </c>
       <c r="B352" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C352" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D352">
         <v>18</v>
       </c>
       <c r="E352" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F352" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="I352" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J352" t="s">
         <v>298</v>
@@ -25223,22 +25226,22 @@
         <v>22</v>
       </c>
       <c r="B353" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C353" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D353">
         <v>19</v>
       </c>
       <c r="E353" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F353" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I353" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J353" t="s">
         <v>298</v>
@@ -25285,22 +25288,22 @@
         <v>22</v>
       </c>
       <c r="B354" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C354" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D354">
         <v>20</v>
       </c>
       <c r="E354" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F354" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="I354" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="J354" t="s">
         <v>278</v>
@@ -25350,16 +25353,16 @@
         <v>22</v>
       </c>
       <c r="B355" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C355" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D355">
         <v>1</v>
       </c>
       <c r="E355" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F355" t="s">
         <v>31</v>
@@ -25415,16 +25418,16 @@
         <v>22</v>
       </c>
       <c r="B356" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C356" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D356">
         <v>2</v>
       </c>
       <c r="E356" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F356" t="s">
         <v>287</v>
@@ -25477,16 +25480,16 @@
         <v>22</v>
       </c>
       <c r="B357" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C357" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D357">
         <v>3</v>
       </c>
       <c r="E357" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F357" t="s">
         <v>292</v>
@@ -25539,16 +25542,16 @@
         <v>22</v>
       </c>
       <c r="B358" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C358" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D358">
         <v>4</v>
       </c>
       <c r="E358" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F358" t="s">
         <v>31</v>
@@ -25557,7 +25560,7 @@
         <v>2</v>
       </c>
       <c r="I358" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J358" t="s">
         <v>275</v>
@@ -25604,22 +25607,22 @@
         <v>22</v>
       </c>
       <c r="B359" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C359" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D359">
         <v>5</v>
       </c>
       <c r="E359" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F359" t="s">
         <v>287</v>
       </c>
       <c r="I359" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J359" t="s">
         <v>275</v>
@@ -25666,16 +25669,16 @@
         <v>22</v>
       </c>
       <c r="B360" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C360" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D360">
         <v>6</v>
       </c>
       <c r="E360" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F360" t="s">
         <v>31</v>
@@ -25731,16 +25734,16 @@
         <v>22</v>
       </c>
       <c r="B361" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C361" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D361">
         <v>7</v>
       </c>
       <c r="E361" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F361" t="s">
         <v>287</v>
@@ -25793,16 +25796,16 @@
         <v>22</v>
       </c>
       <c r="B362" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C362" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D362">
         <v>8</v>
       </c>
       <c r="E362" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F362" t="s">
         <v>31</v>
@@ -25858,16 +25861,16 @@
         <v>22</v>
       </c>
       <c r="B363" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C363" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D363">
         <v>9</v>
       </c>
       <c r="E363" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F363" t="s">
         <v>287</v>
@@ -25920,16 +25923,16 @@
         <v>22</v>
       </c>
       <c r="B364" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C364" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D364">
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F364" t="s">
         <v>31</v>
@@ -25985,16 +25988,16 @@
         <v>22</v>
       </c>
       <c r="B365" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C365" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D365">
         <v>12</v>
       </c>
       <c r="E365" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F365" t="s">
         <v>287</v>
@@ -26047,16 +26050,16 @@
         <v>22</v>
       </c>
       <c r="B366" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C366" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D366">
         <v>13</v>
       </c>
       <c r="E366" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F366" t="s">
         <v>292</v>
@@ -26109,16 +26112,16 @@
         <v>22</v>
       </c>
       <c r="B367" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C367" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D367">
         <v>14</v>
       </c>
       <c r="E367" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F367" t="s">
         <v>31</v>
@@ -26174,16 +26177,16 @@
         <v>22</v>
       </c>
       <c r="B368" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C368" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D368">
         <v>15</v>
       </c>
       <c r="E368" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F368" t="s">
         <v>287</v>
@@ -26236,16 +26239,16 @@
         <v>22</v>
       </c>
       <c r="B369" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C369" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D369">
         <v>16</v>
       </c>
       <c r="E369" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F369" t="s">
         <v>31</v>
@@ -26301,16 +26304,16 @@
         <v>22</v>
       </c>
       <c r="B370" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C370" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D370">
         <v>17</v>
       </c>
       <c r="E370" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F370" t="s">
         <v>287</v>
@@ -26363,10 +26366,10 @@
         <v>22</v>
       </c>
       <c r="B371" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C371" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D371">
         <v>18</v>
@@ -26375,10 +26378,10 @@
         <v>331</v>
       </c>
       <c r="F371" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I371" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="J371" t="s">
         <v>214</v>
@@ -26425,22 +26428,22 @@
         <v>22</v>
       </c>
       <c r="B372" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C372" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D372">
         <v>19</v>
       </c>
       <c r="E372" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F372" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="I372" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="J372" t="s">
         <v>227</v>
@@ -26487,22 +26490,22 @@
         <v>22</v>
       </c>
       <c r="B373" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C373" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D373">
         <v>20</v>
       </c>
       <c r="E373" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F373" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="I373" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="J373" t="s">
         <v>348</v>
@@ -26549,16 +26552,16 @@
         <v>22</v>
       </c>
       <c r="B374" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C374" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D374">
         <v>21</v>
       </c>
       <c r="E374" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="F374" t="s">
         <v>55</v>
@@ -26614,19 +26617,19 @@
         <v>22</v>
       </c>
       <c r="B375" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C375" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D375">
         <v>22</v>
       </c>
       <c r="E375" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F375" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I375" t="s">
         <v>504</v>
@@ -26676,16 +26679,16 @@
         <v>22</v>
       </c>
       <c r="B376" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C376" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D376">
         <v>1</v>
       </c>
       <c r="E376" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F376" t="s">
         <v>31</v>
@@ -26741,16 +26744,16 @@
         <v>22</v>
       </c>
       <c r="B377" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C377" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D377">
         <v>2</v>
       </c>
       <c r="E377" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F377" t="s">
         <v>292</v>
@@ -26803,10 +26806,10 @@
         <v>22</v>
       </c>
       <c r="B378" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C378" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D378">
         <v>3</v>
@@ -26821,10 +26824,10 @@
         <v>2</v>
       </c>
       <c r="I378" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J378" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K378">
         <v>4</v>
@@ -26871,10 +26874,10 @@
         <v>22</v>
       </c>
       <c r="B379" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C379" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D379">
         <v>4</v>
@@ -26886,10 +26889,10 @@
         <v>292</v>
       </c>
       <c r="I379" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="J379" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="K379">
         <v>5</v>
@@ -26936,16 +26939,16 @@
         <v>22</v>
       </c>
       <c r="B380" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C380" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D380">
         <v>5</v>
       </c>
       <c r="E380" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F380" t="s">
         <v>31</v>
@@ -26954,7 +26957,7 @@
         <v>2</v>
       </c>
       <c r="I380" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J380" t="s">
         <v>353</v>
@@ -26993,7 +26996,7 @@
         <v>0</v>
       </c>
       <c r="V380" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="W380" t="s">
         <v>27</v>
@@ -27004,16 +27007,16 @@
         <v>22</v>
       </c>
       <c r="B381" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C381" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D381">
         <v>6</v>
       </c>
       <c r="E381" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F381" t="s">
         <v>287</v>
@@ -27069,16 +27072,16 @@
         <v>22</v>
       </c>
       <c r="B382" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C382" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D382">
         <v>7</v>
       </c>
       <c r="E382" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F382" t="s">
         <v>292</v>
@@ -27131,10 +27134,10 @@
         <v>22</v>
       </c>
       <c r="B383" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C383" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D383">
         <v>8</v>
@@ -27196,10 +27199,10 @@
         <v>22</v>
       </c>
       <c r="B384" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C384" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D384">
         <v>9</v>
@@ -27258,10 +27261,10 @@
         <v>22</v>
       </c>
       <c r="B385" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C385" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D385">
         <v>10</v>
@@ -27270,10 +27273,10 @@
         <v>308</v>
       </c>
       <c r="F385" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="I385" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J385" t="s">
         <v>393</v>
@@ -27320,22 +27323,22 @@
         <v>22</v>
       </c>
       <c r="B386" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C386" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D386">
         <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F386" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="I386" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="J386" t="s">
         <v>524</v>
@@ -27374,7 +27377,7 @@
         <v>0</v>
       </c>
       <c r="V386" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="W386" t="s">
         <v>27</v>
@@ -27385,19 +27388,19 @@
         <v>22</v>
       </c>
       <c r="B387" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C387" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D387">
         <v>12</v>
       </c>
       <c r="E387" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F387" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="I387" t="s">
         <v>307</v>
@@ -27450,22 +27453,22 @@
         <v>22</v>
       </c>
       <c r="B388" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C388" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D388">
         <v>13</v>
       </c>
       <c r="E388" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F388" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="I388" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="J388" t="s">
         <v>370</v>
@@ -27512,28 +27515,28 @@
         <v>22</v>
       </c>
       <c r="B389" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C389" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D389">
         <v>1</v>
       </c>
       <c r="E389" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F389" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G389" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="I389" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="J389" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K389">
         <v>25</v>
@@ -27569,7 +27572,7 @@
         <v>0</v>
       </c>
       <c r="V389" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="W389" t="s">
         <v>27</v>
@@ -27580,22 +27583,22 @@
         <v>22</v>
       </c>
       <c r="B390" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C390" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D390">
         <v>2</v>
       </c>
       <c r="E390" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F390" t="s">
         <v>31</v>
       </c>
       <c r="I390" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="J390" t="s">
         <v>24</v>
@@ -27642,22 +27645,22 @@
         <v>22</v>
       </c>
       <c r="B391" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C391" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D391">
         <v>3</v>
       </c>
       <c r="E391" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F391" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="I391" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J391" t="s">
         <v>24</v>
@@ -27704,22 +27707,22 @@
         <v>22</v>
       </c>
       <c r="B392" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C392" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D392">
         <v>4</v>
       </c>
       <c r="E392" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F392" t="s">
         <v>292</v>
       </c>
       <c r="I392" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="J392" t="s">
         <v>24</v>
@@ -27758,7 +27761,7 @@
         <v>0</v>
       </c>
       <c r="W392" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="393" spans="1:23" x14ac:dyDescent="0.3">
@@ -27766,22 +27769,22 @@
         <v>22</v>
       </c>
       <c r="B393" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C393" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D393">
         <v>5</v>
       </c>
       <c r="E393" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F393" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="I393" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J393" t="s">
         <v>24</v>
@@ -27820,7 +27823,7 @@
         <v>0</v>
       </c>
       <c r="W393" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="394" spans="1:23" x14ac:dyDescent="0.3">
@@ -27828,22 +27831,22 @@
         <v>22</v>
       </c>
       <c r="B394" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C394" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D394">
         <v>6</v>
       </c>
       <c r="E394" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F394" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="I394" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="J394" t="s">
         <v>24</v>
@@ -27882,7 +27885,7 @@
         <v>0</v>
       </c>
       <c r="W394" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="395" spans="1:23" x14ac:dyDescent="0.3">
@@ -27890,22 +27893,22 @@
         <v>22</v>
       </c>
       <c r="B395" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C395" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D395">
         <v>7</v>
       </c>
       <c r="E395" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F395" t="s">
         <v>237</v>
       </c>
       <c r="I395" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J395" t="s">
         <v>24</v>
@@ -27952,28 +27955,28 @@
         <v>22</v>
       </c>
       <c r="B396" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C396" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D396">
         <v>8</v>
       </c>
       <c r="E396" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F396" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G396" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="I396" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="J396" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K396">
         <v>572</v>
@@ -28009,7 +28012,7 @@
         <v>0</v>
       </c>
       <c r="V396" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="W396" t="s">
         <v>27</v>
@@ -28020,22 +28023,22 @@
         <v>22</v>
       </c>
       <c r="B397" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C397" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D397">
         <v>9</v>
       </c>
       <c r="E397" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F397" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="I397" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="J397" t="s">
         <v>24</v>
@@ -28074,7 +28077,7 @@
         <v>0</v>
       </c>
       <c r="W397" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="398" spans="1:23" x14ac:dyDescent="0.3">
@@ -28082,22 +28085,22 @@
         <v>22</v>
       </c>
       <c r="B398" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C398" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D398">
         <v>10</v>
       </c>
       <c r="E398" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F398" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="I398" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="J398" t="s">
         <v>24</v>
@@ -28136,7 +28139,7 @@
         <v>0</v>
       </c>
       <c r="W398" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="399" spans="1:23" x14ac:dyDescent="0.3">
@@ -28144,22 +28147,22 @@
         <v>22</v>
       </c>
       <c r="B399" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C399" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D399">
         <v>11</v>
       </c>
       <c r="E399" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F399" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="I399" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J399" t="s">
         <v>24</v>
@@ -28198,7 +28201,7 @@
         <v>0</v>
       </c>
       <c r="W399" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="400" spans="1:23" x14ac:dyDescent="0.3">
@@ -28206,22 +28209,22 @@
         <v>22</v>
       </c>
       <c r="B400" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C400" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D400">
         <v>12</v>
       </c>
       <c r="E400" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F400" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="I400" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="J400" t="s">
         <v>24</v>
@@ -28268,28 +28271,28 @@
         <v>22</v>
       </c>
       <c r="B401" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C401" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D401">
         <v>13</v>
       </c>
       <c r="E401" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F401" t="s">
         <v>31</v>
       </c>
       <c r="G401" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="I401" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J401" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K401">
         <v>4</v>
@@ -28325,7 +28328,7 @@
         <v>0</v>
       </c>
       <c r="V401" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="W401" t="s">
         <v>27</v>
@@ -28336,22 +28339,22 @@
         <v>22</v>
       </c>
       <c r="B402" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C402" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D402">
         <v>14</v>
       </c>
       <c r="E402" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F402" t="s">
         <v>292</v>
       </c>
       <c r="I402" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="J402" t="s">
         <v>24</v>
@@ -28390,7 +28393,7 @@
         <v>0</v>
       </c>
       <c r="W402" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="403" spans="1:23" x14ac:dyDescent="0.3">
@@ -28398,19 +28401,19 @@
         <v>22</v>
       </c>
       <c r="B403" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C403" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D403">
         <v>15</v>
       </c>
       <c r="E403" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F403" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="J403" t="s">
         <v>24</v>
@@ -28457,19 +28460,19 @@
         <v>22</v>
       </c>
       <c r="B404" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C404" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D404">
         <v>16</v>
       </c>
       <c r="E404" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F404" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J404" t="s">
         <v>24</v>
@@ -28508,7 +28511,7 @@
         <v>51</v>
       </c>
       <c r="W404" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="405" spans="1:23" x14ac:dyDescent="0.3">
@@ -28516,19 +28519,19 @@
         <v>22</v>
       </c>
       <c r="B405" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C405" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D405">
         <v>17</v>
       </c>
       <c r="E405" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F405" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="J405" t="s">
         <v>24</v>
@@ -28575,28 +28578,28 @@
         <v>22</v>
       </c>
       <c r="B406" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C406" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D406">
         <v>18</v>
       </c>
       <c r="E406" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F406" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G406" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="I406" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J406" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="K406">
         <v>248</v>
@@ -28632,7 +28635,7 @@
         <v>0</v>
       </c>
       <c r="V406" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="W406" t="s">
         <v>27</v>
@@ -28643,22 +28646,22 @@
         <v>22</v>
       </c>
       <c r="B407" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C407" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D407">
         <v>19</v>
       </c>
       <c r="E407" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F407" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="I407" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="J407" t="s">
         <v>24</v>
@@ -28697,7 +28700,7 @@
         <v>0</v>
       </c>
       <c r="W407" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="408" spans="1:23" x14ac:dyDescent="0.3">
@@ -28705,22 +28708,22 @@
         <v>22</v>
       </c>
       <c r="B408" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C408" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D408">
         <v>20</v>
       </c>
       <c r="E408" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F408" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="I408" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="J408" t="s">
         <v>24</v>
@@ -28759,7 +28762,7 @@
         <v>0</v>
       </c>
       <c r="W408" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="409" spans="1:23" x14ac:dyDescent="0.3">
@@ -28767,28 +28770,28 @@
         <v>22</v>
       </c>
       <c r="B409" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C409" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D409">
         <v>21</v>
       </c>
       <c r="E409" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F409" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="G409" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="I409" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="J409" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K409">
         <v>6</v>
@@ -28824,7 +28827,7 @@
         <v>0</v>
       </c>
       <c r="V409" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="W409" t="s">
         <v>27</v>
@@ -28835,22 +28838,22 @@
         <v>22</v>
       </c>
       <c r="B410" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C410" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D410">
         <v>22</v>
       </c>
       <c r="E410" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F410" t="s">
         <v>292</v>
       </c>
       <c r="I410" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="J410" t="s">
         <v>24</v>
@@ -28889,7 +28892,7 @@
         <v>0</v>
       </c>
       <c r="W410" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="411" spans="1:23" x14ac:dyDescent="0.3">
@@ -28897,28 +28900,28 @@
         <v>22</v>
       </c>
       <c r="B411" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C411" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D411">
         <v>23</v>
       </c>
       <c r="E411" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F411" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G411" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I411" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="J411" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K411">
         <v>137</v>
@@ -28954,7 +28957,7 @@
         <v>0</v>
       </c>
       <c r="V411" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="W411" t="s">
         <v>27</v>
@@ -28965,22 +28968,22 @@
         <v>22</v>
       </c>
       <c r="B412" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C412" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D412">
         <v>24</v>
       </c>
       <c r="E412" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F412" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I412" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="J412" t="s">
         <v>24</v>
@@ -29019,7 +29022,7 @@
         <v>0</v>
       </c>
       <c r="W412" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="413" spans="1:23" x14ac:dyDescent="0.3">
@@ -29027,28 +29030,28 @@
         <v>22</v>
       </c>
       <c r="B413" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C413" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D413">
         <v>25</v>
       </c>
       <c r="E413" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F413" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G413" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="I413" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="J413" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="K413">
         <v>91</v>
@@ -29084,10 +29087,10 @@
         <v>0</v>
       </c>
       <c r="V413" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="W413" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="414" spans="1:23" x14ac:dyDescent="0.3">
@@ -29095,22 +29098,22 @@
         <v>22</v>
       </c>
       <c r="B414" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C414" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D414">
         <v>26</v>
       </c>
       <c r="E414" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F414" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="I414" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J414" t="s">
         <v>24</v>
@@ -29157,22 +29160,22 @@
         <v>22</v>
       </c>
       <c r="B415" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C415" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D415">
         <v>27</v>
       </c>
       <c r="E415" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F415" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I415" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J415" t="s">
         <v>214</v>
@@ -29211,7 +29214,7 @@
         <v>0</v>
       </c>
       <c r="W415" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="416" spans="1:23" x14ac:dyDescent="0.3">
@@ -29219,22 +29222,22 @@
         <v>22</v>
       </c>
       <c r="B416" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C416" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D416">
         <v>28</v>
       </c>
       <c r="E416" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F416" t="s">
         <v>237</v>
       </c>
       <c r="I416" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J416" t="s">
         <v>227</v>
@@ -29281,22 +29284,22 @@
         <v>22</v>
       </c>
       <c r="B417" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C417" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D417">
         <v>29</v>
       </c>
       <c r="E417" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F417" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="I417" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="J417" t="s">
         <v>227</v>
@@ -29335,7 +29338,7 @@
         <v>0</v>
       </c>
       <c r="W417" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="418" spans="1:23" x14ac:dyDescent="0.3">
@@ -29343,22 +29346,22 @@
         <v>22</v>
       </c>
       <c r="B418" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C418" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D418">
         <v>30</v>
       </c>
       <c r="E418" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F418" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="I418" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J418" t="s">
         <v>323</v>
@@ -29397,10 +29400,10 @@
         <v>0</v>
       </c>
       <c r="V418" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="W418" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="419" spans="1:23" x14ac:dyDescent="0.3">
@@ -29408,22 +29411,22 @@
         <v>22</v>
       </c>
       <c r="B419" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C419" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D419">
         <v>31</v>
       </c>
       <c r="E419" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F419" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="I419" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="J419" t="s">
         <v>214</v>
@@ -29462,7 +29465,7 @@
         <v>0</v>
       </c>
       <c r="W419" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="420" spans="1:23" x14ac:dyDescent="0.3">
@@ -29470,28 +29473,28 @@
         <v>22</v>
       </c>
       <c r="B420" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C420" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D420">
         <v>32</v>
       </c>
       <c r="E420" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F420" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G420" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="I420" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="J420" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="K420">
         <v>234</v>
@@ -29527,7 +29530,7 @@
         <v>0</v>
       </c>
       <c r="V420" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="W420" t="s">
         <v>27</v>
@@ -29538,22 +29541,22 @@
         <v>22</v>
       </c>
       <c r="B421" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C421" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D421">
         <v>33</v>
       </c>
       <c r="E421" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F421" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I421" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="J421" t="s">
         <v>24</v>
@@ -29592,7 +29595,7 @@
         <v>0</v>
       </c>
       <c r="W421" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="422" spans="1:23" x14ac:dyDescent="0.3">
@@ -29600,22 +29603,22 @@
         <v>22</v>
       </c>
       <c r="B422" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C422" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D422">
         <v>34</v>
       </c>
       <c r="E422" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F422" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="I422" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="J422" t="s">
         <v>24</v>
@@ -29665,22 +29668,22 @@
         <v>22</v>
       </c>
       <c r="B423" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C423" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D423">
         <v>35</v>
       </c>
       <c r="E423" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F423" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="I423" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="J423" t="s">
         <v>24</v>
@@ -29719,7 +29722,7 @@
         <v>0</v>
       </c>
       <c r="W423" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="424" spans="1:23" x14ac:dyDescent="0.3">
@@ -29727,22 +29730,22 @@
         <v>22</v>
       </c>
       <c r="B424" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C424" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D424">
         <v>36</v>
       </c>
       <c r="E424" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F424" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="I424" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="J424" t="s">
         <v>24</v>
@@ -29789,22 +29792,22 @@
         <v>22</v>
       </c>
       <c r="B425" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C425" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D425">
         <v>37</v>
       </c>
       <c r="E425" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F425" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="I425" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J425" t="s">
         <v>24</v>
@@ -29843,7 +29846,7 @@
         <v>0</v>
       </c>
       <c r="W425" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="426" spans="1:23" x14ac:dyDescent="0.3">
@@ -29851,22 +29854,22 @@
         <v>22</v>
       </c>
       <c r="B426" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C426" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D426">
         <v>38</v>
       </c>
       <c r="E426" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F426" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I426" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="J426" t="s">
         <v>24</v>
@@ -29913,25 +29916,25 @@
         <v>22</v>
       </c>
       <c r="B427" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C427" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D427">
         <v>39</v>
       </c>
       <c r="E427" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F427" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I427" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="J427" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="K427">
         <v>20</v>
@@ -29967,10 +29970,10 @@
         <v>0</v>
       </c>
       <c r="V427" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="W427" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="428" spans="1:23" x14ac:dyDescent="0.3">
@@ -29978,25 +29981,25 @@
         <v>22</v>
       </c>
       <c r="B428" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C428" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D428">
         <v>40</v>
       </c>
       <c r="E428" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="F428" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="I428" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="J428" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="K428">
         <v>94</v>
@@ -30032,10 +30035,10 @@
         <v>0</v>
       </c>
       <c r="V428" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="W428" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="429" spans="1:23" x14ac:dyDescent="0.3">
@@ -30043,28 +30046,28 @@
         <v>22</v>
       </c>
       <c r="B429" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C429" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D429">
         <v>41</v>
       </c>
       <c r="E429" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F429" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G429" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="I429" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="J429" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="K429">
         <v>20</v>
@@ -30100,7 +30103,7 @@
         <v>0</v>
       </c>
       <c r="V429" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="W429" t="s">
         <v>27</v>
@@ -30111,22 +30114,22 @@
         <v>22</v>
       </c>
       <c r="B430" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C430" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D430">
         <v>42</v>
       </c>
       <c r="E430" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F430" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="I430" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="J430" t="s">
         <v>24</v>
@@ -30165,7 +30168,7 @@
         <v>0</v>
       </c>
       <c r="W430" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="431" spans="1:23" x14ac:dyDescent="0.3">
@@ -30173,22 +30176,22 @@
         <v>22</v>
       </c>
       <c r="B431" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C431" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D431">
         <v>43</v>
       </c>
       <c r="E431" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F431" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="I431" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="J431" t="s">
         <v>24</v>
@@ -30238,25 +30241,25 @@
         <v>22</v>
       </c>
       <c r="B432" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C432" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D432">
         <v>44</v>
       </c>
       <c r="E432" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F432" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="I432" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J432" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="K432">
         <v>81</v>
@@ -30292,7 +30295,7 @@
         <v>0</v>
       </c>
       <c r="W432" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="433" spans="1:23" x14ac:dyDescent="0.3">
@@ -30300,22 +30303,22 @@
         <v>22</v>
       </c>
       <c r="B433" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C433" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D433">
         <v>45</v>
       </c>
       <c r="E433" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F433" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="I433" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="J433" t="s">
         <v>370</v>
@@ -30362,25 +30365,25 @@
         <v>22</v>
       </c>
       <c r="B434" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C434" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D434">
         <v>46</v>
       </c>
       <c r="E434" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F434" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="I434" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J434" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="K434">
         <v>21</v>
@@ -30416,7 +30419,7 @@
         <v>0</v>
       </c>
       <c r="W434" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="435" spans="1:23" x14ac:dyDescent="0.3">
@@ -30424,22 +30427,22 @@
         <v>22</v>
       </c>
       <c r="B435" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C435" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D435">
         <v>47</v>
       </c>
       <c r="E435" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F435" t="s">
         <v>237</v>
       </c>
       <c r="I435" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="J435" t="s">
         <v>214</v>
@@ -30486,22 +30489,22 @@
         <v>22</v>
       </c>
       <c r="B436" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C436" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D436">
         <v>48</v>
       </c>
       <c r="E436" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F436" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="I436" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="J436" t="s">
         <v>24</v>
@@ -30548,22 +30551,22 @@
         <v>22</v>
       </c>
       <c r="B437" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C437" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D437">
         <v>49</v>
       </c>
       <c r="E437" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F437" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="I437" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="J437" t="s">
         <v>24</v>
@@ -30610,25 +30613,25 @@
         <v>22</v>
       </c>
       <c r="B438" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C438" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D438">
         <v>50</v>
       </c>
       <c r="E438" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F438" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="I438" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="J438" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="K438">
         <v>21</v>
@@ -30664,7 +30667,7 @@
         <v>0</v>
       </c>
       <c r="V438" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="W438" t="s">
         <v>27</v>
@@ -30675,22 +30678,22 @@
         <v>22</v>
       </c>
       <c r="B439" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C439" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D439">
         <v>51</v>
       </c>
       <c r="E439" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F439" t="s">
         <v>292</v>
       </c>
       <c r="I439" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="J439" t="s">
         <v>416</v>
@@ -30732,7 +30735,7 @@
         <v>417</v>
       </c>
       <c r="W439" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="440" spans="1:23" x14ac:dyDescent="0.3">
@@ -30740,22 +30743,22 @@
         <v>22</v>
       </c>
       <c r="B440" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C440" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D440">
         <v>52</v>
       </c>
       <c r="E440" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F440" t="s">
         <v>55</v>
       </c>
       <c r="I440" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J440" t="s">
         <v>305</v>
@@ -30802,22 +30805,22 @@
         <v>22</v>
       </c>
       <c r="B441" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C441" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D441">
         <v>53</v>
       </c>
       <c r="E441" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F441" t="s">
         <v>237</v>
       </c>
       <c r="I441" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="J441" t="s">
         <v>227</v>
@@ -30864,22 +30867,22 @@
         <v>22</v>
       </c>
       <c r="B442" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C442" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D442">
         <v>54</v>
       </c>
       <c r="E442" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F442" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="I442" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="J442" t="s">
         <v>227</v>
@@ -30918,7 +30921,7 @@
         <v>0</v>
       </c>
       <c r="W442" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="443" spans="1:23" x14ac:dyDescent="0.3">
@@ -30926,25 +30929,25 @@
         <v>22</v>
       </c>
       <c r="B443" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C443" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D443">
         <v>55</v>
       </c>
       <c r="E443" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F443" t="s">
         <v>55</v>
       </c>
       <c r="I443" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="J443" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="K443">
         <v>8</v>
@@ -30988,25 +30991,25 @@
         <v>22</v>
       </c>
       <c r="B444" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C444" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D444">
         <v>56</v>
       </c>
       <c r="E444" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F444" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="I444" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="J444" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="K444">
         <v>338</v>
@@ -31042,7 +31045,7 @@
         <v>0</v>
       </c>
       <c r="V444" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="W444" t="s">
         <v>27</v>
@@ -31053,22 +31056,22 @@
         <v>22</v>
       </c>
       <c r="B445" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C445" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D445">
         <v>57</v>
       </c>
       <c r="E445" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F445" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="I445" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="J445" t="s">
         <v>290</v>
@@ -31107,7 +31110,7 @@
         <v>0</v>
       </c>
       <c r="W445" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="446" spans="1:23" x14ac:dyDescent="0.3">
@@ -31115,25 +31118,25 @@
         <v>22</v>
       </c>
       <c r="B446" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C446" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D446">
         <v>58</v>
       </c>
       <c r="E446" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F446" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="I446" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="J446" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="K446">
         <v>13</v>
@@ -31169,10 +31172,10 @@
         <v>0</v>
       </c>
       <c r="V446" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="W446" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="447" spans="1:23" x14ac:dyDescent="0.3">
@@ -31180,22 +31183,22 @@
         <v>22</v>
       </c>
       <c r="B447" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C447" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D447">
         <v>59</v>
       </c>
       <c r="E447" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F447" t="s">
         <v>55</v>
       </c>
       <c r="I447" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="J447" t="s">
         <v>227</v>
@@ -31242,25 +31245,25 @@
         <v>22</v>
       </c>
       <c r="B448" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C448" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D448">
         <v>60</v>
       </c>
       <c r="E448" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F448" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="I448" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="J448" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="K448">
         <v>33</v>
@@ -31296,7 +31299,7 @@
         <v>0</v>
       </c>
       <c r="W448" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="449" spans="1:23" x14ac:dyDescent="0.3">
@@ -31304,22 +31307,22 @@
         <v>22</v>
       </c>
       <c r="B449" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C449" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D449">
         <v>61</v>
       </c>
       <c r="E449" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F449" t="s">
         <v>237</v>
       </c>
       <c r="I449" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="J449" t="s">
         <v>227</v>
@@ -31366,16 +31369,16 @@
         <v>22</v>
       </c>
       <c r="B450" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C450" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D450">
         <v>1</v>
       </c>
       <c r="E450" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="K450">
         <v>54</v>
@@ -31395,16 +31398,16 @@
         <v>22</v>
       </c>
       <c r="B451" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C451" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D451">
         <v>1</v>
       </c>
       <c r="E451" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="K451">
         <v>50</v>
@@ -31424,16 +31427,16 @@
         <v>22</v>
       </c>
       <c r="B452" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C452" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D452">
         <v>1</v>
       </c>
       <c r="E452" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="K452">
         <v>4</v>
@@ -31453,16 +31456,16 @@
         <v>22</v>
       </c>
       <c r="B453" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C453" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="D453">
         <v>1</v>
       </c>
       <c r="E453" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="K453">
         <v>61</v>
@@ -31482,16 +31485,16 @@
         <v>22</v>
       </c>
       <c r="B454" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C454" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D454">
         <v>1</v>
       </c>
       <c r="E454" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="K454">
         <v>56</v>
@@ -31511,16 +31514,16 @@
         <v>22</v>
       </c>
       <c r="B455" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C455" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D455">
         <v>1</v>
       </c>
       <c r="E455" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="K455">
         <v>35</v>
@@ -31540,16 +31543,16 @@
         <v>22</v>
       </c>
       <c r="B456" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C456" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D456">
         <v>1</v>
       </c>
       <c r="E456" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="K456">
         <v>29</v>
@@ -31569,16 +31572,16 @@
         <v>22</v>
       </c>
       <c r="B457" t="s">
-        <v>960</v>
+        <v>566</v>
       </c>
       <c r="C457" t="s">
+        <v>891</v>
+      </c>
+      <c r="D457">
+        <v>1</v>
+      </c>
+      <c r="E457" t="s">
         <v>890</v>
-      </c>
-      <c r="D457">
-        <v>1</v>
-      </c>
-      <c r="E457" t="s">
-        <v>889</v>
       </c>
       <c r="K457">
         <v>135</v>
@@ -31598,19 +31601,19 @@
         <v>22</v>
       </c>
       <c r="B458" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C458" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D458">
         <v>1</v>
       </c>
       <c r="E458" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="F458" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="K458">
         <v>339</v>
@@ -31630,19 +31633,19 @@
         <v>22</v>
       </c>
       <c r="B459" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C459" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D459">
         <v>2</v>
       </c>
       <c r="E459" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F459" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="K459">
         <v>19</v>
@@ -31662,19 +31665,19 @@
         <v>22</v>
       </c>
       <c r="B460" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C460" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D460">
         <v>3</v>
       </c>
       <c r="E460" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="F460" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="K460">
         <v>326</v>
@@ -31694,19 +31697,19 @@
         <v>22</v>
       </c>
       <c r="B461" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C461" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D461">
         <v>4</v>
       </c>
       <c r="E461" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="F461" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="K461">
         <v>12</v>
@@ -31726,19 +31729,19 @@
         <v>22</v>
       </c>
       <c r="B462" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C462" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D462">
         <v>5</v>
       </c>
       <c r="E462" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F462" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="K462">
         <v>97</v>
@@ -31758,19 +31761,19 @@
         <v>22</v>
       </c>
       <c r="B463" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C463" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D463">
         <v>6</v>
       </c>
       <c r="E463" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F463" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="K463">
         <v>2</v>
@@ -31790,19 +31793,19 @@
         <v>22</v>
       </c>
       <c r="B464" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C464" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D464">
         <v>7</v>
       </c>
       <c r="E464" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="F464" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="K464">
         <v>16</v>
@@ -31822,19 +31825,19 @@
         <v>22</v>
       </c>
       <c r="B465" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C465" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D465">
         <v>8</v>
       </c>
       <c r="E465" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="F465" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="K465">
         <v>2</v>
@@ -31854,19 +31857,19 @@
         <v>22</v>
       </c>
       <c r="B466" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C466" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D466">
         <v>9</v>
       </c>
       <c r="E466" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="F466" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="K466">
         <v>25</v>
@@ -31886,19 +31889,19 @@
         <v>22</v>
       </c>
       <c r="B467" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C467" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D467">
         <v>10</v>
       </c>
       <c r="E467" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="F467" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="K467">
         <v>49</v>
@@ -31918,19 +31921,19 @@
         <v>22</v>
       </c>
       <c r="B468" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C468" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D468">
         <v>11</v>
       </c>
       <c r="E468" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="F468" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="K468">
         <v>3</v>
@@ -31950,19 +31953,19 @@
         <v>22</v>
       </c>
       <c r="B469" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C469" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D469">
         <v>12</v>
       </c>
       <c r="E469" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="F469" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="K469">
         <v>25</v>
@@ -31982,19 +31985,19 @@
         <v>22</v>
       </c>
       <c r="B470" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C470" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D470">
         <v>13</v>
       </c>
       <c r="E470" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="F470" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="K470">
         <v>15</v>
@@ -32014,19 +32017,19 @@
         <v>22</v>
       </c>
       <c r="B471" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C471" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D471">
         <v>14</v>
       </c>
       <c r="E471" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="F471" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="K471">
         <v>8</v>
@@ -32046,19 +32049,19 @@
         <v>22</v>
       </c>
       <c r="B472" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C472" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D472">
         <v>1</v>
       </c>
       <c r="E472" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="F472" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="K472">
         <v>56</v>
@@ -32078,19 +32081,19 @@
         <v>22</v>
       </c>
       <c r="B473" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C473" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D473">
         <v>2</v>
       </c>
       <c r="E473" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F473" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="K473">
         <v>65</v>
@@ -32110,19 +32113,19 @@
         <v>22</v>
       </c>
       <c r="B474" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C474" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D474">
         <v>3</v>
       </c>
       <c r="E474" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="F474" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="K474">
         <v>54</v>
@@ -32142,19 +32145,19 @@
         <v>22</v>
       </c>
       <c r="B475" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C475" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D475">
         <v>4</v>
       </c>
       <c r="E475" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="F475" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="K475">
         <v>55</v>
@@ -32174,19 +32177,19 @@
         <v>22</v>
       </c>
       <c r="B476" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C476" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D476">
         <v>5</v>
       </c>
       <c r="E476" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F476" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="K476">
         <v>51</v>
@@ -32206,19 +32209,19 @@
         <v>22</v>
       </c>
       <c r="B477" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C477" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D477">
         <v>6</v>
       </c>
       <c r="E477" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="F477" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="K477">
         <v>58</v>
@@ -32238,19 +32241,19 @@
         <v>22</v>
       </c>
       <c r="B478" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C478" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D478">
         <v>7</v>
       </c>
       <c r="E478" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F478" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="K478">
         <v>68</v>
@@ -32270,19 +32273,19 @@
         <v>22</v>
       </c>
       <c r="B479" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C479" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D479">
         <v>1</v>
       </c>
       <c r="E479" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="F479" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="K479">
         <v>6</v>
@@ -32302,19 +32305,19 @@
         <v>22</v>
       </c>
       <c r="B480" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C480" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="D480">
         <v>2</v>
       </c>
       <c r="E480" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="F480" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="K480">
         <v>132</v>
@@ -32334,19 +32337,19 @@
         <v>22</v>
       </c>
       <c r="B481" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C481" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D481">
         <v>3</v>
       </c>
       <c r="E481" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="F481" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="K481">
         <v>82</v>
@@ -32366,19 +32369,19 @@
         <v>22</v>
       </c>
       <c r="B482" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C482" t="s">
-        <v>914</v>
+        <v>919</v>
       </c>
       <c r="D482">
         <v>4</v>
       </c>
       <c r="E482" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="F482" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="K482">
         <v>142</v>
@@ -32398,19 +32401,19 @@
         <v>22</v>
       </c>
       <c r="B483" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C483" t="s">
-        <v>914</v>
+        <v>920</v>
       </c>
       <c r="D483">
         <v>5</v>
       </c>
       <c r="E483" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="F483" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="K483">
         <v>14</v>
@@ -32430,19 +32433,19 @@
         <v>22</v>
       </c>
       <c r="B484" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C484" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="D484">
         <v>6</v>
       </c>
       <c r="E484" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="F484" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="K484">
         <v>82</v>
@@ -32462,19 +32465,19 @@
         <v>22</v>
       </c>
       <c r="B485" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C485" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="D485">
         <v>7</v>
       </c>
       <c r="E485" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="F485" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="K485">
         <v>0</v>
@@ -32494,19 +32497,19 @@
         <v>22</v>
       </c>
       <c r="B486" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C486" t="s">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="D486">
         <v>8</v>
       </c>
       <c r="E486" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="F486" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="K486">
         <v>0</v>
@@ -32526,10 +32529,10 @@
         <v>22</v>
       </c>
       <c r="B487" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C487" t="s">
-        <v>914</v>
+        <v>522</v>
       </c>
       <c r="D487">
         <v>9</v>
@@ -32558,19 +32561,19 @@
         <v>22</v>
       </c>
       <c r="B488" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C488" t="s">
-        <v>914</v>
+        <v>924</v>
       </c>
       <c r="D488">
         <v>10</v>
       </c>
       <c r="E488" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="F488" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="K488">
         <v>9</v>
@@ -32590,10 +32593,10 @@
         <v>22</v>
       </c>
       <c r="B489" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C489" t="s">
-        <v>914</v>
+        <v>453</v>
       </c>
       <c r="D489">
         <v>11</v>
@@ -32622,19 +32625,19 @@
         <v>22</v>
       </c>
       <c r="B490" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C490" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="D490">
         <v>12</v>
       </c>
       <c r="E490" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F490" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="K490">
         <v>0</v>
@@ -32654,19 +32657,19 @@
         <v>22</v>
       </c>
       <c r="B491" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C491" t="s">
-        <v>914</v>
+        <v>926</v>
       </c>
       <c r="D491">
         <v>13</v>
       </c>
       <c r="E491" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F491" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="K491">
         <v>22</v>
@@ -32686,19 +32689,19 @@
         <v>22</v>
       </c>
       <c r="B492" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C492" t="s">
-        <v>914</v>
+        <v>927</v>
       </c>
       <c r="D492">
         <v>14</v>
       </c>
       <c r="E492" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="F492" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="K492">
         <v>0</v>
@@ -32718,19 +32721,19 @@
         <v>22</v>
       </c>
       <c r="B493" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C493" t="s">
-        <v>914</v>
+        <v>928</v>
       </c>
       <c r="D493">
         <v>15</v>
       </c>
       <c r="E493" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="F493" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="K493">
         <v>0</v>
@@ -32750,19 +32753,19 @@
         <v>22</v>
       </c>
       <c r="B494" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C494" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D494">
         <v>1</v>
       </c>
       <c r="E494" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="F494" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="K494">
         <v>106</v>
@@ -32782,19 +32785,19 @@
         <v>22</v>
       </c>
       <c r="B495" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C495" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="D495">
         <v>2</v>
       </c>
       <c r="E495" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="F495" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="K495">
         <v>30</v>
@@ -32814,19 +32817,19 @@
         <v>22</v>
       </c>
       <c r="B496" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C496" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="D496">
         <v>3</v>
       </c>
       <c r="E496" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F496" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="K496">
         <v>42</v>
@@ -32846,19 +32849,19 @@
         <v>22</v>
       </c>
       <c r="B497" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C497" t="s">
-        <v>928</v>
+        <v>933</v>
       </c>
       <c r="D497">
         <v>4</v>
       </c>
       <c r="E497" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="F497" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="K497">
         <v>0</v>
@@ -32878,10 +32881,10 @@
         <v>22</v>
       </c>
       <c r="B498" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C498" t="s">
-        <v>928</v>
+        <v>28</v>
       </c>
       <c r="D498">
         <v>5</v>
@@ -32910,19 +32913,19 @@
         <v>22</v>
       </c>
       <c r="B499" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C499" t="s">
-        <v>928</v>
+        <v>934</v>
       </c>
       <c r="D499">
         <v>6</v>
       </c>
       <c r="E499" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="F499" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="K499">
         <v>5</v>
@@ -32942,19 +32945,19 @@
         <v>22</v>
       </c>
       <c r="B500" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C500" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="D500">
         <v>7</v>
       </c>
       <c r="E500" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="F500" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="K500">
         <v>80</v>
@@ -32974,19 +32977,19 @@
         <v>22</v>
       </c>
       <c r="B501" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C501" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D501">
         <v>8</v>
       </c>
       <c r="E501" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="F501" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="K501">
         <v>50</v>
@@ -33006,19 +33009,19 @@
         <v>22</v>
       </c>
       <c r="B502" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C502" t="s">
-        <v>928</v>
+        <v>937</v>
       </c>
       <c r="D502">
         <v>9</v>
       </c>
       <c r="E502" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="F502" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="K502">
         <v>41</v>
@@ -33038,19 +33041,19 @@
         <v>22</v>
       </c>
       <c r="B503" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C503" t="s">
-        <v>928</v>
+        <v>938</v>
       </c>
       <c r="D503">
         <v>10</v>
       </c>
       <c r="E503" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F503" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="K503">
         <v>0</v>
@@ -33070,19 +33073,19 @@
         <v>22</v>
       </c>
       <c r="B504" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C504" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="D504">
         <v>11</v>
       </c>
       <c r="E504" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="F504" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="K504">
         <v>59</v>
@@ -33102,19 +33105,19 @@
         <v>22</v>
       </c>
       <c r="B505" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C505" t="s">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="D505">
         <v>12</v>
       </c>
       <c r="E505" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F505" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="K505">
         <v>15</v>
@@ -33134,19 +33137,19 @@
         <v>22</v>
       </c>
       <c r="B506" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C506" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="D506">
         <v>13</v>
       </c>
       <c r="E506" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="F506" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="K506">
         <v>0</v>
@@ -33166,19 +33169,19 @@
         <v>22</v>
       </c>
       <c r="B507" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C507" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="D507">
         <v>14</v>
       </c>
       <c r="E507" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="F507" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="K507">
         <v>20</v>
@@ -33198,19 +33201,19 @@
         <v>22</v>
       </c>
       <c r="B508" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C508" t="s">
-        <v>928</v>
+        <v>943</v>
       </c>
       <c r="D508">
         <v>15</v>
       </c>
       <c r="E508" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="F508" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="K508">
         <v>94</v>
@@ -33282,7 +33285,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -33330,7 +33333,7 @@
         <v>21</v>
       </c>
       <c r="X1" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -33338,7 +33341,7 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>29</v>
@@ -33353,7 +33356,7 @@
         <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="J2" t="s">
         <v>305</v>
@@ -33400,7 +33403,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
         <v>29</v>
@@ -33468,7 +33471,7 @@
         <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
         <v>29</v>
@@ -33536,7 +33539,7 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
         <v>29</v>
@@ -33604,7 +33607,7 @@
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
@@ -33625,7 +33628,7 @@
         <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="K6">
         <v>12</v>
@@ -33672,7 +33675,7 @@
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
         <v>29</v>
@@ -33740,7 +33743,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
@@ -33755,7 +33758,7 @@
         <v>50</v>
       </c>
       <c r="J8" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -33796,7 +33799,7 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>29</v>
@@ -33864,7 +33867,7 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -33882,7 +33885,7 @@
         <v>294</v>
       </c>
       <c r="J10" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -33923,7 +33926,7 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
@@ -33938,7 +33941,7 @@
         <v>55</v>
       </c>
       <c r="I11" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="J11" t="s">
         <v>227</v>
@@ -33985,7 +33988,7 @@
         <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
@@ -34044,7 +34047,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
         <v>58</v>
@@ -34065,7 +34068,7 @@
         <v>61</v>
       </c>
       <c r="J13" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="K13">
         <v>36</v>
@@ -34112,7 +34115,7 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -34130,7 +34133,7 @@
         <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K14">
         <v>12</v>
@@ -34174,7 +34177,7 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
         <v>58</v>
@@ -34192,7 +34195,7 @@
         <v>66</v>
       </c>
       <c r="J15" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -34236,7 +34239,7 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>58</v>
@@ -34254,7 +34257,7 @@
         <v>69</v>
       </c>
       <c r="J16" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="K16">
         <v>6</v>
@@ -34298,7 +34301,7 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -34316,7 +34319,7 @@
         <v>71</v>
       </c>
       <c r="J17" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K17">
         <v>12</v>
@@ -34360,7 +34363,7 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
         <v>58</v>
@@ -34378,7 +34381,7 @@
         <v>73</v>
       </c>
       <c r="J18" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K18">
         <v>3</v>
@@ -34422,7 +34425,7 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
         <v>58</v>
@@ -34440,7 +34443,7 @@
         <v>76</v>
       </c>
       <c r="J19" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -34484,7 +34487,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
         <v>58</v>
@@ -34502,7 +34505,7 @@
         <v>78</v>
       </c>
       <c r="J20" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K20">
         <v>3</v>
@@ -34546,7 +34549,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
@@ -34564,7 +34567,7 @@
         <v>79</v>
       </c>
       <c r="J21" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="K21">
         <v>3</v>
@@ -34608,7 +34611,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
         <v>58</v>
@@ -34626,7 +34629,7 @@
         <v>80</v>
       </c>
       <c r="J22" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="K22">
         <v>3</v>
@@ -34670,7 +34673,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
         <v>81</v>
@@ -34691,7 +34694,7 @@
         <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="K23">
         <v>54</v>
@@ -34738,7 +34741,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C24" t="s">
         <v>81</v>
@@ -34756,7 +34759,7 @@
         <v>84</v>
       </c>
       <c r="J24" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K24">
         <v>9</v>
@@ -34800,7 +34803,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
         <v>81</v>
@@ -34818,7 +34821,7 @@
         <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -34862,7 +34865,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>81</v>
@@ -34880,7 +34883,7 @@
         <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -34924,7 +34927,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C27" t="s">
         <v>81</v>
@@ -34942,7 +34945,7 @@
         <v>90</v>
       </c>
       <c r="J27" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="K27">
         <v>9</v>
@@ -34986,7 +34989,7 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C28" t="s">
         <v>81</v>
@@ -35004,7 +35007,7 @@
         <v>92</v>
       </c>
       <c r="J28" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="K28">
         <v>6</v>
@@ -35048,7 +35051,7 @@
         <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C29" t="s">
         <v>81</v>
@@ -35066,7 +35069,7 @@
         <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -35110,7 +35113,7 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C30" t="s">
         <v>81</v>
@@ -35128,7 +35131,7 @@
         <v>96</v>
       </c>
       <c r="J30" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="K30">
         <v>4</v>
@@ -35172,7 +35175,7 @@
         <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
         <v>81</v>
@@ -35190,7 +35193,7 @@
         <v>97</v>
       </c>
       <c r="J31" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K31">
         <v>3</v>
@@ -35234,7 +35237,7 @@
         <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C32" t="s">
         <v>81</v>
@@ -35252,7 +35255,7 @@
         <v>98</v>
       </c>
       <c r="J32" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K32">
         <v>3</v>
@@ -35296,7 +35299,7 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C33" t="s">
         <v>81</v>
@@ -35314,7 +35317,7 @@
         <v>99</v>
       </c>
       <c r="J33" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="K33">
         <v>3</v>
@@ -35358,7 +35361,7 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
         <v>58</v>
@@ -35379,7 +35382,7 @@
         <v>102</v>
       </c>
       <c r="J34" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="K34">
         <v>33</v>
@@ -35426,7 +35429,7 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
         <v>58</v>
@@ -35444,7 +35447,7 @@
         <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="K35">
         <v>2.5</v>
@@ -35488,7 +35491,7 @@
         <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
         <v>58</v>
@@ -35506,7 +35509,7 @@
         <v>106</v>
       </c>
       <c r="J36" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K36">
         <v>3</v>
@@ -35550,7 +35553,7 @@
         <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
         <v>58</v>
@@ -35568,7 +35571,7 @@
         <v>107</v>
       </c>
       <c r="J37" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="K37">
         <v>3</v>
@@ -35612,7 +35615,7 @@
         <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
         <v>81</v>
@@ -35633,7 +35636,7 @@
         <v>109</v>
       </c>
       <c r="J38" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="K38">
         <v>30</v>
@@ -35680,7 +35683,7 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C39" t="s">
         <v>81</v>
@@ -35698,7 +35701,7 @@
         <v>110</v>
       </c>
       <c r="J39" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -35742,7 +35745,7 @@
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
         <v>81</v>
@@ -35760,7 +35763,7 @@
         <v>111</v>
       </c>
       <c r="J40" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="K40">
         <v>1.5</v>
@@ -35804,7 +35807,7 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C41" t="s">
         <v>81</v>
@@ -35822,7 +35825,7 @@
         <v>110</v>
       </c>
       <c r="J41" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -35866,7 +35869,7 @@
         <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
         <v>81</v>
@@ -35884,7 +35887,7 @@
         <v>113</v>
       </c>
       <c r="J42" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="K42">
         <v>3</v>
@@ -35928,7 +35931,7 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
         <v>114</v>
@@ -35987,7 +35990,7 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
         <v>114</v>
@@ -36046,7 +36049,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C45" t="s">
         <v>114</v>
@@ -36105,7 +36108,7 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
         <v>114</v>
@@ -36164,7 +36167,7 @@
         <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
         <v>114</v>
@@ -36179,7 +36182,7 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="K47">
         <v>4</v>
@@ -36223,7 +36226,7 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
         <v>114</v>
@@ -36282,7 +36285,7 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
         <v>114</v>
@@ -36341,7 +36344,7 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
         <v>114</v>
@@ -36400,7 +36403,7 @@
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C51" t="s">
         <v>114</v>
@@ -36459,7 +36462,7 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
         <v>114</v>
@@ -36607,7 +36610,7 @@
         <v>134</v>
       </c>
       <c r="J54" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="K54">
         <v>3</v>
@@ -36935,7 +36938,7 @@
         <v>148</v>
       </c>
       <c r="J59" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K59">
         <v>6</v>
@@ -37000,7 +37003,7 @@
         <v>149</v>
       </c>
       <c r="J60" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="K60">
         <v>6</v>
@@ -37047,16 +37050,16 @@
         <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D61">
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F61" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="K61">
         <v>3</v>
@@ -37097,16 +37100,16 @@
         <v>126</v>
       </c>
       <c r="C62" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D62">
         <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F62" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="K62">
         <v>14</v>
@@ -37147,16 +37150,16 @@
         <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D63">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F63" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="K63">
         <v>3</v>
@@ -37194,7 +37197,7 @@
         <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C64" t="s">
         <v>150</v>
@@ -37203,13 +37206,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F64" t="s">
         <v>151</v>
       </c>
       <c r="I64" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="J64" t="s">
         <v>305</v>
@@ -37259,7 +37262,7 @@
         <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C65" t="s">
         <v>150</v>
@@ -37280,7 +37283,7 @@
         <v>154</v>
       </c>
       <c r="J65" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="K65">
         <v>12</v>
@@ -37327,7 +37330,7 @@
         <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C66" t="s">
         <v>150</v>
@@ -37392,7 +37395,7 @@
         <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
         <v>150</v>
@@ -37457,7 +37460,7 @@
         <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C68" t="s">
         <v>150</v>
@@ -37478,7 +37481,7 @@
         <v>161</v>
       </c>
       <c r="J68" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K68">
         <v>9</v>
@@ -37525,7 +37528,7 @@
         <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C69" t="s">
         <v>150</v>
@@ -37546,7 +37549,7 @@
         <v>161</v>
       </c>
       <c r="J69" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K69">
         <v>9</v>
@@ -37593,7 +37596,7 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
         <v>150</v>
@@ -37614,7 +37617,7 @@
         <v>161</v>
       </c>
       <c r="J70" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="K70">
         <v>15</v>
@@ -37661,7 +37664,7 @@
         <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C71" t="s">
         <v>150</v>
@@ -37726,7 +37729,7 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C72" t="s">
         <v>150</v>
@@ -37741,7 +37744,7 @@
         <v>19</v>
       </c>
       <c r="I72" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="J72" t="s">
         <v>227</v>
@@ -37791,7 +37794,7 @@
         <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
         <v>166</v>
@@ -37849,7 +37852,7 @@
         <v>0</v>
       </c>
       <c r="V73" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="W73" t="s">
         <v>27</v>
@@ -37860,7 +37863,7 @@
         <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C74" t="s">
         <v>166</v>
@@ -37878,7 +37881,7 @@
         <v>170</v>
       </c>
       <c r="J74" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="K74">
         <v>6</v>
@@ -37922,7 +37925,7 @@
         <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C75" t="s">
         <v>166</v>
@@ -37940,7 +37943,7 @@
         <v>171</v>
       </c>
       <c r="J75" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="K75">
         <v>15</v>
@@ -37984,7 +37987,7 @@
         <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C76" t="s">
         <v>166</v>
@@ -38002,7 +38005,7 @@
         <v>173</v>
       </c>
       <c r="J76" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K76">
         <v>12</v>
@@ -38046,7 +38049,7 @@
         <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C77" t="s">
         <v>166</v>
@@ -38064,7 +38067,7 @@
         <v>175</v>
       </c>
       <c r="J77" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="K77">
         <v>3</v>
@@ -38108,7 +38111,7 @@
         <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C78" t="s">
         <v>166</v>
@@ -38126,7 +38129,7 @@
         <v>177</v>
       </c>
       <c r="J78" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K78">
         <v>12</v>
@@ -38170,7 +38173,7 @@
         <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C79" t="s">
         <v>166</v>
@@ -38188,7 +38191,7 @@
         <v>179</v>
       </c>
       <c r="J79" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="K79">
         <v>12</v>
@@ -38232,7 +38235,7 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
         <v>166</v>
@@ -38250,7 +38253,7 @@
         <v>181</v>
       </c>
       <c r="J80" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="K80">
         <v>9</v>
@@ -38294,7 +38297,7 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C81" t="s">
         <v>182</v>
@@ -38315,7 +38318,7 @@
         <v>184</v>
       </c>
       <c r="J81" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="K81">
         <v>36</v>
@@ -38351,7 +38354,7 @@
         <v>0</v>
       </c>
       <c r="V81" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="W81" t="s">
         <v>27</v>
@@ -38362,7 +38365,7 @@
         <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C82" t="s">
         <v>182</v>
@@ -38380,7 +38383,7 @@
         <v>185</v>
       </c>
       <c r="J82" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="K82">
         <v>3</v>
@@ -38424,7 +38427,7 @@
         <v>22</v>
       </c>
       <c r="B83" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C83" t="s">
         <v>182</v>
@@ -38442,7 +38445,7 @@
         <v>187</v>
       </c>
       <c r="J83" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="K83">
         <v>3</v>
@@ -38486,7 +38489,7 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C84" t="s">
         <v>182</v>
@@ -38504,7 +38507,7 @@
         <v>189</v>
       </c>
       <c r="J84" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="K84">
         <v>6</v>
@@ -38548,7 +38551,7 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C85" t="s">
         <v>190</v>
@@ -38607,7 +38610,7 @@
         <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C86" t="s">
         <v>190</v>
@@ -38666,7 +38669,7 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C87" t="s">
         <v>190</v>
@@ -38725,7 +38728,7 @@
         <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
         <v>190</v>
@@ -38784,7 +38787,7 @@
         <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C89" t="s">
         <v>190</v>
@@ -38843,19 +38846,19 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
       <c r="E90" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F90" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="K90">
         <v>82</v>
@@ -38893,19 +38896,19 @@
         <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C91" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D91">
         <v>1</v>
       </c>
       <c r="E91" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F91" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="K91">
         <v>32</v>
@@ -38943,19 +38946,19 @@
         <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>960</v>
+        <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D92">
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F92" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="K92">
         <v>9</v>

--- a/input/Anjar_manning.xlsx
+++ b/input/Anjar_manning.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0200711\Desktop\sahith_welspun_own\Manning_FInal_sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD021ED-94B1-4B9E-A38F-3C14E9D33586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963D8663-2511-47F1-A1A2-E4DC3C13C718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{AE9D74B8-CDDF-4B26-A051-7E6D95F9E466}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4643" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="853">
   <si>
     <t>Location</t>
   </si>
@@ -14617,29 +14617,26 @@
       <c r="J186" t="s">
         <v>298</v>
       </c>
-      <c r="K186">
+      <c r="L186">
         <v>12</v>
       </c>
-      <c r="L186" t="s">
-        <v>25</v>
-      </c>
-      <c r="M186">
-        <v>0</v>
+      <c r="M186" t="s">
+        <v>25</v>
       </c>
       <c r="N186">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O186">
         <v>12</v>
       </c>
       <c r="P186">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R186">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S186">
         <v>4</v>
@@ -14648,9 +14645,12 @@
         <v>4</v>
       </c>
       <c r="U186">
-        <v>0</v>
-      </c>
-      <c r="W186" t="s">
+        <v>4</v>
+      </c>
+      <c r="V186">
+        <v>0</v>
+      </c>
+      <c r="X186" t="s">
         <v>74</v>
       </c>
     </row>
@@ -14685,29 +14685,26 @@
       <c r="J187" t="s">
         <v>729</v>
       </c>
-      <c r="K187">
+      <c r="L187">
         <v>18</v>
       </c>
-      <c r="L187" t="s">
-        <v>25</v>
-      </c>
-      <c r="M187">
-        <v>0</v>
+      <c r="M187" t="s">
+        <v>25</v>
       </c>
       <c r="N187">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O187">
         <v>18</v>
       </c>
       <c r="P187">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q187">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R187">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S187">
         <v>6</v>
@@ -14716,9 +14713,12 @@
         <v>6</v>
       </c>
       <c r="U187">
-        <v>0</v>
-      </c>
-      <c r="W187" t="s">
+        <v>6</v>
+      </c>
+      <c r="V187">
+        <v>0</v>
+      </c>
+      <c r="X187" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14750,29 +14750,26 @@
       <c r="J188" t="s">
         <v>733</v>
       </c>
-      <c r="K188">
+      <c r="L188">
         <v>93</v>
       </c>
-      <c r="L188" t="s">
-        <v>25</v>
-      </c>
-      <c r="M188">
-        <v>0</v>
+      <c r="M188" t="s">
+        <v>25</v>
       </c>
       <c r="N188">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="O188">
         <v>93</v>
       </c>
       <c r="P188">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="Q188">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R188">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S188">
         <v>31</v>
@@ -14781,9 +14778,12 @@
         <v>31</v>
       </c>
       <c r="U188">
-        <v>0</v>
-      </c>
-      <c r="W188" t="s">
+        <v>31</v>
+      </c>
+      <c r="V188">
+        <v>0</v>
+      </c>
+      <c r="X188" t="s">
         <v>27</v>
       </c>
     </row>
@@ -14815,29 +14815,26 @@
       <c r="J189" t="s">
         <v>275</v>
       </c>
-      <c r="K189">
+      <c r="L189">
         <v>9</v>
       </c>
-      <c r="L189" t="s">
-        <v>25</v>
-      </c>
-      <c r="M189">
-        <v>0</v>
+      <c r="M189" t="s">
+        <v>25</v>
       </c>
       <c r="N189">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O189">
         <v>9</v>
       </c>
       <c r="P189">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q189">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R189">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S189">
         <v>3</v>
@@ -14846,9 +14843,12 @@
         <v>3</v>
       </c>
       <c r="U189">
-        <v>0</v>
-      </c>
-      <c r="W189" t="s">
+        <v>3</v>
+      </c>
+      <c r="V189">
+        <v>0</v>
+      </c>
+      <c r="X189" t="s">
         <v>74</v>
       </c>
     </row>
@@ -14880,14 +14880,11 @@
       <c r="J190" t="s">
         <v>738</v>
       </c>
-      <c r="K190">
-        <v>0</v>
-      </c>
-      <c r="L190" t="s">
-        <v>25</v>
-      </c>
-      <c r="M190">
-        <v>0</v>
+      <c r="L190">
+        <v>0</v>
+      </c>
+      <c r="M190" t="s">
+        <v>25</v>
       </c>
       <c r="N190">
         <v>0</v>
@@ -14896,10 +14893,10 @@
         <v>0</v>
       </c>
       <c r="P190">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q190">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -14913,7 +14910,10 @@
       <c r="U190">
         <v>0</v>
       </c>
-      <c r="W190" t="s">
+      <c r="V190">
+        <v>0</v>
+      </c>
+      <c r="X190" t="s">
         <v>74</v>
       </c>
     </row>
@@ -14945,29 +14945,26 @@
       <c r="J191" t="s">
         <v>275</v>
       </c>
-      <c r="K191">
+      <c r="L191">
         <v>9</v>
       </c>
-      <c r="L191" t="s">
-        <v>25</v>
-      </c>
-      <c r="M191">
-        <v>0</v>
+      <c r="M191" t="s">
+        <v>25</v>
       </c>
       <c r="N191">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O191">
         <v>9</v>
       </c>
       <c r="P191">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R191">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S191">
         <v>3</v>
@@ -14976,10 +14973,10 @@
         <v>3</v>
       </c>
       <c r="U191">
-        <v>0</v>
-      </c>
-      <c r="W191" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="V191">
+        <v>0</v>
       </c>
       <c r="X191" t="s">
         <v>27</v>
@@ -15013,41 +15010,38 @@
       <c r="J192" t="s">
         <v>743</v>
       </c>
-      <c r="K192">
+      <c r="L192">
         <v>4</v>
       </c>
-      <c r="L192" t="s">
-        <v>25</v>
-      </c>
-      <c r="M192">
-        <v>0</v>
+      <c r="M192" t="s">
+        <v>25</v>
       </c>
       <c r="N192">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O192">
         <v>4</v>
       </c>
       <c r="P192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q192">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S192">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T192">
         <v>1</v>
       </c>
       <c r="U192">
-        <v>0</v>
-      </c>
-      <c r="W192" t="s">
-        <v>74</v>
+        <v>1</v>
+      </c>
+      <c r="V192">
+        <v>0</v>
       </c>
       <c r="X192" t="s">
         <v>74</v>
@@ -15081,17 +15075,14 @@
       <c r="J193" t="s">
         <v>227</v>
       </c>
-      <c r="K193">
-        <v>3</v>
-      </c>
-      <c r="L193" t="s">
-        <v>25</v>
-      </c>
-      <c r="M193">
-        <v>0</v>
+      <c r="L193">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>25</v>
       </c>
       <c r="N193">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O193">
         <v>3</v>
@@ -15100,10 +15091,10 @@
         <v>3</v>
       </c>
       <c r="Q193">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S193">
         <v>1</v>
@@ -15112,10 +15103,10 @@
         <v>1</v>
       </c>
       <c r="U193">
-        <v>0</v>
-      </c>
-      <c r="W193" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="V193">
+        <v>0</v>
       </c>
       <c r="X193" t="s">
         <v>27</v>
@@ -15149,29 +15140,26 @@
       <c r="J194" t="s">
         <v>747</v>
       </c>
-      <c r="K194">
+      <c r="L194">
         <v>189</v>
       </c>
-      <c r="L194" t="s">
-        <v>25</v>
-      </c>
-      <c r="M194">
-        <v>0</v>
+      <c r="M194" t="s">
+        <v>25</v>
       </c>
       <c r="N194">
-        <v>189</v>
+        <v>0</v>
       </c>
       <c r="O194">
         <v>189</v>
       </c>
       <c r="P194">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="Q194">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R194">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="S194">
         <v>64</v>
@@ -15180,10 +15168,10 @@
         <v>64</v>
       </c>
       <c r="U194">
-        <v>0</v>
-      </c>
-      <c r="W194" t="s">
-        <v>27</v>
+        <v>64</v>
+      </c>
+      <c r="V194">
+        <v>0</v>
       </c>
       <c r="X194" t="s">
         <v>27</v>
@@ -15217,44 +15205,41 @@
       <c r="J195" t="s">
         <v>749</v>
       </c>
-      <c r="K195">
-        <v>25</v>
-      </c>
-      <c r="L195" t="s">
-        <v>25</v>
-      </c>
-      <c r="M195">
-        <v>0</v>
+      <c r="L195">
+        <v>25</v>
+      </c>
+      <c r="M195" t="s">
+        <v>25</v>
       </c>
       <c r="N195">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O195">
         <v>25</v>
       </c>
       <c r="P195">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="Q195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R195">
+        <v>0</v>
+      </c>
+      <c r="S195">
         <v>9</v>
-      </c>
-      <c r="S195">
-        <v>8</v>
       </c>
       <c r="T195">
         <v>8</v>
       </c>
       <c r="U195">
-        <v>0</v>
-      </c>
-      <c r="W195" t="s">
+        <v>8</v>
+      </c>
+      <c r="V195">
+        <v>0</v>
+      </c>
+      <c r="X195" t="s">
         <v>27</v>
-      </c>
-      <c r="X195" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.3">
@@ -15285,29 +15270,26 @@
       <c r="J196" t="s">
         <v>298</v>
       </c>
-      <c r="K196">
+      <c r="L196">
         <v>12</v>
       </c>
-      <c r="L196" t="s">
-        <v>25</v>
-      </c>
-      <c r="M196">
-        <v>0</v>
+      <c r="M196" t="s">
+        <v>25</v>
       </c>
       <c r="N196">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O196">
         <v>12</v>
       </c>
       <c r="P196">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q196">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R196">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S196">
         <v>4</v>
@@ -15316,13 +15298,13 @@
         <v>4</v>
       </c>
       <c r="U196">
-        <v>0</v>
-      </c>
-      <c r="W196" t="s">
+        <v>4</v>
+      </c>
+      <c r="V196">
+        <v>0</v>
+      </c>
+      <c r="X196" t="s">
         <v>74</v>
-      </c>
-      <c r="X196" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:24" x14ac:dyDescent="0.3">
@@ -15353,29 +15335,26 @@
       <c r="J197" t="s">
         <v>275</v>
       </c>
-      <c r="K197">
+      <c r="L197">
         <v>9</v>
       </c>
-      <c r="L197" t="s">
-        <v>25</v>
-      </c>
-      <c r="M197">
-        <v>0</v>
+      <c r="M197" t="s">
+        <v>25</v>
       </c>
       <c r="N197">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O197">
         <v>9</v>
       </c>
       <c r="P197">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R197">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S197">
         <v>3</v>
@@ -15384,13 +15363,13 @@
         <v>3</v>
       </c>
       <c r="U197">
-        <v>0</v>
-      </c>
-      <c r="W197" t="s">
+        <v>3</v>
+      </c>
+      <c r="V197">
+        <v>0</v>
+      </c>
+      <c r="X197" t="s">
         <v>27</v>
-      </c>
-      <c r="X197" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="198" spans="1:24" x14ac:dyDescent="0.3">
@@ -15421,17 +15400,14 @@
       <c r="J198" t="s">
         <v>227</v>
       </c>
-      <c r="K198">
-        <v>3</v>
-      </c>
-      <c r="L198" t="s">
-        <v>25</v>
-      </c>
-      <c r="M198">
-        <v>0</v>
+      <c r="L198">
+        <v>3</v>
+      </c>
+      <c r="M198" t="s">
+        <v>25</v>
       </c>
       <c r="N198">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O198">
         <v>3</v>
@@ -15440,10 +15416,10 @@
         <v>3</v>
       </c>
       <c r="Q198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S198">
         <v>1</v>
@@ -15452,10 +15428,10 @@
         <v>1</v>
       </c>
       <c r="U198">
-        <v>0</v>
-      </c>
-      <c r="W198" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="V198">
+        <v>0</v>
       </c>
       <c r="X198" t="s">
         <v>27</v>
@@ -15489,44 +15465,41 @@
       <c r="J199" t="s">
         <v>259</v>
       </c>
-      <c r="K199">
+      <c r="L199">
         <v>10</v>
       </c>
-      <c r="L199" t="s">
-        <v>25</v>
-      </c>
-      <c r="M199">
-        <v>0</v>
+      <c r="M199" t="s">
+        <v>25</v>
       </c>
       <c r="N199">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O199">
         <v>10</v>
       </c>
       <c r="P199">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q199">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R199">
+        <v>0</v>
+      </c>
+      <c r="S199">
         <v>4</v>
       </c>
-      <c r="S199">
-        <v>3</v>
-      </c>
       <c r="T199">
         <v>3</v>
       </c>
       <c r="U199">
-        <v>0</v>
-      </c>
-      <c r="W199" t="s">
+        <v>3</v>
+      </c>
+      <c r="V199">
+        <v>0</v>
+      </c>
+      <c r="X199" t="s">
         <v>74</v>
-      </c>
-      <c r="X199" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="200" spans="1:24" x14ac:dyDescent="0.3">
@@ -15560,29 +15533,26 @@
       <c r="J200" t="s">
         <v>754</v>
       </c>
-      <c r="K200">
+      <c r="L200">
         <v>33</v>
       </c>
-      <c r="L200" t="s">
-        <v>25</v>
-      </c>
-      <c r="M200">
-        <v>0</v>
+      <c r="M200" t="s">
+        <v>25</v>
       </c>
       <c r="N200">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="O200">
         <v>33</v>
       </c>
       <c r="P200">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="Q200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R200">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S200">
         <v>9</v>
@@ -15591,10 +15561,10 @@
         <v>9</v>
       </c>
       <c r="U200">
-        <v>0</v>
-      </c>
-      <c r="W200" t="s">
-        <v>27</v>
+        <v>9</v>
+      </c>
+      <c r="V200">
+        <v>0</v>
       </c>
       <c r="X200" t="s">
         <v>27</v>
@@ -15628,17 +15598,14 @@
       <c r="J201" t="s">
         <v>227</v>
       </c>
-      <c r="K201">
-        <v>3</v>
-      </c>
-      <c r="L201" t="s">
-        <v>25</v>
-      </c>
-      <c r="M201">
-        <v>0</v>
+      <c r="L201">
+        <v>3</v>
+      </c>
+      <c r="M201" t="s">
+        <v>25</v>
       </c>
       <c r="N201">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O201">
         <v>3</v>
@@ -15647,10 +15614,10 @@
         <v>3</v>
       </c>
       <c r="Q201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S201">
         <v>1</v>
@@ -15659,13 +15626,13 @@
         <v>1</v>
       </c>
       <c r="U201">
-        <v>0</v>
-      </c>
-      <c r="W201" t="s">
+        <v>1</v>
+      </c>
+      <c r="V201">
+        <v>0</v>
+      </c>
+      <c r="X201" t="s">
         <v>27</v>
-      </c>
-      <c r="X201" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="202" spans="1:24" x14ac:dyDescent="0.3">
@@ -15696,29 +15663,26 @@
       <c r="J202" t="s">
         <v>758</v>
       </c>
-      <c r="K202">
+      <c r="L202">
         <v>18</v>
       </c>
-      <c r="L202" t="s">
-        <v>25</v>
-      </c>
-      <c r="M202">
-        <v>0</v>
+      <c r="M202" t="s">
+        <v>25</v>
       </c>
       <c r="N202">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O202">
         <v>18</v>
       </c>
       <c r="P202">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R202">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S202">
         <v>5</v>
@@ -15727,9 +15691,12 @@
         <v>5</v>
       </c>
       <c r="U202">
-        <v>0</v>
-      </c>
-      <c r="W202" t="s">
+        <v>5</v>
+      </c>
+      <c r="V202">
+        <v>0</v>
+      </c>
+      <c r="X202" t="s">
         <v>74</v>
       </c>
     </row>
@@ -15761,29 +15728,26 @@
       <c r="J203" t="s">
         <v>214</v>
       </c>
-      <c r="K203">
+      <c r="L203">
         <v>6</v>
       </c>
-      <c r="L203" t="s">
-        <v>25</v>
-      </c>
-      <c r="M203">
-        <v>0</v>
+      <c r="M203" t="s">
+        <v>25</v>
       </c>
       <c r="N203">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O203">
         <v>6</v>
       </c>
       <c r="P203">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R203">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S203">
         <v>2</v>
@@ -15792,9 +15756,12 @@
         <v>2</v>
       </c>
       <c r="U203">
-        <v>0</v>
-      </c>
-      <c r="W203" t="s">
+        <v>2</v>
+      </c>
+      <c r="V203">
+        <v>0</v>
+      </c>
+      <c r="X203" t="s">
         <v>27</v>
       </c>
     </row>
@@ -15826,29 +15793,26 @@
       <c r="J204" t="s">
         <v>763</v>
       </c>
-      <c r="K204">
+      <c r="L204">
         <v>121</v>
       </c>
-      <c r="L204" t="s">
-        <v>25</v>
-      </c>
-      <c r="M204">
-        <v>0</v>
+      <c r="M204" t="s">
+        <v>25</v>
       </c>
       <c r="N204">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="O204">
         <v>121</v>
       </c>
       <c r="P204">
-        <v>3</v>
+        <v>121</v>
       </c>
       <c r="Q204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R204">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S204">
         <v>33</v>
@@ -15857,9 +15821,12 @@
         <v>33</v>
       </c>
       <c r="U204">
-        <v>0</v>
-      </c>
-      <c r="W204" t="s">
+        <v>33</v>
+      </c>
+      <c r="V204">
+        <v>0</v>
+      </c>
+      <c r="X204" t="s">
         <v>74</v>
       </c>
     </row>
@@ -15891,40 +15858,40 @@
       <c r="J205" t="s">
         <v>766</v>
       </c>
-      <c r="K205">
+      <c r="L205">
         <v>56</v>
       </c>
-      <c r="L205" t="s">
-        <v>25</v>
-      </c>
-      <c r="M205">
-        <v>0</v>
+      <c r="M205" t="s">
+        <v>25</v>
       </c>
       <c r="N205">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="O205">
         <v>56</v>
       </c>
       <c r="P205">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="Q205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R205">
+        <v>0</v>
+      </c>
+      <c r="S205">
         <v>16</v>
-      </c>
-      <c r="S205">
-        <v>15</v>
       </c>
       <c r="T205">
         <v>15</v>
       </c>
       <c r="U205">
-        <v>0</v>
-      </c>
-      <c r="W205" t="s">
+        <v>15</v>
+      </c>
+      <c r="V205">
+        <v>0</v>
+      </c>
+      <c r="X205" t="s">
         <v>74</v>
       </c>
     </row>
@@ -15959,29 +15926,26 @@
       <c r="J206" t="s">
         <v>769</v>
       </c>
-      <c r="K206">
+      <c r="L206">
         <v>81</v>
       </c>
-      <c r="L206" t="s">
-        <v>25</v>
-      </c>
-      <c r="M206">
-        <v>0</v>
+      <c r="M206" t="s">
+        <v>25</v>
       </c>
       <c r="N206">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="O206">
         <v>81</v>
       </c>
       <c r="P206">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="Q206">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R206">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S206">
         <v>29</v>
@@ -15990,9 +15954,12 @@
         <v>29</v>
       </c>
       <c r="U206">
-        <v>0</v>
-      </c>
-      <c r="W206" t="s">
+        <v>29</v>
+      </c>
+      <c r="V206">
+        <v>0</v>
+      </c>
+      <c r="X206" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16024,29 +15991,26 @@
       <c r="J207" t="s">
         <v>772</v>
       </c>
-      <c r="K207">
+      <c r="L207">
         <v>24</v>
       </c>
-      <c r="L207" t="s">
-        <v>25</v>
-      </c>
-      <c r="M207">
-        <v>0</v>
+      <c r="M207" t="s">
+        <v>25</v>
       </c>
       <c r="N207">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O207">
         <v>24</v>
       </c>
       <c r="P207">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q207">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R207">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S207">
         <v>8</v>
@@ -16055,9 +16019,12 @@
         <v>8</v>
       </c>
       <c r="U207">
-        <v>0</v>
-      </c>
-      <c r="W207" t="s">
+        <v>8</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="X207" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16092,29 +16059,26 @@
       <c r="J208" t="s">
         <v>774</v>
       </c>
-      <c r="K208">
+      <c r="L208">
         <v>36</v>
       </c>
-      <c r="L208" t="s">
-        <v>25</v>
-      </c>
-      <c r="M208">
-        <v>0</v>
+      <c r="M208" t="s">
+        <v>25</v>
       </c>
       <c r="N208">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O208">
         <v>36</v>
       </c>
       <c r="P208">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="Q208">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R208">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S208">
         <v>6</v>
@@ -16123,9 +16087,12 @@
         <v>6</v>
       </c>
       <c r="U208">
-        <v>0</v>
-      </c>
-      <c r="W208" t="s">
+        <v>6</v>
+      </c>
+      <c r="V208">
+        <v>0</v>
+      </c>
+      <c r="X208" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16157,40 +16124,40 @@
       <c r="J209" t="s">
         <v>777</v>
       </c>
-      <c r="K209">
+      <c r="L209">
         <v>20</v>
       </c>
-      <c r="L209" t="s">
-        <v>25</v>
-      </c>
-      <c r="M209">
-        <v>0</v>
+      <c r="M209" t="s">
+        <v>25</v>
       </c>
       <c r="N209">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O209">
         <v>20</v>
       </c>
       <c r="P209">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Q209">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R209">
+        <v>0</v>
+      </c>
+      <c r="S209">
         <v>4</v>
       </c>
-      <c r="S209">
-        <v>3</v>
-      </c>
       <c r="T209">
         <v>3</v>
       </c>
       <c r="U209">
-        <v>0</v>
-      </c>
-      <c r="W209" t="s">
+        <v>3</v>
+      </c>
+      <c r="V209">
+        <v>0</v>
+      </c>
+      <c r="X209" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16222,29 +16189,26 @@
       <c r="J210" t="s">
         <v>780</v>
       </c>
-      <c r="K210">
+      <c r="L210">
         <v>12</v>
       </c>
-      <c r="L210" t="s">
-        <v>25</v>
-      </c>
-      <c r="M210">
-        <v>0</v>
+      <c r="M210" t="s">
+        <v>25</v>
       </c>
       <c r="N210">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O210">
         <v>12</v>
       </c>
       <c r="P210">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q210">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R210">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S210">
         <v>4</v>
@@ -16253,9 +16217,12 @@
         <v>4</v>
       </c>
       <c r="U210">
-        <v>0</v>
-      </c>
-      <c r="W210" t="s">
+        <v>4</v>
+      </c>
+      <c r="V210">
+        <v>0</v>
+      </c>
+      <c r="X210" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16290,29 +16257,26 @@
       <c r="J211" t="s">
         <v>783</v>
       </c>
-      <c r="K211">
+      <c r="L211">
         <v>8</v>
       </c>
-      <c r="L211" t="s">
-        <v>25</v>
-      </c>
-      <c r="M211">
-        <v>0</v>
+      <c r="M211" t="s">
+        <v>25</v>
       </c>
       <c r="N211">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O211">
         <v>8</v>
       </c>
       <c r="P211">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q211">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R211">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S211">
         <v>3</v>
@@ -16321,9 +16285,12 @@
         <v>3</v>
       </c>
       <c r="U211">
-        <v>0</v>
-      </c>
-      <c r="W211" t="s">
+        <v>3</v>
+      </c>
+      <c r="V211">
+        <v>0</v>
+      </c>
+      <c r="X211" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16355,29 +16322,26 @@
       <c r="J212" t="s">
         <v>275</v>
       </c>
-      <c r="K212">
+      <c r="L212">
         <v>9</v>
       </c>
-      <c r="L212" t="s">
-        <v>25</v>
-      </c>
-      <c r="M212">
-        <v>0</v>
+      <c r="M212" t="s">
+        <v>25</v>
       </c>
       <c r="N212">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O212">
         <v>9</v>
       </c>
       <c r="P212">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q212">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R212">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S212">
         <v>3</v>
@@ -16386,9 +16350,12 @@
         <v>3</v>
       </c>
       <c r="U212">
-        <v>0</v>
-      </c>
-      <c r="W212" t="s">
+        <v>3</v>
+      </c>
+      <c r="V212">
+        <v>0</v>
+      </c>
+      <c r="X212" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16420,17 +16387,14 @@
       <c r="J213" t="s">
         <v>227</v>
       </c>
-      <c r="K213">
-        <v>3</v>
-      </c>
-      <c r="L213" t="s">
-        <v>25</v>
-      </c>
-      <c r="M213">
-        <v>0</v>
+      <c r="L213">
+        <v>3</v>
+      </c>
+      <c r="M213" t="s">
+        <v>25</v>
       </c>
       <c r="N213">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O213">
         <v>3</v>
@@ -16439,10 +16403,10 @@
         <v>3</v>
       </c>
       <c r="Q213">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R213">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S213">
         <v>1</v>
@@ -16451,9 +16415,12 @@
         <v>1</v>
       </c>
       <c r="U213">
-        <v>0</v>
-      </c>
-      <c r="W213" t="s">
+        <v>1</v>
+      </c>
+      <c r="V213">
+        <v>0</v>
+      </c>
+      <c r="X213" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16485,29 +16452,26 @@
       <c r="J214" t="s">
         <v>275</v>
       </c>
-      <c r="K214">
+      <c r="L214">
         <v>9</v>
       </c>
-      <c r="L214" t="s">
-        <v>25</v>
-      </c>
-      <c r="M214">
-        <v>0</v>
+      <c r="M214" t="s">
+        <v>25</v>
       </c>
       <c r="N214">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O214">
         <v>9</v>
       </c>
       <c r="P214">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q214">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R214">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S214">
         <v>3</v>
@@ -16516,9 +16480,12 @@
         <v>3</v>
       </c>
       <c r="U214">
-        <v>0</v>
-      </c>
-      <c r="W214" t="s">
+        <v>3</v>
+      </c>
+      <c r="V214">
+        <v>0</v>
+      </c>
+      <c r="X214" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16550,17 +16517,14 @@
       <c r="J215" t="s">
         <v>227</v>
       </c>
-      <c r="K215">
-        <v>3</v>
-      </c>
-      <c r="L215" t="s">
-        <v>25</v>
-      </c>
-      <c r="M215">
-        <v>0</v>
+      <c r="L215">
+        <v>3</v>
+      </c>
+      <c r="M215" t="s">
+        <v>25</v>
       </c>
       <c r="N215">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O215">
         <v>3</v>
@@ -16569,10 +16533,10 @@
         <v>3</v>
       </c>
       <c r="Q215">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S215">
         <v>1</v>
@@ -16581,9 +16545,12 @@
         <v>1</v>
       </c>
       <c r="U215">
-        <v>0</v>
-      </c>
-      <c r="W215" t="s">
+        <v>1</v>
+      </c>
+      <c r="V215">
+        <v>0</v>
+      </c>
+      <c r="X215" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16618,29 +16585,26 @@
       <c r="J216" t="s">
         <v>789</v>
       </c>
-      <c r="K216">
+      <c r="L216">
         <v>27</v>
       </c>
-      <c r="L216" t="s">
-        <v>25</v>
-      </c>
-      <c r="M216">
-        <v>0</v>
+      <c r="M216" t="s">
+        <v>25</v>
       </c>
       <c r="N216">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="O216">
         <v>27</v>
       </c>
       <c r="P216">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="Q216">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R216">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S216">
         <v>9</v>
@@ -16649,9 +16613,12 @@
         <v>9</v>
       </c>
       <c r="U216">
-        <v>0</v>
-      </c>
-      <c r="W216" t="s">
+        <v>9</v>
+      </c>
+      <c r="V216">
+        <v>0</v>
+      </c>
+      <c r="X216" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16683,29 +16650,26 @@
       <c r="J217" t="s">
         <v>353</v>
       </c>
-      <c r="K217">
+      <c r="L217">
         <v>24</v>
       </c>
-      <c r="L217" t="s">
-        <v>25</v>
-      </c>
-      <c r="M217">
-        <v>0</v>
+      <c r="M217" t="s">
+        <v>25</v>
       </c>
       <c r="N217">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O217">
         <v>24</v>
       </c>
       <c r="P217">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q217">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R217">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S217">
         <v>8</v>
@@ -16714,9 +16678,12 @@
         <v>8</v>
       </c>
       <c r="U217">
-        <v>0</v>
-      </c>
-      <c r="W217" t="s">
+        <v>8</v>
+      </c>
+      <c r="V217">
+        <v>0</v>
+      </c>
+      <c r="X217" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16748,29 +16715,26 @@
       <c r="J218" t="s">
         <v>275</v>
       </c>
-      <c r="K218">
+      <c r="L218">
         <v>9</v>
       </c>
-      <c r="L218" t="s">
-        <v>25</v>
-      </c>
-      <c r="M218">
-        <v>0</v>
+      <c r="M218" t="s">
+        <v>25</v>
       </c>
       <c r="N218">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O218">
         <v>9</v>
       </c>
       <c r="P218">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q218">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R218">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S218">
         <v>3</v>
@@ -16779,9 +16743,12 @@
         <v>3</v>
       </c>
       <c r="U218">
-        <v>0</v>
-      </c>
-      <c r="W218" t="s">
+        <v>3</v>
+      </c>
+      <c r="V218">
+        <v>0</v>
+      </c>
+      <c r="X218" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16816,29 +16783,26 @@
       <c r="J219" t="s">
         <v>796</v>
       </c>
-      <c r="K219">
+      <c r="L219">
         <v>15</v>
       </c>
-      <c r="L219" t="s">
-        <v>25</v>
-      </c>
-      <c r="M219">
-        <v>0</v>
+      <c r="M219" t="s">
+        <v>25</v>
       </c>
       <c r="N219">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O219">
         <v>15</v>
       </c>
       <c r="P219">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q219">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R219">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S219">
         <v>2</v>
@@ -16847,9 +16811,12 @@
         <v>2</v>
       </c>
       <c r="U219">
-        <v>0</v>
-      </c>
-      <c r="W219" t="s">
+        <v>2</v>
+      </c>
+      <c r="V219">
+        <v>0</v>
+      </c>
+      <c r="X219" t="s">
         <v>27</v>
       </c>
     </row>
@@ -16884,29 +16851,26 @@
       <c r="J220" t="s">
         <v>799</v>
       </c>
-      <c r="K220">
-        <v>22</v>
-      </c>
-      <c r="L220" t="s">
-        <v>25</v>
-      </c>
-      <c r="M220">
-        <v>0</v>
+      <c r="L220">
+        <v>22</v>
+      </c>
+      <c r="M220" t="s">
+        <v>25</v>
       </c>
       <c r="N220">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O220">
         <v>22</v>
       </c>
       <c r="P220">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="Q220">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R220">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S220">
         <v>3</v>
@@ -16915,9 +16879,12 @@
         <v>3</v>
       </c>
       <c r="U220">
-        <v>0</v>
-      </c>
-      <c r="W220" t="s">
+        <v>3</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+      <c r="X220" t="s">
         <v>74</v>
       </c>
     </row>
@@ -16952,29 +16919,26 @@
       <c r="J221" t="s">
         <v>801</v>
       </c>
-      <c r="K221">
+      <c r="L221">
         <v>99</v>
       </c>
-      <c r="L221" t="s">
-        <v>25</v>
-      </c>
-      <c r="M221">
-        <v>0</v>
+      <c r="M221" t="s">
+        <v>25</v>
       </c>
       <c r="N221">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="O221">
         <v>99</v>
       </c>
       <c r="P221">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="Q221">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R221">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="S221">
         <v>33</v>
@@ -16983,9 +16947,12 @@
         <v>33</v>
       </c>
       <c r="U221">
-        <v>0</v>
-      </c>
-      <c r="W221" t="s">
+        <v>33</v>
+      </c>
+      <c r="V221">
+        <v>0</v>
+      </c>
+      <c r="X221" t="s">
         <v>27</v>
       </c>
     </row>
@@ -17017,29 +16984,26 @@
       <c r="J222" t="s">
         <v>804</v>
       </c>
-      <c r="K222">
+      <c r="L222">
         <v>12</v>
       </c>
-      <c r="L222" t="s">
-        <v>25</v>
-      </c>
-      <c r="M222">
-        <v>0</v>
+      <c r="M222" t="s">
+        <v>25</v>
       </c>
       <c r="N222">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O222">
         <v>12</v>
       </c>
       <c r="P222">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q222">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R222">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S222">
         <v>4</v>
@@ -17048,9 +17012,12 @@
         <v>4</v>
       </c>
       <c r="U222">
-        <v>0</v>
-      </c>
-      <c r="W222" t="s">
+        <v>4</v>
+      </c>
+      <c r="V222">
+        <v>0</v>
+      </c>
+      <c r="X222" t="s">
         <v>74</v>
       </c>
     </row>
@@ -17082,17 +17049,14 @@
       <c r="J223" t="s">
         <v>227</v>
       </c>
-      <c r="K223">
-        <v>3</v>
-      </c>
-      <c r="L223" t="s">
-        <v>25</v>
-      </c>
-      <c r="M223">
-        <v>0</v>
+      <c r="L223">
+        <v>3</v>
+      </c>
+      <c r="M223" t="s">
+        <v>25</v>
       </c>
       <c r="N223">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O223">
         <v>3</v>
@@ -17101,10 +17065,10 @@
         <v>3</v>
       </c>
       <c r="Q223">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S223">
         <v>1</v>
@@ -17113,10 +17077,10 @@
         <v>1</v>
       </c>
       <c r="U223">
-        <v>0</v>
-      </c>
-      <c r="W223" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
       </c>
       <c r="X223" t="s">
         <v>27</v>
@@ -17150,41 +17114,38 @@
       <c r="J224" t="s">
         <v>807</v>
       </c>
-      <c r="K224">
-        <v>22</v>
-      </c>
-      <c r="L224" t="s">
-        <v>25</v>
-      </c>
-      <c r="M224">
-        <v>0</v>
+      <c r="L224">
+        <v>22</v>
+      </c>
+      <c r="M224" t="s">
+        <v>25</v>
       </c>
       <c r="N224">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O224">
         <v>22</v>
       </c>
       <c r="P224">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="Q224">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R224">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S224">
         <v>8</v>
       </c>
       <c r="T224">
+        <v>8</v>
+      </c>
+      <c r="U224">
         <v>7</v>
       </c>
-      <c r="U224">
-        <v>0</v>
-      </c>
-      <c r="W224" t="s">
-        <v>74</v>
+      <c r="V224">
+        <v>0</v>
       </c>
       <c r="X224" t="s">
         <v>74</v>
@@ -17221,29 +17182,26 @@
       <c r="J225" t="s">
         <v>809</v>
       </c>
-      <c r="K225">
+      <c r="L225">
         <v>102</v>
       </c>
-      <c r="L225" t="s">
-        <v>25</v>
-      </c>
-      <c r="M225">
-        <v>0</v>
+      <c r="M225" t="s">
+        <v>25</v>
       </c>
       <c r="N225">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="O225">
         <v>102</v>
       </c>
       <c r="P225">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="Q225">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R225">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="S225">
         <v>34</v>
@@ -17252,10 +17210,10 @@
         <v>34</v>
       </c>
       <c r="U225">
-        <v>0</v>
-      </c>
-      <c r="W225" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="V225">
+        <v>0</v>
       </c>
       <c r="X225" t="s">
         <v>27</v>
@@ -17289,41 +17247,38 @@
       <c r="J226" t="s">
         <v>812</v>
       </c>
-      <c r="K226">
+      <c r="L226">
         <v>71</v>
       </c>
-      <c r="L226" t="s">
-        <v>25</v>
-      </c>
-      <c r="M226">
-        <v>0</v>
+      <c r="M226" t="s">
+        <v>25</v>
       </c>
       <c r="N226">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="O226">
         <v>71</v>
       </c>
       <c r="P226">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="Q226">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R226">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S226">
         <v>24</v>
       </c>
       <c r="T226">
+        <v>24</v>
+      </c>
+      <c r="U226">
         <v>23</v>
       </c>
-      <c r="U226">
-        <v>0</v>
-      </c>
-      <c r="W226" t="s">
-        <v>74</v>
+      <c r="V226">
+        <v>0</v>
       </c>
       <c r="X226" t="s">
         <v>74</v>
@@ -17357,29 +17312,26 @@
       <c r="J227" t="s">
         <v>353</v>
       </c>
-      <c r="K227">
+      <c r="L227">
         <v>24</v>
       </c>
-      <c r="L227" t="s">
-        <v>25</v>
-      </c>
-      <c r="M227">
-        <v>0</v>
+      <c r="M227" t="s">
+        <v>25</v>
       </c>
       <c r="N227">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O227">
         <v>24</v>
       </c>
       <c r="P227">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q227">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R227">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S227">
         <v>8</v>
@@ -17388,13 +17340,13 @@
         <v>8</v>
       </c>
       <c r="U227">
-        <v>0</v>
-      </c>
-      <c r="W227" t="s">
+        <v>8</v>
+      </c>
+      <c r="V227">
+        <v>0</v>
+      </c>
+      <c r="X227" t="s">
         <v>27</v>
-      </c>
-      <c r="X227" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.3">
@@ -17425,29 +17377,26 @@
       <c r="J228" t="s">
         <v>275</v>
       </c>
-      <c r="K228">
+      <c r="L228">
         <v>9</v>
       </c>
-      <c r="L228" t="s">
-        <v>25</v>
-      </c>
-      <c r="M228">
-        <v>0</v>
+      <c r="M228" t="s">
+        <v>25</v>
       </c>
       <c r="N228">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O228">
         <v>9</v>
       </c>
       <c r="P228">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q228">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R228">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S228">
         <v>3</v>
@@ -17456,10 +17405,10 @@
         <v>3</v>
       </c>
       <c r="U228">
-        <v>0</v>
-      </c>
-      <c r="W228" t="s">
-        <v>27</v>
+        <v>3</v>
+      </c>
+      <c r="V228">
+        <v>0</v>
       </c>
       <c r="X228" t="s">
         <v>27</v>
@@ -17493,29 +17442,26 @@
       <c r="J229" t="s">
         <v>298</v>
       </c>
-      <c r="K229">
+      <c r="L229">
         <v>12</v>
       </c>
-      <c r="L229" t="s">
-        <v>25</v>
-      </c>
-      <c r="M229">
-        <v>0</v>
+      <c r="M229" t="s">
+        <v>25</v>
       </c>
       <c r="N229">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O229">
         <v>12</v>
       </c>
       <c r="P229">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R229">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S229">
         <v>4</v>
@@ -17524,10 +17470,10 @@
         <v>4</v>
       </c>
       <c r="U229">
-        <v>0</v>
-      </c>
-      <c r="W229" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="V229">
+        <v>0</v>
       </c>
       <c r="X229" t="s">
         <v>27</v>
@@ -17561,41 +17507,38 @@
       <c r="J230" t="s">
         <v>820</v>
       </c>
-      <c r="K230">
+      <c r="L230">
         <v>5</v>
       </c>
-      <c r="L230" t="s">
-        <v>25</v>
-      </c>
-      <c r="M230">
-        <v>0</v>
+      <c r="M230" t="s">
+        <v>25</v>
       </c>
       <c r="N230">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O230">
         <v>5</v>
       </c>
       <c r="P230">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S230">
         <v>2</v>
       </c>
       <c r="T230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U230">
-        <v>0</v>
-      </c>
-      <c r="W230" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="V230">
+        <v>0</v>
       </c>
       <c r="X230" t="s">
         <v>27</v>
@@ -17629,32 +17572,29 @@
       <c r="J231" t="s">
         <v>236</v>
       </c>
-      <c r="K231">
-        <v>1</v>
-      </c>
-      <c r="L231" t="s">
-        <v>25</v>
-      </c>
-      <c r="M231">
-        <v>0</v>
+      <c r="L231">
+        <v>1</v>
+      </c>
+      <c r="M231" t="s">
+        <v>25</v>
       </c>
       <c r="N231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O231">
         <v>1</v>
       </c>
       <c r="P231">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q231">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T231">
         <v>0</v>
@@ -17662,8 +17602,8 @@
       <c r="U231">
         <v>0</v>
       </c>
-      <c r="W231" t="s">
-        <v>74</v>
+      <c r="V231">
+        <v>0</v>
       </c>
       <c r="X231" t="s">
         <v>74</v>
@@ -17697,29 +17637,26 @@
       <c r="J232" t="s">
         <v>275</v>
       </c>
-      <c r="K232">
+      <c r="L232">
         <v>9</v>
       </c>
-      <c r="L232" t="s">
-        <v>25</v>
-      </c>
-      <c r="M232">
-        <v>0</v>
+      <c r="M232" t="s">
+        <v>25</v>
       </c>
       <c r="N232">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O232">
         <v>9</v>
       </c>
       <c r="P232">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R232">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S232">
         <v>3</v>
@@ -17728,10 +17665,10 @@
         <v>3</v>
       </c>
       <c r="U232">
-        <v>0</v>
-      </c>
-      <c r="W232" t="s">
-        <v>74</v>
+        <v>3</v>
+      </c>
+      <c r="V232">
+        <v>0</v>
       </c>
       <c r="X232" t="s">
         <v>74</v>
@@ -17765,29 +17702,26 @@
       <c r="J233" t="s">
         <v>298</v>
       </c>
-      <c r="K233">
+      <c r="L233">
         <v>12</v>
       </c>
-      <c r="L233" t="s">
-        <v>25</v>
-      </c>
-      <c r="M233">
-        <v>0</v>
+      <c r="M233" t="s">
+        <v>25</v>
       </c>
       <c r="N233">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O233">
         <v>12</v>
       </c>
       <c r="P233">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q233">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S233">
         <v>4</v>
@@ -17796,10 +17730,10 @@
         <v>4</v>
       </c>
       <c r="U233">
-        <v>0</v>
-      </c>
-      <c r="W233" t="s">
-        <v>27</v>
+        <v>4</v>
+      </c>
+      <c r="V233">
+        <v>0</v>
       </c>
       <c r="X233" t="s">
         <v>27</v>
@@ -17833,29 +17767,26 @@
       <c r="J234" t="s">
         <v>827</v>
       </c>
-      <c r="K234">
+      <c r="L234">
         <v>30</v>
       </c>
-      <c r="L234" t="s">
-        <v>25</v>
-      </c>
-      <c r="M234">
-        <v>0</v>
+      <c r="M234" t="s">
+        <v>25</v>
       </c>
       <c r="N234">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O234">
         <v>30</v>
       </c>
       <c r="P234">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="Q234">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R234">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S234">
         <v>10</v>
@@ -17864,13 +17795,13 @@
         <v>10</v>
       </c>
       <c r="U234">
-        <v>0</v>
-      </c>
-      <c r="W234" t="s">
+        <v>10</v>
+      </c>
+      <c r="V234">
+        <v>0</v>
+      </c>
+      <c r="X234" t="s">
         <v>27</v>
-      </c>
-      <c r="X234" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="235" spans="1:24" x14ac:dyDescent="0.3">
@@ -17901,29 +17832,26 @@
       <c r="J235" t="s">
         <v>290</v>
       </c>
-      <c r="K235">
+      <c r="L235">
         <v>18</v>
       </c>
-      <c r="L235" t="s">
-        <v>25</v>
-      </c>
-      <c r="M235">
-        <v>0</v>
+      <c r="M235" t="s">
+        <v>25</v>
       </c>
       <c r="N235">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O235">
         <v>18</v>
       </c>
       <c r="P235">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q235">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R235">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S235">
         <v>6</v>
@@ -17932,13 +17860,13 @@
         <v>6</v>
       </c>
       <c r="U235">
-        <v>0</v>
-      </c>
-      <c r="W235" t="s">
+        <v>6</v>
+      </c>
+      <c r="V235">
+        <v>0</v>
+      </c>
+      <c r="X235" t="s">
         <v>74</v>
-      </c>
-      <c r="X235" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="236" spans="1:24" x14ac:dyDescent="0.3">
@@ -17969,29 +17897,26 @@
       <c r="J236" t="s">
         <v>832</v>
       </c>
-      <c r="K236">
+      <c r="L236">
         <v>362.7</v>
       </c>
-      <c r="L236" t="s">
-        <v>25</v>
-      </c>
-      <c r="M236">
-        <v>0</v>
+      <c r="M236" t="s">
+        <v>25</v>
       </c>
       <c r="N236">
-        <v>362.7</v>
+        <v>0</v>
       </c>
       <c r="O236">
         <v>362.7</v>
       </c>
       <c r="P236">
-        <v>3</v>
+        <v>362.7</v>
       </c>
       <c r="Q236">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R236">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="S236">
         <v>121</v>
@@ -18000,10 +17925,10 @@
         <v>121</v>
       </c>
       <c r="U236">
-        <v>0</v>
-      </c>
-      <c r="W236" t="s">
-        <v>74</v>
+        <v>121</v>
+      </c>
+      <c r="V236">
+        <v>0</v>
       </c>
       <c r="X236" t="s">
         <v>74</v>
@@ -18037,29 +17962,26 @@
       <c r="J237" t="s">
         <v>834</v>
       </c>
-      <c r="K237">
+      <c r="L237">
         <v>161.6</v>
       </c>
-      <c r="L237" t="s">
-        <v>25</v>
-      </c>
-      <c r="M237">
-        <v>0</v>
+      <c r="M237" t="s">
+        <v>25</v>
       </c>
       <c r="N237">
-        <v>161.6</v>
+        <v>0</v>
       </c>
       <c r="O237">
         <v>161.6</v>
       </c>
       <c r="P237">
-        <v>3</v>
+        <v>161.6</v>
       </c>
       <c r="Q237">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R237">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="S237">
         <v>54</v>
@@ -18068,13 +17990,13 @@
         <v>54</v>
       </c>
       <c r="U237">
-        <v>0</v>
-      </c>
-      <c r="W237" t="s">
+        <v>54</v>
+      </c>
+      <c r="V237">
+        <v>0</v>
+      </c>
+      <c r="X237" t="s">
         <v>74</v>
-      </c>
-      <c r="X237" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="238" spans="1:24" x14ac:dyDescent="0.3">
@@ -18105,17 +18027,14 @@
       <c r="J238" t="s">
         <v>227</v>
       </c>
-      <c r="K238">
-        <v>3</v>
-      </c>
-      <c r="L238" t="s">
-        <v>25</v>
-      </c>
-      <c r="M238">
-        <v>0</v>
+      <c r="L238">
+        <v>3</v>
+      </c>
+      <c r="M238" t="s">
+        <v>25</v>
       </c>
       <c r="N238">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O238">
         <v>3</v>
@@ -18124,10 +18043,10 @@
         <v>3</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S238">
         <v>1</v>
@@ -18136,13 +18055,13 @@
         <v>1</v>
       </c>
       <c r="U238">
-        <v>0</v>
-      </c>
-      <c r="W238" t="s">
+        <v>1</v>
+      </c>
+      <c r="V238">
+        <v>0</v>
+      </c>
+      <c r="X238" t="s">
         <v>74</v>
-      </c>
-      <c r="X238" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="239" spans="1:24" x14ac:dyDescent="0.3">
@@ -18173,29 +18092,26 @@
       <c r="J239" t="s">
         <v>290</v>
       </c>
-      <c r="K239">
+      <c r="L239">
         <v>18</v>
       </c>
-      <c r="L239" t="s">
-        <v>25</v>
-      </c>
-      <c r="M239">
-        <v>0</v>
+      <c r="M239" t="s">
+        <v>25</v>
       </c>
       <c r="N239">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O239">
         <v>18</v>
       </c>
       <c r="P239">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q239">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R239">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S239">
         <v>6</v>
@@ -18204,13 +18120,13 @@
         <v>6</v>
       </c>
       <c r="U239">
-        <v>0</v>
-      </c>
-      <c r="W239" t="s">
+        <v>6</v>
+      </c>
+      <c r="V239">
+        <v>0</v>
+      </c>
+      <c r="X239" t="s">
         <v>74</v>
-      </c>
-      <c r="X239" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="240" spans="1:24" x14ac:dyDescent="0.3">
@@ -18241,29 +18157,26 @@
       <c r="J240" t="s">
         <v>354</v>
       </c>
-      <c r="K240">
+      <c r="L240">
         <v>15</v>
       </c>
-      <c r="L240" t="s">
-        <v>25</v>
-      </c>
-      <c r="M240">
-        <v>0</v>
+      <c r="M240" t="s">
+        <v>25</v>
       </c>
       <c r="N240">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O240">
         <v>15</v>
       </c>
       <c r="P240">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q240">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R240">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S240">
         <v>5</v>
@@ -18272,10 +18185,10 @@
         <v>5</v>
       </c>
       <c r="U240">
-        <v>0</v>
-      </c>
-      <c r="W240" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="V240">
+        <v>0</v>
       </c>
       <c r="X240" t="s">
         <v>27</v>
@@ -18309,17 +18222,14 @@
       <c r="J241" t="s">
         <v>227</v>
       </c>
-      <c r="K241">
-        <v>3</v>
-      </c>
-      <c r="L241" t="s">
-        <v>25</v>
-      </c>
-      <c r="M241">
-        <v>0</v>
+      <c r="L241">
+        <v>3</v>
+      </c>
+      <c r="M241" t="s">
+        <v>25</v>
       </c>
       <c r="N241">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O241">
         <v>3</v>
@@ -18328,10 +18238,10 @@
         <v>3</v>
       </c>
       <c r="Q241">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S241">
         <v>1</v>
@@ -18340,10 +18250,10 @@
         <v>1</v>
       </c>
       <c r="U241">
-        <v>0</v>
-      </c>
-      <c r="W241" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="V241">
+        <v>0</v>
       </c>
       <c r="X241" t="s">
         <v>27</v>
@@ -18377,29 +18287,26 @@
       <c r="J242" t="s">
         <v>353</v>
       </c>
-      <c r="K242">
+      <c r="L242">
         <v>24</v>
       </c>
-      <c r="L242" t="s">
-        <v>25</v>
-      </c>
-      <c r="M242">
-        <v>0</v>
+      <c r="M242" t="s">
+        <v>25</v>
       </c>
       <c r="N242">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O242">
         <v>24</v>
       </c>
       <c r="P242">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="Q242">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R242">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S242">
         <v>8</v>
@@ -18408,10 +18315,10 @@
         <v>8</v>
       </c>
       <c r="U242">
-        <v>0</v>
-      </c>
-      <c r="W242" t="s">
-        <v>27</v>
+        <v>8</v>
+      </c>
+      <c r="V242">
+        <v>0</v>
       </c>
       <c r="X242" t="s">
         <v>27</v>
@@ -18445,29 +18352,26 @@
       <c r="J243" t="s">
         <v>354</v>
       </c>
-      <c r="K243">
+      <c r="L243">
         <v>15</v>
       </c>
-      <c r="L243" t="s">
-        <v>25</v>
-      </c>
-      <c r="M243">
-        <v>0</v>
+      <c r="M243" t="s">
+        <v>25</v>
       </c>
       <c r="N243">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O243">
         <v>15</v>
       </c>
       <c r="P243">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q243">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R243">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S243">
         <v>5</v>
@@ -18476,13 +18380,13 @@
         <v>5</v>
       </c>
       <c r="U243">
-        <v>0</v>
-      </c>
-      <c r="W243" t="s">
+        <v>5</v>
+      </c>
+      <c r="V243">
+        <v>0</v>
+      </c>
+      <c r="X243" t="s">
         <v>74</v>
-      </c>
-      <c r="X243" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="244" spans="1:24" x14ac:dyDescent="0.3">
@@ -18513,29 +18417,26 @@
       <c r="J244" t="s">
         <v>214</v>
       </c>
-      <c r="K244">
+      <c r="L244">
         <v>6</v>
       </c>
-      <c r="L244" t="s">
-        <v>25</v>
-      </c>
-      <c r="M244">
-        <v>0</v>
+      <c r="M244" t="s">
+        <v>25</v>
       </c>
       <c r="N244">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O244">
         <v>6</v>
       </c>
       <c r="P244">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q244">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R244">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S244">
         <v>2</v>
@@ -18544,13 +18445,13 @@
         <v>2</v>
       </c>
       <c r="U244">
-        <v>0</v>
-      </c>
-      <c r="W244" t="s">
+        <v>2</v>
+      </c>
+      <c r="V244">
+        <v>0</v>
+      </c>
+      <c r="X244" t="s">
         <v>74</v>
-      </c>
-      <c r="X244" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="245" spans="1:24" x14ac:dyDescent="0.3">
@@ -18581,29 +18482,26 @@
       <c r="J245" t="s">
         <v>354</v>
       </c>
-      <c r="K245">
+      <c r="L245">
         <v>15</v>
       </c>
-      <c r="L245" t="s">
-        <v>25</v>
-      </c>
-      <c r="M245">
-        <v>0</v>
+      <c r="M245" t="s">
+        <v>25</v>
       </c>
       <c r="N245">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O245">
         <v>15</v>
       </c>
       <c r="P245">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q245">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R245">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S245">
         <v>5</v>
@@ -18612,10 +18510,10 @@
         <v>5</v>
       </c>
       <c r="U245">
-        <v>0</v>
-      </c>
-      <c r="W245" t="s">
-        <v>74</v>
+        <v>5</v>
+      </c>
+      <c r="V245">
+        <v>0</v>
       </c>
       <c r="X245" t="s">
         <v>74</v>
@@ -18649,29 +18547,26 @@
       <c r="J246" t="s">
         <v>275</v>
       </c>
-      <c r="K246">
+      <c r="L246">
         <v>9</v>
       </c>
-      <c r="L246" t="s">
-        <v>25</v>
-      </c>
-      <c r="M246">
-        <v>0</v>
+      <c r="M246" t="s">
+        <v>25</v>
       </c>
       <c r="N246">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O246">
         <v>9</v>
       </c>
       <c r="P246">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="Q246">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R246">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S246">
         <v>3</v>
@@ -18680,10 +18575,10 @@
         <v>3</v>
       </c>
       <c r="U246">
-        <v>0</v>
-      </c>
-      <c r="W246" t="s">
-        <v>74</v>
+        <v>3</v>
+      </c>
+      <c r="V246">
+        <v>0</v>
       </c>
       <c r="X246" t="s">
         <v>74</v>
@@ -18717,17 +18612,14 @@
       <c r="J247" t="s">
         <v>227</v>
       </c>
-      <c r="K247">
-        <v>3</v>
-      </c>
-      <c r="L247" t="s">
-        <v>25</v>
-      </c>
-      <c r="M247">
-        <v>0</v>
+      <c r="L247">
+        <v>3</v>
+      </c>
+      <c r="M247" t="s">
+        <v>25</v>
       </c>
       <c r="N247">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O247">
         <v>3</v>
@@ -18736,10 +18628,10 @@
         <v>3</v>
       </c>
       <c r="Q247">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S247">
         <v>1</v>
@@ -18748,13 +18640,13 @@
         <v>1</v>
       </c>
       <c r="U247">
-        <v>0</v>
-      </c>
-      <c r="W247" t="s">
+        <v>1</v>
+      </c>
+      <c r="V247">
+        <v>0</v>
+      </c>
+      <c r="X247" t="s">
         <v>74</v>
-      </c>
-      <c r="X247" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="248" spans="1:24" x14ac:dyDescent="0.3">
@@ -18785,29 +18677,26 @@
       <c r="J248" t="s">
         <v>214</v>
       </c>
-      <c r="K248">
+      <c r="L248">
         <v>6</v>
       </c>
-      <c r="L248" t="s">
-        <v>25</v>
-      </c>
-      <c r="M248">
-        <v>0</v>
+      <c r="M248" t="s">
+        <v>25</v>
       </c>
       <c r="N248">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O248">
         <v>6</v>
       </c>
       <c r="P248">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q248">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S248">
         <v>2</v>
@@ -18816,13 +18705,13 @@
         <v>2</v>
       </c>
       <c r="U248">
-        <v>0</v>
-      </c>
-      <c r="W248" t="s">
+        <v>2</v>
+      </c>
+      <c r="V248">
+        <v>0</v>
+      </c>
+      <c r="X248" t="s">
         <v>74</v>
-      </c>
-      <c r="X248" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="249" spans="1:24" x14ac:dyDescent="0.3">
@@ -18853,29 +18742,26 @@
       <c r="J249" t="s">
         <v>354</v>
       </c>
-      <c r="K249">
+      <c r="L249">
         <v>15</v>
       </c>
-      <c r="L249" t="s">
-        <v>25</v>
-      </c>
-      <c r="M249">
-        <v>0</v>
+      <c r="M249" t="s">
+        <v>25</v>
       </c>
       <c r="N249">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O249">
         <v>15</v>
       </c>
       <c r="P249">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="Q249">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R249">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S249">
         <v>5</v>
@@ -18884,10 +18770,10 @@
         <v>5</v>
       </c>
       <c r="U249">
-        <v>0</v>
-      </c>
-      <c r="W249" t="s">
-        <v>74</v>
+        <v>5</v>
+      </c>
+      <c r="V249">
+        <v>0</v>
       </c>
       <c r="X249" t="s">
         <v>74</v>
@@ -18921,29 +18807,26 @@
       <c r="J250" t="s">
         <v>214</v>
       </c>
-      <c r="K250">
+      <c r="L250">
         <v>6</v>
       </c>
-      <c r="L250" t="s">
-        <v>25</v>
-      </c>
-      <c r="M250">
-        <v>0</v>
+      <c r="M250" t="s">
+        <v>25</v>
       </c>
       <c r="N250">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O250">
         <v>6</v>
       </c>
       <c r="P250">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q250">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R250">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S250">
         <v>2</v>
@@ -18952,10 +18835,10 @@
         <v>2</v>
       </c>
       <c r="U250">
-        <v>0</v>
-      </c>
-      <c r="W250" t="s">
-        <v>74</v>
+        <v>2</v>
+      </c>
+      <c r="V250">
+        <v>0</v>
       </c>
       <c r="X250" t="s">
         <v>74</v>
@@ -18980,17 +18863,14 @@
       <c r="F251" t="s">
         <v>852</v>
       </c>
-      <c r="K251">
-        <v>548</v>
-      </c>
-      <c r="N251">
+      <c r="L251">
         <v>548</v>
       </c>
       <c r="O251">
         <v>548</v>
       </c>
-      <c r="X251" t="s">
-        <v>27</v>
+      <c r="P251">
+        <v>548</v>
       </c>
     </row>
     <row r="252" spans="1:24" x14ac:dyDescent="0.3">
